--- a/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v5.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v5.xlsx
@@ -735,7 +735,7 @@
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9028571428571429</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -748,9 +748,13 @@
         </is>
       </c>
       <c r="Z2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Stakeholder Feedback Solicitation</t>
+        </is>
+      </c>
       <c r="AB2" t="b">
         <v>0</v>
       </c>
@@ -1086,9 +1090,13 @@
         </is>
       </c>
       <c r="Z4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Concept Planning</t>
+        </is>
+      </c>
       <c r="AB4" t="b">
         <v>0</v>
       </c>
@@ -1265,7 +1273,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Skill name uses 'Planning' which is not present in evidence; evidence describes gathering and evaluating concepts, not planning</t>
+          <t>Skill name uses 'Planning' but evidence describes gathering and evaluating concepts, not planning</t>
         </is>
       </c>
       <c r="AF5" t="b">
@@ -1717,22 +1725,26 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>keep:0, "Idea Viability Evaluation":6, "Solution Viability Assessment":1</t>
+          <t>keep:0, "Idea Viability Evaluation":7</t>
         </is>
       </c>
       <c r="Z8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Solution Viability Assessment</t>
+        </is>
+      </c>
       <c r="AB8" t="b">
         <v>0</v>
       </c>
@@ -2206,12 +2218,12 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>keep:0, "Solution Research":5, "Information Research":2</t>
+          <t>keep:1, "Solution Research":4, "Information Research":2</t>
         </is>
       </c>
       <c r="Z11" t="b">
@@ -2365,22 +2377,26 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>keep:5, "Solution Presentation":2</t>
+          <t>keep:3, "Solution Presentation":4</t>
         </is>
       </c>
       <c r="Z12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Solution Viability Assessment</t>
+        </is>
+      </c>
       <c r="AB12" t="b">
         <v>0</v>
       </c>
@@ -2700,9 +2716,13 @@
         </is>
       </c>
       <c r="Z14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Idea Viability Evaluation</t>
+        </is>
+      </c>
       <c r="AB14" t="b">
         <v>0</v>
       </c>
@@ -3017,16 +3037,16 @@
         <v>1</v>
       </c>
       <c r="W16" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>keep:0, "Discussion Facilitation":7</t>
+          <t>keep:3, "Discussion Facilitation":4</t>
         </is>
       </c>
       <c r="Z16" t="b">
@@ -3805,16 +3825,16 @@
         <v>1</v>
       </c>
       <c r="W21" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>keep:0, "Insight Presentation":7</t>
+          <t>keep:1, "Insight Presentation":6</t>
         </is>
       </c>
       <c r="Z21" t="b">
@@ -6003,13 +6023,17 @@
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>keep:4, "Device Configuration":3</t>
+          <t>keep:5, "Device Configuration":2</t>
         </is>
       </c>
       <c r="Z36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Device Inventory Management</t>
+        </is>
+      </c>
       <c r="AB36" t="b">
         <v>0</v>
       </c>
@@ -6543,7 +6567,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Password Strength Creation</t>
+          <t>Password Creation</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -6639,15 +6663,19 @@
         </is>
       </c>
       <c r="V40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X40" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/7: </t>
+        </is>
+      </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:2, "Password Creation":5</t>
         </is>
       </c>
       <c r="Z40" t="b">
@@ -6814,9 +6842,13 @@
         </is>
       </c>
       <c r="Z41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA41" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>Security Plan Communication</t>
+        </is>
+      </c>
       <c r="AB41" t="b">
         <v>0</v>
       </c>
@@ -7131,22 +7163,18 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>keep:6, "Physical Security Plan Communication":1</t>
+          <t>keep:5, "Physical Security Plan Communication":2</t>
         </is>
       </c>
       <c r="Z43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>Physical Security Planning</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="b">
         <v>0</v>
       </c>
@@ -7517,7 +7545,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Security Trend Monitoring</t>
+          <t>Security Development Monitoring</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -7617,15 +7645,19 @@
         </is>
       </c>
       <c r="V46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W46" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X46" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 4/7: </t>
+        </is>
+      </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>keep:4, "Security Development Monitoring":3</t>
+          <t>keep:3, "Security Development Monitoring":4</t>
         </is>
       </c>
       <c r="Z46" t="b">
@@ -7950,12 +7982,12 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>keep:2, "Multi-factor Authentication Enablement":5</t>
+          <t>keep:1, "Multi-factor Authentication Enablement":6</t>
         </is>
       </c>
       <c r="Z48" t="b">
@@ -8246,7 +8278,7 @@
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr">
@@ -8452,7 +8484,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Documentation Preparation</t>
+          <t>Evaluation Documentation</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -8539,15 +8571,19 @@
         </is>
       </c>
       <c r="V52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W52" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X52" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 4/7: </t>
+        </is>
+      </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>keep:4, "Evaluation Documentation":3</t>
+          <t>keep:1, "Evaluation Documentation":4, "Evaluation Documentation Preparation":2</t>
         </is>
       </c>
       <c r="Z52" t="b">
@@ -8598,7 +8634,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ICT Gap Identification</t>
+          <t>Ict Gap Identification</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -8697,19 +8733,15 @@
         </is>
       </c>
       <c r="V53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 6/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>keep:1, "ICT Gap Identification":6</t>
+          <t>keep:4, "ICT Gap Identification":3</t>
         </is>
       </c>
       <c r="Z53" t="b">
@@ -9017,7 +9049,7 @@
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>keep:5, "Innovative Idea Investigation":2</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z55" t="b">
@@ -9068,7 +9100,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Numerical Data Interpretation</t>
+          <t>Financial Impact Interpretation</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -9155,15 +9187,19 @@
         </is>
       </c>
       <c r="V56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W56" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X56" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 4/7: </t>
+        </is>
+      </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>keep:4, "Financial Impact Interpretation":3</t>
+          <t>keep:3, "Financial Impact Interpretation":4</t>
         </is>
       </c>
       <c r="Z56" t="b">
@@ -9450,12 +9486,12 @@
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>keep:6, "Action Plan Scheduling":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z58" t="b">
@@ -9596,12 +9632,12 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>keep:6, "Implementation Difficulty Assessment":1</t>
+          <t>keep:4, "Change Implementation Planning":2, "Change Difficulty Assessment":1</t>
         </is>
       </c>
       <c r="Z59" t="b">
@@ -10817,7 +10853,7 @@
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>keep:5, "Feedback Management":2</t>
+          <t>keep:4, "Feedback Management":3</t>
         </is>
       </c>
       <c r="Z67" t="b">
@@ -11557,16 +11593,16 @@
         <v>1</v>
       </c>
       <c r="W72" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>keep:1, "Privacy Policy Documentation":6</t>
+          <t>keep:0, "Privacy Policy Documentation":7</t>
         </is>
       </c>
       <c r="Z72" t="b">
@@ -11876,7 +11912,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Foundation Skill describes work style (sequencing, scheduling, monitoring) already embedded in PCs and other skills; not a distinct standalone skill</t>
+          <t>Foundation Skill describes work style (sequencing, scheduling, monitoring) already embedded in PCs and other skills</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -12068,7 +12104,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Digital Information Security</t>
+          <t>Secure Digital Handling</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -12158,19 +12194,15 @@
         </is>
       </c>
       <c r="V76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 4/7: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>keep:3, "Digital Information Security":4</t>
+          <t>keep:6, "Digital Information Security":1</t>
         </is>
       </c>
       <c r="Z76" t="b">
@@ -12314,16 +12346,16 @@
         <v>1</v>
       </c>
       <c r="W77" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>keep:1, "Policy Distribution":6</t>
+          <t>keep:0, "Policy Distribution":7</t>
         </is>
       </c>
       <c r="Z77" t="b">
@@ -12627,12 +12659,12 @@
         <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>keep:6, "Blockchain Platform Installation":1</t>
+          <t>keep:5, "Blockchain Platform Installation":2</t>
         </is>
       </c>
       <c r="Z79" t="b">
@@ -12787,12 +12819,12 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>keep:1, "Blockchain Anomaly Problem Solving/Blockchain Anomaly Solving":4, "Blockchain Anomaly Resolution":2</t>
+          <t>keep:0, "Blockchain Anomaly Problem Solving":5, "Blockchain Anomaly Resolution":2</t>
         </is>
       </c>
       <c r="Z80" t="b">
@@ -13264,9 +13296,13 @@
         </is>
       </c>
       <c r="Z83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA83" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>Documentation Submission</t>
+        </is>
+      </c>
       <c r="AB83" t="b">
         <v>0</v>
       </c>
@@ -13420,9 +13456,13 @@
         </is>
       </c>
       <c r="Z84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA84" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>Design Documentation Preparation</t>
+        </is>
+      </c>
       <c r="AB84" t="b">
         <v>0</v>
       </c>
@@ -13723,12 +13763,12 @@
         <v>0</v>
       </c>
       <c r="W86" t="n">
-        <v>0.95</v>
+        <v>0.9516666666666667</v>
       </c>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Maintenance Schedule Development":1</t>
         </is>
       </c>
       <c r="Z86" t="b">
@@ -13879,16 +13919,16 @@
         <v>1</v>
       </c>
       <c r="W87" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>keep:0, "Maintenance Testing":7</t>
+          <t>keep:2, "Maintenance Testing":5</t>
         </is>
       </c>
       <c r="Z87" t="b">
@@ -15317,9 +15357,13 @@
         </is>
       </c>
       <c r="Z96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA96" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>False Data Detection</t>
+        </is>
+      </c>
       <c r="AB96" t="b">
         <v>0</v>
       </c>
@@ -15467,16 +15511,16 @@
         <v>1</v>
       </c>
       <c r="W97" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>keep:1, "Dataset Creation":6</t>
+          <t>keep:0, "Dataset Creation":7</t>
         </is>
       </c>
       <c r="Z97" t="b">
@@ -16450,9 +16494,13 @@
         </is>
       </c>
       <c r="Z103" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA103" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>Data Log Ingestion</t>
+        </is>
+      </c>
       <c r="AB103" t="b">
         <v>0</v>
       </c>
@@ -16604,12 +16652,12 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>keep:1, "Threat Findings Communication":6</t>
+          <t>keep:3, "Threat Findings Communication":4</t>
         </is>
       </c>
       <c r="Z104" t="b">
@@ -16768,13 +16816,17 @@
       <c r="X105" t="inlineStr"/>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>keep:4, "Threat Data Collation":3</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z105" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA105" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>Data Log Ingestion</t>
+        </is>
+      </c>
       <c r="AB105" t="b">
         <v>0</v>
       </c>
@@ -16921,7 +16973,7 @@
       <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:5, "Anomaly Detection":1, "Anomaly Troubleshooting":1</t>
         </is>
       </c>
       <c r="Z106" t="b">
@@ -17222,7 +17274,7 @@
         <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X108" t="inlineStr"/>
       <c r="Y108" t="inlineStr">
@@ -17992,7 +18044,7 @@
       <c r="X113" t="inlineStr"/>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>keep:4, "Protection Strategy Coordination":3</t>
+          <t>keep:4, "Protection Strategy Coordination/Protection Plan Coordination":3</t>
         </is>
       </c>
       <c r="Z113" t="b">
@@ -18000,9 +18052,13 @@
       </c>
       <c r="AA113" t="inlineStr"/>
       <c r="AB113" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC113" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>FS describes work style (planning and coordinating) rather than a distinct task; capability already embedded in strategy development PCs</t>
+        </is>
+      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -18293,7 +18349,7 @@
         <v>0</v>
       </c>
       <c r="W115" t="n">
-        <v>0.95</v>
+        <v>0.9428571428571428</v>
       </c>
       <c r="X115" t="inlineStr"/>
       <c r="Y115" t="inlineStr">
@@ -18761,7 +18817,7 @@
       <c r="X118" t="inlineStr"/>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>keep:4, "Risk Evaluation":3</t>
+          <t>keep:5, "Risk Assessment":2</t>
         </is>
       </c>
       <c r="Z118" t="b">
@@ -19225,12 +19281,12 @@
         <v>0</v>
       </c>
       <c r="W121" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X121" t="inlineStr"/>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>keep:6, "Data Type Identification":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z121" t="b">
@@ -19389,7 +19445,7 @@
       <c r="X122" t="inlineStr"/>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>keep:6, "Feedback Submission Management":1</t>
+          <t>keep:6, "Feedback Management":1</t>
         </is>
       </c>
       <c r="Z122" t="b">
@@ -19706,12 +19762,12 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>keep:0, "Contextual Anomaly Identification":4, "Security Contextual Problem Solving":2, "Contextual Anomaly Detection":1</t>
+          <t>keep:0, "Contextual Anomaly Identification":5, "Security Contextual Problem Solving":2</t>
         </is>
       </c>
       <c r="Z124" t="b">
@@ -19874,7 +19930,7 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>keep:0, "Security Findings Documentation/Security Requirements Documentation":7</t>
+          <t>keep:0, "Security Requirements Documentation":7</t>
         </is>
       </c>
       <c r="Z125" t="b">
@@ -20028,7 +20084,7 @@
         <v>0</v>
       </c>
       <c r="W126" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X126" t="inlineStr"/>
       <c r="Y126" t="inlineStr">
@@ -20530,7 +20586,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>FS describes work style (planning) not a distinct task; capability already embedded in PCs and other skills</t>
+          <t>FS describes work style (planning and reviewing) not a distinct task; capability already embedded in PCs and other skills</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -21354,7 +21410,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>FS describes work style (autonomous decision making) not a distinct task; capability is implicit in PCs</t>
+          <t>FS describes work style (autonomous decision making) not a distinct task; capability already implicit in PCs</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -22369,16 +22425,16 @@
         <v>1</v>
       </c>
       <c r="W140" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>keep:0, "Incident Response Exercise Design":7</t>
+          <t>keep:0, "Incident Response Exercise Design":6, "Incident Response Training":1</t>
         </is>
       </c>
       <c r="Z140" t="b">
@@ -22730,9 +22786,13 @@
         </is>
       </c>
       <c r="Z142" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA142" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>Technical Data Interpretation</t>
+        </is>
+      </c>
       <c r="AB142" t="b">
         <v>0</v>
       </c>
@@ -22897,7 +22957,7 @@
         <v>0</v>
       </c>
       <c r="W143" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X143" t="inlineStr"/>
       <c r="Y143" t="inlineStr">
@@ -23262,9 +23322,13 @@
       </c>
       <c r="AA145" t="inlineStr"/>
       <c r="AB145" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC145" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>FS capability is embedded in other skills such as Risk Analysis and Incident Response Plan Evaluation, not a distinct standalone skill</t>
+        </is>
+      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
@@ -23423,9 +23487,13 @@
         </is>
       </c>
       <c r="Z146" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA146" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>Critical Function Identification</t>
+        </is>
+      </c>
       <c r="AB146" t="b">
         <v>0</v>
       </c>
@@ -23596,7 +23664,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>FS describes work style/strategic compliance already embedded in other skills and PCs; not a distinct unit task</t>
+          <t>FS describes work style/strategic compliance rather than a distinct unit task; capability is implicit in other skills and PCs</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -24091,9 +24159,13 @@
         </is>
       </c>
       <c r="Z150" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA150" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>Disaster Strategy Documentation</t>
+        </is>
+      </c>
       <c r="AB150" t="b">
         <v>0</v>
       </c>
@@ -24256,9 +24328,13 @@
         </is>
       </c>
       <c r="Z151" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA151" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>Compliance Management</t>
+        </is>
+      </c>
       <c r="AB151" t="b">
         <v>0</v>
       </c>
@@ -24590,9 +24666,13 @@
         </is>
       </c>
       <c r="Z153" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA153" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>Strategic Planning</t>
+        </is>
+      </c>
       <c r="AB153" t="b">
         <v>0</v>
       </c>
@@ -24750,7 +24830,7 @@
         <v>0</v>
       </c>
       <c r="W154" t="n">
-        <v>0.9428571428571428</v>
+        <v>0.95</v>
       </c>
       <c r="X154" t="inlineStr"/>
       <c r="Y154" t="inlineStr">
@@ -24763,9 +24843,13 @@
       </c>
       <c r="AA154" t="inlineStr"/>
       <c r="AB154" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC154" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Foundation Skill describes a general problem‑solving capability that is already embedded in multiple PC‑based skills (e.g., Risk Analysis, Contingency Plan Development) and does not add a distinct standalone activity</t>
+        </is>
+      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
@@ -24924,9 +25008,13 @@
         </is>
       </c>
       <c r="Z155" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA155" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>Disaster Recovery Planning</t>
+        </is>
+      </c>
       <c r="AB155" t="b">
         <v>0</v>
       </c>
@@ -25245,12 +25333,12 @@
         <v>0</v>
       </c>
       <c r="W157" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X157" t="inlineStr"/>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>keep:6, "Priority Planning":1</t>
+          <t>keep:5, "Strategy Prioritisation":2</t>
         </is>
       </c>
       <c r="Z157" t="b">
@@ -25798,7 +25886,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Answer Substantiation</t>
+          <t>Response Substantiation</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -25818,16 +25906,16 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Provides clear, evidence‑based responses to stakeholder questions, supporting answers with relevant data and rationale.</t>
+          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting decisions with relevant data and reasoning.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>evidence based response, stakeholder inquiry, substantiated answer, data support, rationale provision</t>
+          <t>evidence based answers, stakeholder queries, substantiated responses, data support, reasoning justification</t>
         </is>
       </c>
       <c r="J161" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -25882,14 +25970,14 @@
       </c>
       <c r="U161" t="inlineStr">
         <is>
-          <t>Answer Substantiation</t>
+          <t>Response Substantiation</t>
         </is>
       </c>
       <c r="V161" t="b">
         <v>0</v>
       </c>
       <c r="W161" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="X161" t="inlineStr">
         <is>
@@ -25914,7 +26002,7 @@
       </c>
       <c r="AG161" t="inlineStr">
         <is>
-          <t>Provides clear, evidence‑based responses to stakeholder questions, supporting answers with relevant data and rationale.</t>
+          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting decisions with relevant data and reasoning.</t>
         </is>
       </c>
       <c r="AH161" t="b">
@@ -25922,7 +26010,7 @@
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>evidence based response, stakeholder inquiry, substantiated answer, data support, rationale provision</t>
+          <t>evidence based answers, stakeholder queries, substantiated responses, data support, reasoning justification</t>
         </is>
       </c>
       <c r="AJ161" t="b">
@@ -25963,12 +26051,12 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Assists in confirming and documenting the types of information stored on each registered digital device.</t>
+          <t>Assists in identifying and confirming the types of information stored on each registered digital device.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>device data inventory, information classification, data mapping, asset documentation, storage verification</t>
+          <t>device data inventory, information classification, storage verification, digital asset audit, data mapping</t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -26059,7 +26147,7 @@
       </c>
       <c r="AG162" t="inlineStr">
         <is>
-          <t>Assists in confirming and documenting the types of information stored on each registered digital device.</t>
+          <t>Assists in identifying and confirming the types of information stored on each registered digital device.</t>
         </is>
       </c>
       <c r="AH162" t="b">
@@ -26067,7 +26155,7 @@
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>device data inventory, information classification, data mapping, asset documentation, storage verification</t>
+          <t>device data inventory, information classification, storage verification, digital asset audit, data mapping</t>
         </is>
       </c>
       <c r="AJ162" t="b">
@@ -26088,7 +26176,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Sign‑off Coordination</t>
+          <t>Sign‑off Acquisition</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -26108,16 +26196,16 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Secures final approval from designated personnel by managing sign‑off processes and confirming compliance.</t>
+          <t>Secures final approval from designated stakeholders by coordinating, presenting, and confirming sign‑off requirements.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>approval process, stakeholder engagement, compliance confirmation, sign‑off management, finalisation</t>
+          <t>approval coordination, stakeholder engagement, sign‑off confirmation, final authorization, approval documentation</t>
         </is>
       </c>
       <c r="J163" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
@@ -26174,14 +26262,14 @@
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>Sign‑off Coordination</t>
+          <t>Sign‑off Acquisition</t>
         </is>
       </c>
       <c r="V163" t="b">
         <v>0</v>
       </c>
       <c r="W163" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="X163" t="inlineStr">
         <is>
@@ -26206,7 +26294,7 @@
       </c>
       <c r="AG163" t="inlineStr">
         <is>
-          <t>Secures final approval from designated personnel by managing sign‑off processes and confirming compliance.</t>
+          <t>Secures final approval from designated stakeholders by coordinating, presenting, and confirming sign‑off requirements.</t>
         </is>
       </c>
       <c r="AH163" t="b">
@@ -26214,7 +26302,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>approval process, stakeholder engagement, compliance confirmation, sign‑off management, finalisation</t>
+          <t>approval coordination, stakeholder engagement, sign‑off confirmation, final authorization, approval documentation</t>
         </is>
       </c>
       <c r="AJ163" t="b">
@@ -26255,12 +26343,12 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation, considering relevant legislation and policies.</t>
+          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>process evaluation, transaction analysis, blockchain suitability, regulatory compliance, organisational policy</t>
+          <t>process analysis, transaction evaluation, blockchain suitability, organisational fit, compliance assessment</t>
         </is>
       </c>
       <c r="J164" t="n">
@@ -26361,7 +26449,7 @@
       </c>
       <c r="AG164" t="inlineStr">
         <is>
-          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation, considering relevant legislation and policies.</t>
+          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation.</t>
         </is>
       </c>
       <c r="AH164" t="b">
@@ -26369,7 +26457,7 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>process evaluation, transaction analysis, blockchain suitability, regulatory compliance, organisational policy</t>
+          <t>process analysis, transaction evaluation, blockchain suitability, organisational fit, compliance assessment</t>
         </is>
       </c>
       <c r="AJ164" t="b">
@@ -26410,12 +26498,12 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Collaborates with relevant personnel to discuss and confirm data log requirements and processing strategy.</t>
+          <t>Facilitates discussion with relevant personnel to confirm data log requirements and processing strategy.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>data log requirements, processing strategy, personnel consultation, requirement discussion, log strategy confirmation</t>
+          <t>data log requirements, processing strategy, personnel consultation, requirement confirmation, collaborative discussion</t>
         </is>
       </c>
       <c r="J165" t="n">
@@ -26506,7 +26594,7 @@
       </c>
       <c r="AG165" t="inlineStr">
         <is>
-          <t>Collaborates with relevant personnel to discuss and confirm data log requirements and processing strategy.</t>
+          <t>Facilitates discussion with relevant personnel to confirm data log requirements and processing strategy.</t>
         </is>
       </c>
       <c r="AH165" t="b">
@@ -26514,7 +26602,7 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>data log requirements, processing strategy, personnel consultation, requirement discussion, log strategy confirmation</t>
+          <t>data log requirements, processing strategy, personnel consultation, requirement confirmation, collaborative discussion</t>
         </is>
       </c>
       <c r="AJ165" t="b">
@@ -26555,7 +26643,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Evaluates gathered threat data results to confirm reliability and consistency before further processing.</t>
+          <t>Evaluates threat data results to confirm reliability and consistency before further processing.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -26651,7 +26739,7 @@
       </c>
       <c r="AG166" t="inlineStr">
         <is>
-          <t>Evaluates gathered threat data results to confirm reliability and consistency before further processing.</t>
+          <t>Evaluates threat data results to confirm reliability and consistency before further processing.</t>
         </is>
       </c>
       <c r="AH166" t="b">
@@ -26700,12 +26788,12 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Assess the current protection plan's effectiveness and ensure it aligns with organisational and legislative requirements.</t>
+          <t>Evaluates how well the current protection plan meets organisational needs and regulatory standards.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>protection plan assessment, organisational alignment, effectiveness analysis, legislative compliance, critical asset identification</t>
+          <t>plan effectiveness, organisational requirements, alignment assessment, critical assets, legislative compliance</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -26803,7 +26891,7 @@
       </c>
       <c r="AG167" t="inlineStr">
         <is>
-          <t>Assess the current protection plan's effectiveness and ensure it aligns with organisational and legislative requirements.</t>
+          <t>Evaluates how well the current protection plan meets organisational needs and regulatory standards.</t>
         </is>
       </c>
       <c r="AH167" t="b">
@@ -26811,7 +26899,7 @@
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>protection plan assessment, organisational alignment, effectiveness analysis, legislative compliance, critical asset identification</t>
+          <t>plan effectiveness, organisational requirements, alignment assessment, critical assets, legislative compliance</t>
         </is>
       </c>
       <c r="AJ167" t="b">
@@ -26837,7 +26925,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>DOMAIN_KNOWLEDGE</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -26847,17 +26935,17 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>THEORETICAL</t>
+          <t>PRACTICAL</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Aligns the current incident response plan with required standards and documents the comparison for stakeholders.</t>
+          <t>Aligns the current incident response plan with requirements and documents the comparison for stakeholders.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>incident response plan, alignment assessment, documentation, requirements mapping, stakeholder feedback</t>
+          <t>incident response plan, alignment, documentation, requirements, feedback</t>
         </is>
       </c>
       <c r="J168" t="n">
@@ -26962,7 +27050,7 @@
       </c>
       <c r="AG168" t="inlineStr">
         <is>
-          <t>Aligns the current incident response plan with required standards and documents the comparison for stakeholders.</t>
+          <t>Aligns the current incident response plan with requirements and documents the comparison for stakeholders.</t>
         </is>
       </c>
       <c r="AH168" t="b">
@@ -26970,7 +27058,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>incident response plan, alignment assessment, documentation, requirements mapping, stakeholder feedback</t>
+          <t>incident response plan, alignment, documentation, requirements, feedback</t>
         </is>
       </c>
       <c r="AJ168" t="b">
@@ -27011,12 +27099,12 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Assist in gathering, processing, and preserving evidence in line with organisational and legal requirements.</t>
+          <t>Assist in gathering, processing and preserving incident evidence in line with organisational requirements and standards.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>evidence collection, evidence processing, evidence preservation, incident response, legal compliance</t>
+          <t>evidence collection, evidence processing, evidence preservation, incident response, organisational requirements</t>
         </is>
       </c>
       <c r="J169" t="n">
@@ -27120,7 +27208,7 @@
       </c>
       <c r="AG169" t="inlineStr">
         <is>
-          <t>Assist in gathering, processing, and preserving evidence in line with organisational and legal requirements.</t>
+          <t>Assist in gathering, processing and preserving incident evidence in line with organisational requirements and standards.</t>
         </is>
       </c>
       <c r="AH169" t="b">
@@ -27128,7 +27216,7 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>evidence collection, evidence processing, evidence preservation, incident response, legal compliance</t>
+          <t>evidence collection, evidence processing, evidence preservation, incident response, organisational requirements</t>
         </is>
       </c>
       <c r="AJ169" t="b">

--- a/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v5.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v5.xlsx
@@ -735,7 +735,7 @@
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9028571428571429</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1725,16 +1725,16 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>keep:0, "Idea Viability Evaluation":7</t>
+          <t>keep:0, "Idea Viability Evaluation":6, "Solution Viability Assessment":1</t>
         </is>
       </c>
       <c r="Z8" t="b">
@@ -2214,16 +2214,16 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>keep:1, "Solution Research":4, "Information Research":2</t>
+          <t>keep:0, "Solution Research":7</t>
         </is>
       </c>
       <c r="Z11" t="b">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>keep:3, "Solution Presentation":4</t>
+          <t>keep:2, "Solution Presentation":5</t>
         </is>
       </c>
       <c r="Z12" t="b">
@@ -2548,16 +2548,16 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>keep:1, "Solution Refinement":6</t>
+          <t>keep:0, "Solution Refinement":7</t>
         </is>
       </c>
       <c r="Z13" t="b">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Discussion Facilitation</t>
+          <t>Team Facilitation</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3034,19 +3034,15 @@
         </is>
       </c>
       <c r="V16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 4/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>keep:3, "Discussion Facilitation":4</t>
+          <t>keep:4, "Discussion Facilitation":3</t>
         </is>
       </c>
       <c r="Z16" t="b">
@@ -3825,16 +3821,16 @@
         <v>1</v>
       </c>
       <c r="W21" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>keep:1, "Insight Presentation":6</t>
+          <t>keep:0, "Insight Presentation":7</t>
         </is>
       </c>
       <c r="Z21" t="b">
@@ -4469,7 +4465,7 @@
         <v>1</v>
       </c>
       <c r="W25" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9028571428571429</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -5101,7 +5097,7 @@
         <v>1</v>
       </c>
       <c r="W29" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -5110,7 +5106,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Technology Platform Utilisation":1</t>
         </is>
       </c>
       <c r="Z29" t="b">
@@ -6023,7 +6019,7 @@
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>keep:5, "Device Configuration":2</t>
+          <t>keep:4, "Device Configuration":3</t>
         </is>
       </c>
       <c r="Z36" t="b">
@@ -6365,7 +6361,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>domain term "inventory" (asset management) not found in unit text</t>
+          <t>Skill name uses 'Inventory Management' while evidence describes creating and maintaining a register; 'inventory' is not mentioned and implies a different activity</t>
         </is>
       </c>
       <c r="AF38" t="b">
@@ -6567,7 +6563,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Password Creation</t>
+          <t>Password Strength Creation</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -6663,19 +6659,15 @@
         </is>
       </c>
       <c r="V40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 5/7: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>keep:2, "Password Creation":5</t>
+          <t>keep:6, "Password Creation":1</t>
         </is>
       </c>
       <c r="Z40" t="b">
@@ -6842,13 +6834,9 @@
         </is>
       </c>
       <c r="Z41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>Security Plan Communication</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA41" t="inlineStr"/>
       <c r="AB41" t="b">
         <v>0</v>
       </c>
@@ -6996,16 +6984,16 @@
         <v>1</v>
       </c>
       <c r="W42" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>keep:1, "Data Risk Categorisation":6</t>
+          <t>keep:0, "Data Risk Categorisation":7</t>
         </is>
       </c>
       <c r="Z42" t="b">
@@ -7163,18 +7151,22 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>keep:5, "Physical Security Plan Communication":2</t>
+          <t>keep:6, "Physical Security Planning":1</t>
         </is>
       </c>
       <c r="Z43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>Physical Security Planning</t>
+        </is>
+      </c>
       <c r="AB43" t="b">
         <v>0</v>
       </c>
@@ -7545,7 +7537,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Security Development Monitoring</t>
+          <t>Security Trend Monitoring</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -7645,19 +7637,15 @@
         </is>
       </c>
       <c r="V46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 4/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>keep:3, "Security Development Monitoring":4</t>
+          <t>keep:4, "Security Development Monitoring":3</t>
         </is>
       </c>
       <c r="Z46" t="b">
@@ -7982,12 +7970,12 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>keep:1, "Multi-factor Authentication Enablement":6</t>
+          <t>keep:2, "Multi-factor Authentication Enablement":5</t>
         </is>
       </c>
       <c r="Z48" t="b">
@@ -8278,7 +8266,7 @@
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr">
@@ -8574,16 +8562,16 @@
         <v>1</v>
       </c>
       <c r="W52" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>keep:1, "Evaluation Documentation":4, "Evaluation Documentation Preparation":2</t>
+          <t>keep:0, "Evaluation Documentation":7</t>
         </is>
       </c>
       <c r="Z52" t="b">
@@ -9100,7 +9088,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Financial Impact Interpretation</t>
+          <t>Numerical Data Interpretation</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -9187,19 +9175,15 @@
         </is>
       </c>
       <c r="V56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 4/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>keep:3, "Financial Impact Interpretation":4</t>
+          <t>keep:4, "Financial Impact Interpretation":3</t>
         </is>
       </c>
       <c r="Z56" t="b">
@@ -9632,12 +9616,12 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>keep:4, "Change Implementation Planning":2, "Change Difficulty Assessment":1</t>
+          <t>keep:6, "Implementation Difficulty Assessment":1</t>
         </is>
       </c>
       <c r="Z59" t="b">
@@ -10853,7 +10837,7 @@
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>keep:4, "Feedback Management":3</t>
+          <t>keep:5, "Feedback Management":2</t>
         </is>
       </c>
       <c r="Z67" t="b">
@@ -12197,12 +12181,12 @@
         <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>keep:6, "Digital Information Security":1</t>
+          <t>keep:5, "Digital Information Security":2</t>
         </is>
       </c>
       <c r="Z76" t="b">
@@ -12664,7 +12648,7 @@
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>keep:5, "Blockchain Platform Installation":2</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z79" t="b">
@@ -12715,7 +12699,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Blockchain Anomaly Problem Solving</t>
+          <t>Blockchain Anomaly Resolution</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -12819,12 +12803,12 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>keep:0, "Blockchain Anomaly Problem Solving":5, "Blockchain Anomaly Resolution":2</t>
+          <t>keep:0, "Blockchain Anomaly Resolution":6, "Blockchain Anomaly Problem Solving":1</t>
         </is>
       </c>
       <c r="Z80" t="b">
@@ -12832,9 +12816,13 @@
       </c>
       <c r="AA80" t="inlineStr"/>
       <c r="AB80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC80" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Foundation Skill describes problem‑solving behavior that is already embedded in the unit's problem‑solving requirement and other blockchain solution skills</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -13296,13 +13284,9 @@
         </is>
       </c>
       <c r="Z83" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>Documentation Submission</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA83" t="inlineStr"/>
       <c r="AB83" t="b">
         <v>0</v>
       </c>
@@ -13456,13 +13440,9 @@
         </is>
       </c>
       <c r="Z84" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>Design Documentation Preparation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA84" t="inlineStr"/>
       <c r="AB84" t="b">
         <v>0</v>
       </c>
@@ -13763,7 +13743,7 @@
         <v>0</v>
       </c>
       <c r="W86" t="n">
-        <v>0.9516666666666667</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr">
@@ -13923,12 +13903,12 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>keep:2, "Maintenance Testing":5</t>
+          <t>keep:1, "Maintenance Testing":6</t>
         </is>
       </c>
       <c r="Z87" t="b">
@@ -15357,13 +15337,9 @@
         </is>
       </c>
       <c r="Z96" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>False Data Detection</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA96" t="inlineStr"/>
       <c r="AB96" t="b">
         <v>0</v>
       </c>
@@ -15511,16 +15487,16 @@
         <v>1</v>
       </c>
       <c r="W97" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>keep:0, "Dataset Creation":7</t>
+          <t>keep:1, "Dataset Creation":6</t>
         </is>
       </c>
       <c r="Z97" t="b">
@@ -15528,7 +15504,7 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>Threat Data Collection</t>
+          <t>Threat Data Collation</t>
         </is>
       </c>
       <c r="AB97" t="b">
@@ -16708,7 +16684,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Threat Data Collection</t>
+          <t>Threat Data Collation</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -16808,15 +16784,19 @@
         </is>
       </c>
       <c r="V105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W105" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X105" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/7: </t>
+        </is>
+      </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:2, "Threat Data Collation":5</t>
         </is>
       </c>
       <c r="Z105" t="b">
@@ -16824,7 +16804,7 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>Data Log Ingestion</t>
+          <t>Dataset Creation</t>
         </is>
       </c>
       <c r="AB105" t="b">
@@ -16973,7 +16953,7 @@
       <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>keep:5, "Anomaly Detection":1, "Anomaly Troubleshooting":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z106" t="b">
@@ -17274,7 +17254,7 @@
         <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X108" t="inlineStr"/>
       <c r="Y108" t="inlineStr">
@@ -18044,7 +18024,7 @@
       <c r="X113" t="inlineStr"/>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>keep:4, "Protection Strategy Coordination/Protection Plan Coordination":3</t>
+          <t>keep:4, "Protection Strategy Coordination":3</t>
         </is>
       </c>
       <c r="Z113" t="b">
@@ -18056,7 +18036,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>FS describes work style (planning and coordinating) rather than a distinct task; capability already embedded in strategy development PCs</t>
+          <t>FS describes work style (planning and coordination) rather than a distinct task; capability already embedded in PCs and other skills</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -18349,7 +18329,7 @@
         <v>0</v>
       </c>
       <c r="W115" t="n">
-        <v>0.9428571428571428</v>
+        <v>0.95</v>
       </c>
       <c r="X115" t="inlineStr"/>
       <c r="Y115" t="inlineStr">
@@ -18812,12 +18792,12 @@
         <v>0</v>
       </c>
       <c r="W118" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X118" t="inlineStr"/>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>keep:5, "Risk Assessment":2</t>
+          <t>keep:3, "Risk Assessment":3, "Risk Evaluation":1</t>
         </is>
       </c>
       <c r="Z118" t="b">
@@ -19440,12 +19420,12 @@
         <v>0</v>
       </c>
       <c r="W122" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X122" t="inlineStr"/>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>keep:6, "Feedback Management":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z122" t="b">
@@ -20084,7 +20064,7 @@
         <v>0</v>
       </c>
       <c r="W126" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X126" t="inlineStr"/>
       <c r="Y126" t="inlineStr">
@@ -20406,7 +20386,7 @@
         <v>0</v>
       </c>
       <c r="W128" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X128" t="inlineStr"/>
       <c r="Y128" t="inlineStr">
@@ -21410,7 +21390,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>FS describes work style (autonomous decision making) not a distinct task; capability already implicit in PCs</t>
+          <t>FS describes work style (autonomous decision making) not a distinct task; capability is implicit in PCs</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -21909,16 +21889,16 @@
         <v>1</v>
       </c>
       <c r="W137" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>keep:0, "Incident Response Plan Evaluation":7</t>
+          <t>keep:1, "Incident Response Plan Evaluation":6</t>
         </is>
       </c>
       <c r="Z137" t="b">
@@ -22425,16 +22405,16 @@
         <v>1</v>
       </c>
       <c r="W140" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>keep:0, "Incident Response Exercise Design":6, "Incident Response Training":1</t>
+          <t>keep:0, "Incident Response Exercise Design":7</t>
         </is>
       </c>
       <c r="Z140" t="b">
@@ -22777,12 +22757,12 @@
         <v>0</v>
       </c>
       <c r="W142" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X142" t="inlineStr"/>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Technical Data Interpretation":1</t>
         </is>
       </c>
       <c r="Z142" t="b">
@@ -23326,7 +23306,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>FS capability is embedded in other skills such as Risk Analysis and Incident Response Plan Evaluation, not a distinct standalone skill</t>
+          <t>FS capability is embedded in other skills such as Risk Analysis and Incident Response Plan Evaluation</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -23491,7 +23471,7 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>Critical Function Identification</t>
+          <t>Risk Analysis</t>
         </is>
       </c>
       <c r="AB146" t="b">
@@ -24847,7 +24827,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Foundation Skill describes a general problem‑solving capability that is already embedded in multiple PC‑based skills (e.g., Risk Analysis, Contingency Plan Development) and does not add a distinct standalone activity</t>
+          <t>Foundation Skill describes a work style (problem solving) that is already embedded in multiple performance criteria and other skills</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -25338,7 +25318,7 @@
       <c r="X157" t="inlineStr"/>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>keep:5, "Strategy Prioritisation":2</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z157" t="b">
@@ -25837,13 +25817,9 @@
         </is>
       </c>
       <c r="Z160" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA160" t="inlineStr">
-        <is>
-          <t>Risk Analysis</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA160" t="inlineStr"/>
       <c r="AB160" t="b">
         <v>0</v>
       </c>
@@ -25915,7 +25891,7 @@
         </is>
       </c>
       <c r="J161" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -25977,7 +25953,7 @@
         <v>0</v>
       </c>
       <c r="W161" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="X161" t="inlineStr">
         <is>
@@ -26056,7 +26032,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>device data inventory, information classification, storage verification, digital asset audit, data mapping</t>
+          <t>device data inventory, information classification, storage verification, asset documentation, data mapping</t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -26155,7 +26131,7 @@
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>device data inventory, information classification, storage verification, digital asset audit, data mapping</t>
+          <t>device data inventory, information classification, storage verification, asset documentation, data mapping</t>
         </is>
       </c>
       <c r="AJ162" t="b">
@@ -26201,7 +26177,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>approval coordination, stakeholder engagement, sign‑off confirmation, final authorization, approval documentation</t>
+          <t>approval coordination, stakeholder confirmation, sign‑off documentation, final endorsement, approval process</t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -26302,7 +26278,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>approval coordination, stakeholder engagement, sign‑off confirmation, final authorization, approval documentation</t>
+          <t>approval coordination, stakeholder confirmation, sign‑off documentation, final endorsement, approval process</t>
         </is>
       </c>
       <c r="AJ163" t="b">
@@ -26348,7 +26324,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>process analysis, transaction evaluation, blockchain suitability, organisational fit, compliance assessment</t>
+          <t>organisational processes, transaction types, blockchain suitability, legislative impact, policy compliance</t>
         </is>
       </c>
       <c r="J164" t="n">
@@ -26457,7 +26433,7 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>process analysis, transaction evaluation, blockchain suitability, organisational fit, compliance assessment</t>
+          <t>organisational processes, transaction types, blockchain suitability, legislative impact, policy compliance</t>
         </is>
       </c>
       <c r="AJ164" t="b">
@@ -26507,7 +26483,7 @@
         </is>
       </c>
       <c r="J165" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
@@ -26569,7 +26545,7 @@
         <v>0</v>
       </c>
       <c r="W165" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="X165" t="inlineStr">
         <is>
@@ -26643,7 +26619,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Evaluates threat data results to confirm reliability and consistency before further processing.</t>
+          <t>Evaluates gathered threat data results to ensure reliability and consistency across sources and methods.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -26739,7 +26715,7 @@
       </c>
       <c r="AG166" t="inlineStr">
         <is>
-          <t>Evaluates threat data results to confirm reliability and consistency before further processing.</t>
+          <t>Evaluates gathered threat data results to ensure reliability and consistency across sources and methods.</t>
         </is>
       </c>
       <c r="AH166" t="b">
@@ -26788,12 +26764,12 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Evaluates how well the current protection plan meets organisational needs and regulatory standards.</t>
+          <t>Assess the current protection plan's effectiveness and ensure it aligns with organisational and legislative requirements.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>plan effectiveness, organisational requirements, alignment assessment, critical assets, legislative compliance</t>
+          <t>protection plan assessment, organisational alignment, effectiveness analysis, legislative compliance, critical asset identification</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -26891,7 +26867,7 @@
       </c>
       <c r="AG167" t="inlineStr">
         <is>
-          <t>Evaluates how well the current protection plan meets organisational needs and regulatory standards.</t>
+          <t>Assess the current protection plan's effectiveness and ensure it aligns with organisational and legislative requirements.</t>
         </is>
       </c>
       <c r="AH167" t="b">
@@ -26899,7 +26875,7 @@
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>plan effectiveness, organisational requirements, alignment assessment, critical assets, legislative compliance</t>
+          <t>protection plan assessment, organisational alignment, effectiveness analysis, legislative compliance, critical asset identification</t>
         </is>
       </c>
       <c r="AJ167" t="b">
@@ -26940,12 +26916,12 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Aligns the current incident response plan with requirements and documents the comparison for stakeholders.</t>
+          <t>The worker assesses the current incident response plan, documents its conformity with requirements, and submits it for feedback.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>incident response plan, alignment, documentation, requirements, feedback</t>
+          <t>incident response plan, alignment assessment, documentation, requirements compliance, feedback submission</t>
         </is>
       </c>
       <c r="J168" t="n">
@@ -27050,7 +27026,7 @@
       </c>
       <c r="AG168" t="inlineStr">
         <is>
-          <t>Aligns the current incident response plan with requirements and documents the comparison for stakeholders.</t>
+          <t>The worker assesses the current incident response plan, documents its conformity with requirements, and submits it for feedback.</t>
         </is>
       </c>
       <c r="AH168" t="b">
@@ -27058,7 +27034,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>incident response plan, alignment, documentation, requirements, feedback</t>
+          <t>incident response plan, alignment assessment, documentation, requirements compliance, feedback submission</t>
         </is>
       </c>
       <c r="AJ168" t="b">
@@ -27099,7 +27075,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Assist in gathering, processing and preserving incident evidence in line with organisational requirements and standards.</t>
+          <t>Assist in gathering, processing, and preserving incident evidence in line with organisational requirements and standards.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -27208,7 +27184,7 @@
       </c>
       <c r="AG169" t="inlineStr">
         <is>
-          <t>Assist in gathering, processing and preserving incident evidence in line with organisational requirements and standards.</t>
+          <t>Assist in gathering, processing, and preserving incident evidence in line with organisational requirements and standards.</t>
         </is>
       </c>
       <c r="AH169" t="b">
@@ -27257,12 +27233,12 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Identify essential business functions, critical data, and software, and assess ICT risk impacts on them.</t>
+          <t>Identify essential business functions, critical data, and software, and assess risk impacts on ICT systems.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>business critical functions, security environment, critical data, software assets, ICT risk assessment</t>
+          <t>business critical functions, security environment, critical data, software assets, risk impact assessment</t>
         </is>
       </c>
       <c r="J170" t="n">
@@ -27361,7 +27337,7 @@
       </c>
       <c r="AG170" t="inlineStr">
         <is>
-          <t>Identify essential business functions, critical data, and software, and assess ICT risk impacts on them.</t>
+          <t>Identify essential business functions, critical data, and software, and assess risk impacts on ICT systems.</t>
         </is>
       </c>
       <c r="AH170" t="b">
@@ -27369,7 +27345,7 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>business critical functions, security environment, critical data, software assets, ICT risk assessment</t>
+          <t>business critical functions, security environment, critical data, software assets, risk impact assessment</t>
         </is>
       </c>
       <c r="AJ170" t="b">

--- a/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v5.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v5.xlsx
@@ -748,13 +748,9 @@
         </is>
       </c>
       <c r="Z2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Stakeholder Feedback Solicitation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="b">
         <v>0</v>
       </c>
@@ -1090,13 +1086,9 @@
         </is>
       </c>
       <c r="Z4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Concept Planning</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="b">
         <v>0</v>
       </c>
@@ -1729,22 +1721,18 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>keep:0, "Idea Viability Evaluation":6, "Solution Viability Assessment":1</t>
+          <t>keep:0, "Idea Viability Evaluation":5, "Solution Viability Assessment":2</t>
         </is>
       </c>
       <c r="Z8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Solution Viability Assessment</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="b">
         <v>0</v>
       </c>
@@ -2381,22 +2369,18 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>keep:2, "Solution Presentation":5</t>
+          <t>keep:3, "Solution Presentation":4</t>
         </is>
       </c>
       <c r="Z12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Solution Viability Assessment</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="b">
         <v>0</v>
       </c>
@@ -2548,16 +2532,16 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>keep:0, "Solution Refinement":7</t>
+          <t>keep:2, "Solution Refinement":5</t>
         </is>
       </c>
       <c r="Z13" t="b">
@@ -2716,13 +2700,9 @@
         </is>
       </c>
       <c r="Z14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Idea Viability Evaluation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="b">
         <v>0</v>
       </c>
@@ -2930,7 +2910,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Team Facilitation</t>
+          <t>Discussion Facilitation</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3034,15 +3014,19 @@
         </is>
       </c>
       <c r="V16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X16" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 6/7: </t>
+        </is>
+      </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>keep:4, "Discussion Facilitation":3</t>
+          <t>keep:1, "Discussion Facilitation":6</t>
         </is>
       </c>
       <c r="Z16" t="b">
@@ -4465,7 +4449,7 @@
         <v>1</v>
       </c>
       <c r="W25" t="n">
-        <v>0.9028571428571429</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -5097,7 +5081,7 @@
         <v>1</v>
       </c>
       <c r="W29" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -5106,7 +5090,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>keep:6, "Technology Platform Utilisation":1</t>
+          <t>keep:5, "Technology Platform Utilisation":2</t>
         </is>
       </c>
       <c r="Z29" t="b">
@@ -6023,13 +6007,9 @@
         </is>
       </c>
       <c r="Z36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>Device Inventory Management</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="b">
         <v>0</v>
       </c>
@@ -6361,7 +6341,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>Skill name uses 'Inventory Management' while evidence describes creating and maintaining a register; 'inventory' is not mentioned and implies a different activity</t>
+          <t>Skill name uses 'Inventory Management' while evidence describes creating and maintaining a register, which is a distinct activity</t>
         </is>
       </c>
       <c r="AF38" t="b">
@@ -6662,12 +6642,12 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>keep:6, "Password Creation":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z40" t="b">
@@ -7156,7 +7136,7 @@
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>keep:6, "Physical Security Planning":1</t>
+          <t>keep:6, "Physical Security Plan Communication":1</t>
         </is>
       </c>
       <c r="Z43" t="b">
@@ -7640,7 +7620,7 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0.95</v>
+        <v>0.9524999999999999</v>
       </c>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr">
@@ -7859,7 +7839,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Multi-factor Authentication Enablement</t>
+          <t>Two-factor Authentication Enablement</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -7966,16 +7946,16 @@
         <v>1</v>
       </c>
       <c r="W48" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t>postprocess: spelling/redundancy</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>keep:2, "Multi-factor Authentication Enablement":5</t>
+          <t>keep:4, "Multi-factor Authentication Enablement":3</t>
         </is>
       </c>
       <c r="Z48" t="b">
@@ -8562,16 +8542,16 @@
         <v>1</v>
       </c>
       <c r="W52" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>keep:0, "Evaluation Documentation":7</t>
+          <t>keep:0, "Evaluation Documentation":6, "Evaluation Documentation Preparation":1</t>
         </is>
       </c>
       <c r="Z52" t="b">
@@ -8729,7 +8709,7 @@
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>keep:4, "ICT Gap Identification":3</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z53" t="b">
@@ -9183,7 +9163,7 @@
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>keep:4, "Financial Impact Interpretation":3</t>
+          <t>keep:5, "Financial Impact Interpretation":2</t>
         </is>
       </c>
       <c r="Z56" t="b">
@@ -9616,12 +9596,12 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>keep:6, "Implementation Difficulty Assessment":1</t>
+          <t>keep:5, "Change Implementation Planning":1, "Implementation Difficulty Assessment":1</t>
         </is>
       </c>
       <c r="Z59" t="b">
@@ -9637,7 +9617,7 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>Skill name includes 'Planning' which is not present in the evidence; evidence only involves evaluating difficulty</t>
+          <t>Skill name uses 'Planning' but evidence only involves evaluating difficulty, not planning</t>
         </is>
       </c>
       <c r="AF59" t="b">
@@ -10739,7 +10719,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Feedback Handling</t>
+          <t>Feedback Management</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -10829,15 +10809,19 @@
         </is>
       </c>
       <c r="V67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W67" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X67" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 4/7: </t>
+        </is>
+      </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>keep:5, "Feedback Management":2</t>
+          <t>keep:3, "Feedback Management":4</t>
         </is>
       </c>
       <c r="Z67" t="b">
@@ -12181,12 +12165,12 @@
         <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>keep:5, "Digital Information Security":2</t>
+          <t>keep:6, "Digital Information Security":1</t>
         </is>
       </c>
       <c r="Z76" t="b">
@@ -12330,16 +12314,16 @@
         <v>1</v>
       </c>
       <c r="W77" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>keep:0, "Policy Distribution":7</t>
+          <t>keep:1, "Policy Distribution":6</t>
         </is>
       </c>
       <c r="Z77" t="b">
@@ -12803,12 +12787,12 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>keep:0, "Blockchain Anomaly Resolution":6, "Blockchain Anomaly Problem Solving":1</t>
+          <t>keep:0, "Blockchain Anomaly Resolution":4, "Blockchain Anomaly Problem Solving/Blockchain Anomaly Solving":3</t>
         </is>
       </c>
       <c r="Z80" t="b">
@@ -12820,7 +12804,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Foundation Skill describes problem‑solving behavior that is already embedded in the unit's problem‑solving requirement and other blockchain solution skills</t>
+          <t>Foundation Skill describes problem‑solving capability already embedded in other skills and PCs; it is a work style rather than a distinct task</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -13743,12 +13727,12 @@
         <v>0</v>
       </c>
       <c r="W86" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>keep:6, "Maintenance Schedule Development":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z86" t="b">
@@ -13899,16 +13883,16 @@
         <v>1</v>
       </c>
       <c r="W87" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>keep:1, "Maintenance Testing":6</t>
+          <t>keep:0, "Maintenance Testing":7</t>
         </is>
       </c>
       <c r="Z87" t="b">
@@ -15491,12 +15475,12 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>keep:1, "Dataset Creation":6</t>
+          <t>keep:2, "Dataset Creation":5</t>
         </is>
       </c>
       <c r="Z97" t="b">
@@ -15504,7 +15488,7 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>Threat Data Collation</t>
+          <t>Threat Data Collection</t>
         </is>
       </c>
       <c r="AB97" t="b">
@@ -16684,7 +16668,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Threat Data Collation</t>
+          <t>Threat Data Collection</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -16784,19 +16768,15 @@
         </is>
       </c>
       <c r="V105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W105" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 5/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X105" t="inlineStr"/>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>keep:2, "Threat Data Collation":5</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z105" t="b">
@@ -16948,12 +16928,12 @@
         <v>0</v>
       </c>
       <c r="W106" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Anomaly Detection":1</t>
         </is>
       </c>
       <c r="Z106" t="b">
@@ -18024,7 +18004,7 @@
       <c r="X113" t="inlineStr"/>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>keep:4, "Protection Strategy Coordination":3</t>
+          <t>keep:5, "Protection Strategy Coordination":2</t>
         </is>
       </c>
       <c r="Z113" t="b">
@@ -18036,7 +18016,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>FS describes work style (planning and coordination) rather than a distinct task; capability already embedded in PCs and other skills</t>
+          <t>FS describes work style (planning and coordination) already embedded in PCs and other skills</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -18176,7 +18156,7 @@
         <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>0.95</v>
+        <v>0.9428571428571428</v>
       </c>
       <c r="X114" t="inlineStr"/>
       <c r="Y114" t="inlineStr">
@@ -18792,12 +18772,12 @@
         <v>0</v>
       </c>
       <c r="W118" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X118" t="inlineStr"/>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>keep:3, "Risk Assessment":3, "Risk Evaluation":1</t>
+          <t>keep:5, "Risk Evaluation":1, "Protection Risk Assessment":1</t>
         </is>
       </c>
       <c r="Z118" t="b">
@@ -19631,7 +19611,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Contextual Anomaly Identification</t>
+          <t>Problem Solving in Security</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -19738,16 +19718,16 @@
         <v>1</v>
       </c>
       <c r="W124" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t>postprocess: spelling/redundancy</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>keep:0, "Contextual Anomaly Identification":5, "Security Contextual Problem Solving":2</t>
+          <t>keep:0, "Security Contextual Problem Solving":3, "Contextual Anomaly Identification":3, "Contextual Anomaly Detection":1</t>
         </is>
       </c>
       <c r="Z124" t="b">
@@ -19755,9 +19735,13 @@
       </c>
       <c r="AA124" t="inlineStr"/>
       <c r="AB124" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC124" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Foundation Skill describes a work style (recognising anomalies) that is already embedded in other skills and PCs</t>
+        </is>
+      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
@@ -19901,16 +19885,16 @@
         <v>1</v>
       </c>
       <c r="W125" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>keep:0, "Security Requirements Documentation":7</t>
+          <t>keep:1, "Security Requirements Documentation":6</t>
         </is>
       </c>
       <c r="Z125" t="b">
@@ -20386,7 +20370,7 @@
         <v>0</v>
       </c>
       <c r="W128" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X128" t="inlineStr"/>
       <c r="Y128" t="inlineStr">
@@ -21193,16 +21177,16 @@
         <v>1</v>
       </c>
       <c r="W133" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>keep:0, "Technical Documentation Reading":7</t>
+          <t>keep:2, "Technical Documentation Reading":5</t>
         </is>
       </c>
       <c r="Z133" t="b">
@@ -21390,7 +21374,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>FS describes work style (autonomous decision making) not a distinct task; capability is implicit in PCs</t>
+          <t>FS describes work style (autonomous decision making) not a distinct task; capability already implicit in PCs</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -21889,16 +21873,16 @@
         <v>1</v>
       </c>
       <c r="W137" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>keep:1, "Incident Response Plan Evaluation":6</t>
+          <t>keep:0, "Incident Response Plan Evaluation":7</t>
         </is>
       </c>
       <c r="Z137" t="b">
@@ -22757,12 +22741,12 @@
         <v>0</v>
       </c>
       <c r="W142" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X142" t="inlineStr"/>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>keep:6, "Technical Data Interpretation":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z142" t="b">
@@ -23306,7 +23290,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>FS capability is embedded in other skills such as Risk Analysis and Incident Response Plan Evaluation</t>
+          <t>FS capability is embedded in other skills such as Risk Analysis and Incident Response Plan Evaluation, not a distinct standalone skill</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -23467,13 +23451,9 @@
         </is>
       </c>
       <c r="Z146" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA146" t="inlineStr">
-        <is>
-          <t>Risk Analysis</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA146" t="inlineStr"/>
       <c r="AB146" t="b">
         <v>0</v>
       </c>
@@ -23644,7 +23624,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>FS describes work style/strategic compliance rather than a distinct unit task; capability is implicit in other skills and PCs</t>
+          <t>Foundation Skill describes work style (ensuring compliance) already implicit in other skills and not a distinct task for this unit</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -23809,9 +23789,13 @@
         </is>
       </c>
       <c r="Z148" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA148" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>Disaster Recovery Planning</t>
+        </is>
+      </c>
       <c r="AB148" t="b">
         <v>0</v>
       </c>
@@ -24308,13 +24292,9 @@
         </is>
       </c>
       <c r="Z151" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA151" t="inlineStr">
-        <is>
-          <t>Compliance Management</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA151" t="inlineStr"/>
       <c r="AB151" t="b">
         <v>0</v>
       </c>
@@ -24646,13 +24626,9 @@
         </is>
       </c>
       <c r="Z153" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA153" t="inlineStr">
-        <is>
-          <t>Strategic Planning</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA153" t="inlineStr"/>
       <c r="AB153" t="b">
         <v>0</v>
       </c>
@@ -24823,13 +24799,9 @@
       </c>
       <c r="AA154" t="inlineStr"/>
       <c r="AB154" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Foundation Skill describes a work style (problem solving) that is already embedded in multiple performance criteria and other skills</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC154" t="inlineStr"/>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
@@ -25318,7 +25290,7 @@
       <c r="X157" t="inlineStr"/>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:5, "Strategy Prioritisation":2</t>
         </is>
       </c>
       <c r="Z157" t="b">
@@ -25882,16 +25854,16 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting decisions with relevant data and reasoning.</t>
+          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting each response with relevant data or rationale.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>evidence based answers, stakeholder queries, substantiated responses, data support, reasoning justification</t>
+          <t>evidence based answers, stakeholder queries, substantiated responses, data support, rationale provision</t>
         </is>
       </c>
       <c r="J161" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -25953,7 +25925,7 @@
         <v>0</v>
       </c>
       <c r="W161" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="X161" t="inlineStr">
         <is>
@@ -25978,7 +25950,7 @@
       </c>
       <c r="AG161" t="inlineStr">
         <is>
-          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting decisions with relevant data and reasoning.</t>
+          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting each response with relevant data or rationale.</t>
         </is>
       </c>
       <c r="AH161" t="b">
@@ -25986,7 +25958,7 @@
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>evidence based answers, stakeholder queries, substantiated responses, data support, reasoning justification</t>
+          <t>evidence based answers, stakeholder queries, substantiated responses, data support, rationale provision</t>
         </is>
       </c>
       <c r="AJ161" t="b">
@@ -26017,7 +25989,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>ASSIST</t>
+          <t>APPLY</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -26027,16 +25999,16 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Assists in identifying and confirming the types of information stored on each registered digital device.</t>
+          <t>Identify and confirm the types of information stored on each registered digital device within the organisation.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>device data inventory, information classification, storage verification, asset documentation, data mapping</t>
+          <t>device data inventory, information classification, data mapping, asset documentation, storage verification</t>
         </is>
       </c>
       <c r="J162" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
@@ -26098,7 +26070,7 @@
         <v>0</v>
       </c>
       <c r="W162" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="X162" t="inlineStr">
         <is>
@@ -26123,7 +26095,7 @@
       </c>
       <c r="AG162" t="inlineStr">
         <is>
-          <t>Assists in identifying and confirming the types of information stored on each registered digital device.</t>
+          <t>Identify and confirm the types of information stored on each registered digital device within the organisation.</t>
         </is>
       </c>
       <c r="AH162" t="b">
@@ -26131,7 +26103,7 @@
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>device data inventory, information classification, storage verification, asset documentation, data mapping</t>
+          <t>device data inventory, information classification, data mapping, asset documentation, storage verification</t>
         </is>
       </c>
       <c r="AJ162" t="b">
@@ -26152,7 +26124,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Sign‑off Acquisition</t>
+          <t>Sign‑off Coordination</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -26172,12 +26144,12 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Secures final approval from designated stakeholders by coordinating, presenting, and confirming sign‑off requirements.</t>
+          <t>Secures final approval from designated personnel by organising, presenting, and confirming required documentation.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>approval coordination, stakeholder confirmation, sign‑off documentation, final endorsement, approval process</t>
+          <t>approval process, stakeholder engagement, documentation review, sign‑off meeting, finalisation</t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -26238,7 +26210,7 @@
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>Sign‑off Acquisition</t>
+          <t>Sign‑off Coordination</t>
         </is>
       </c>
       <c r="V163" t="b">
@@ -26270,7 +26242,7 @@
       </c>
       <c r="AG163" t="inlineStr">
         <is>
-          <t>Secures final approval from designated stakeholders by coordinating, presenting, and confirming sign‑off requirements.</t>
+          <t>Secures final approval from designated personnel by organising, presenting, and confirming required documentation.</t>
         </is>
       </c>
       <c r="AH163" t="b">
@@ -26278,7 +26250,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>approval coordination, stakeholder confirmation, sign‑off documentation, final endorsement, approval process</t>
+          <t>approval process, stakeholder engagement, documentation review, sign‑off meeting, finalisation</t>
         </is>
       </c>
       <c r="AJ163" t="b">
@@ -26319,12 +26291,12 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation.</t>
+          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation, considering relevant legislation and policies.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>organisational processes, transaction types, blockchain suitability, legislative impact, policy compliance</t>
+          <t>process evaluation, transaction analysis, blockchain suitability, regulatory compliance, organisational policy</t>
         </is>
       </c>
       <c r="J164" t="n">
@@ -26425,7 +26397,7 @@
       </c>
       <c r="AG164" t="inlineStr">
         <is>
-          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation.</t>
+          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation, considering relevant legislation and policies.</t>
         </is>
       </c>
       <c r="AH164" t="b">
@@ -26433,7 +26405,7 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>organisational processes, transaction types, blockchain suitability, legislative impact, policy compliance</t>
+          <t>process evaluation, transaction analysis, blockchain suitability, regulatory compliance, organisational policy</t>
         </is>
       </c>
       <c r="AJ164" t="b">
@@ -26479,11 +26451,11 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>data log requirements, processing strategy, personnel consultation, requirement confirmation, collaborative discussion</t>
+          <t>data log requirements, processing strategy, personnel consultation, requirement confirmation, log discussion</t>
         </is>
       </c>
       <c r="J165" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
@@ -26545,7 +26517,7 @@
         <v>0</v>
       </c>
       <c r="W165" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="X165" t="inlineStr">
         <is>
@@ -26578,7 +26550,7 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>data log requirements, processing strategy, personnel consultation, requirement confirmation, collaborative discussion</t>
+          <t>data log requirements, processing strategy, personnel consultation, requirement confirmation, log discussion</t>
         </is>
       </c>
       <c r="AJ165" t="b">
@@ -26619,7 +26591,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Evaluates gathered threat data results to ensure reliability and consistency across sources and methods.</t>
+          <t>Evaluates threat data results to confirm reliability and consistency before further processing.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -26715,7 +26687,7 @@
       </c>
       <c r="AG166" t="inlineStr">
         <is>
-          <t>Evaluates gathered threat data results to ensure reliability and consistency across sources and methods.</t>
+          <t>Evaluates threat data results to confirm reliability and consistency before further processing.</t>
         </is>
       </c>
       <c r="AH166" t="b">
@@ -26925,7 +26897,7 @@
         </is>
       </c>
       <c r="J168" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -27001,7 +26973,7 @@
         <v>0</v>
       </c>
       <c r="W168" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="X168" t="inlineStr">
         <is>
@@ -27075,7 +27047,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Assist in gathering, processing, and preserving incident evidence in line with organisational requirements and standards.</t>
+          <t>Assist in gathering, processing and preserving incident evidence in line with organisational requirements and standards.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -27184,7 +27156,7 @@
       </c>
       <c r="AG169" t="inlineStr">
         <is>
-          <t>Assist in gathering, processing, and preserving incident evidence in line with organisational requirements and standards.</t>
+          <t>Assist in gathering, processing and preserving incident evidence in line with organisational requirements and standards.</t>
         </is>
       </c>
       <c r="AH169" t="b">
@@ -27233,12 +27205,12 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Identify essential business functions, critical data, and software, and assess risk impacts on ICT systems.</t>
+          <t>Identify essential business functions, critical data, and software, and assess ICT risk impacts on them.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>business critical functions, security environment, critical data, software assets, risk impact assessment</t>
+          <t>business critical functions, security environment, critical data, software assets, ICT risk assessment</t>
         </is>
       </c>
       <c r="J170" t="n">
@@ -27337,7 +27309,7 @@
       </c>
       <c r="AG170" t="inlineStr">
         <is>
-          <t>Identify essential business functions, critical data, and software, and assess risk impacts on ICT systems.</t>
+          <t>Identify essential business functions, critical data, and software, and assess ICT risk impacts on them.</t>
         </is>
       </c>
       <c r="AH170" t="b">
@@ -27345,7 +27317,7 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>business critical functions, security environment, critical data, software assets, risk impact assessment</t>
+          <t>business critical functions, security environment, critical data, software assets, ICT risk assessment</t>
         </is>
       </c>
       <c r="AJ170" t="b">

--- a/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v5.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v5.xlsx
@@ -1721,12 +1721,12 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>keep:0, "Idea Viability Evaluation":5, "Solution Viability Assessment":2</t>
+          <t>keep:0, "Idea Viability Evaluation":6, "Solution Viability Assessment":1</t>
         </is>
       </c>
       <c r="Z8" t="b">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>keep:2, "Solution Refinement":5</t>
+          <t>keep:1, "Solution Refinement":6</t>
         </is>
       </c>
       <c r="Z13" t="b">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>keep:1, "Discussion Facilitation":6</t>
+          <t>keep:3, "Discussion Facilitation":4</t>
         </is>
       </c>
       <c r="Z16" t="b">
@@ -3805,16 +3805,16 @@
         <v>1</v>
       </c>
       <c r="W21" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>keep:0, "Insight Presentation":7</t>
+          <t>keep:2, "Insight Presentation":5</t>
         </is>
       </c>
       <c r="Z21" t="b">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>keep:5, "Technology Platform Utilisation":2</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z29" t="b">
@@ -6003,7 +6003,7 @@
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>keep:4, "Device Configuration":3</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z36" t="b">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>Skill name uses 'Inventory Management' while evidence describes creating and maintaining a register, which is a distinct activity</t>
+          <t>domain term "inventory" (asset management) not found in unit text</t>
         </is>
       </c>
       <c r="AF38" t="b">
@@ -6642,12 +6642,12 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Password Creation":1</t>
         </is>
       </c>
       <c r="Z40" t="b">
@@ -6814,9 +6814,13 @@
         </is>
       </c>
       <c r="Z41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA41" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>Security Plan Communication</t>
+        </is>
+      </c>
       <c r="AB41" t="b">
         <v>0</v>
       </c>
@@ -6964,16 +6968,16 @@
         <v>1</v>
       </c>
       <c r="W42" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>keep:0, "Data Risk Categorisation":7</t>
+          <t>keep:2, "Data Risk Categorisation":5</t>
         </is>
       </c>
       <c r="Z42" t="b">
@@ -7131,22 +7135,18 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>keep:6, "Physical Security Plan Communication":1</t>
+          <t>keep:4, "Physical Security Plan Communication":3</t>
         </is>
       </c>
       <c r="Z43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>Physical Security Planning</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="b">
         <v>0</v>
       </c>
@@ -7298,7 +7298,7 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Security Trend Monitoring</t>
+          <t>Security Development Monitoring</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -7617,15 +7617,19 @@
         </is>
       </c>
       <c r="V46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W46" t="n">
-        <v>0.9524999999999999</v>
-      </c>
-      <c r="X46" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 6/7: </t>
+        </is>
+      </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>keep:4, "Security Development Monitoring":3</t>
+          <t>keep:1, "Security Development Monitoring":6</t>
         </is>
       </c>
       <c r="Z46" t="b">
@@ -7839,7 +7843,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Two-factor Authentication Enablement</t>
+          <t>Multi-factor Authentication Enablement</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -7946,16 +7950,16 @@
         <v>1</v>
       </c>
       <c r="W48" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>keep:4, "Multi-factor Authentication Enablement":3</t>
+          <t>keep:3, "Multi-factor Authentication Enablement":4</t>
         </is>
       </c>
       <c r="Z48" t="b">
@@ -8546,12 +8550,12 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>keep:0, "Evaluation Documentation":6, "Evaluation Documentation Preparation":1</t>
+          <t>keep:1, "Evaluation Documentation":4, "Evaluation Documentation Preparation":2</t>
         </is>
       </c>
       <c r="Z52" t="b">
@@ -8602,7 +8606,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Ict Gap Identification</t>
+          <t>ICT Gap Identification</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -8701,15 +8705,19 @@
         </is>
       </c>
       <c r="V53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W53" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X53" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 6/7: </t>
+        </is>
+      </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:1, "ICT Gap Identification":6</t>
         </is>
       </c>
       <c r="Z53" t="b">
@@ -9163,7 +9171,7 @@
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>keep:5, "Financial Impact Interpretation":2</t>
+          <t>keep:4, "Financial Impact Interpretation":3</t>
         </is>
       </c>
       <c r="Z56" t="b">
@@ -9321,9 +9329,13 @@
       </c>
       <c r="AC57" t="inlineStr"/>
       <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>Skill name 'Policy Compliance Assessment' does not match evidence which describes detailing standards, targets and implementation methods in an action plan</t>
+        </is>
+      </c>
       <c r="AF57" t="b">
         <v>0</v>
       </c>
@@ -9601,7 +9613,7 @@
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>keep:5, "Change Implementation Planning":1, "Implementation Difficulty Assessment":1</t>
+          <t>keep:4, "Implementation Difficulty Assessment/Change Difficulty Assessment":3</t>
         </is>
       </c>
       <c r="Z59" t="b">
@@ -9617,7 +9629,7 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>Skill name uses 'Planning' but evidence only involves evaluating difficulty, not planning</t>
+          <t>Skill name uses 'Planning' but evidence describes evaluating difficulty, not planning</t>
         </is>
       </c>
       <c r="AF59" t="b">
@@ -10361,16 +10373,16 @@
         <v>1</v>
       </c>
       <c r="W64" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>keep:0, "Legislative Text Analysis":7</t>
+          <t>keep:1, "Legislative Text Analysis":6</t>
         </is>
       </c>
       <c r="Z64" t="b">
@@ -10719,7 +10731,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Feedback Management</t>
+          <t>Feedback Handling</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -10809,19 +10821,15 @@
         </is>
       </c>
       <c r="V67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 4/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>keep:3, "Feedback Management":4</t>
+          <t>keep:4, "Feedback Management":3</t>
         </is>
       </c>
       <c r="Z67" t="b">
@@ -12165,12 +12173,12 @@
         <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>keep:6, "Digital Information Security":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z76" t="b">
@@ -12314,16 +12322,16 @@
         <v>1</v>
       </c>
       <c r="W77" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>keep:1, "Policy Distribution":6</t>
+          <t>keep:0, "Policy Distribution":7</t>
         </is>
       </c>
       <c r="Z77" t="b">
@@ -12787,12 +12795,12 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>keep:0, "Blockchain Anomaly Resolution":4, "Blockchain Anomaly Problem Solving/Blockchain Anomaly Solving":3</t>
+          <t>keep:0, "Blockchain Anomaly Resolution":6, "Blockchain Anomaly Problem Solving":1</t>
         </is>
       </c>
       <c r="Z80" t="b">
@@ -12804,7 +12812,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Foundation Skill describes problem‑solving capability already embedded in other skills and PCs; it is a work style rather than a distinct task</t>
+          <t>Foundation Skill describes problem‑solving capability already embedded in other skills and PCs; not a distinct standalone activity</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -13883,16 +13891,16 @@
         <v>1</v>
       </c>
       <c r="W87" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>keep:0, "Maintenance Testing":7</t>
+          <t>keep:1, "Maintenance Testing":6</t>
         </is>
       </c>
       <c r="Z87" t="b">
@@ -15475,12 +15483,12 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>keep:2, "Dataset Creation":5</t>
+          <t>keep:1, "Dataset Creation":6</t>
         </is>
       </c>
       <c r="Z97" t="b">
@@ -16780,13 +16788,9 @@
         </is>
       </c>
       <c r="Z105" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA105" t="inlineStr">
-        <is>
-          <t>Dataset Creation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA105" t="inlineStr"/>
       <c r="AB105" t="b">
         <v>0</v>
       </c>
@@ -16928,12 +16932,12 @@
         <v>0</v>
       </c>
       <c r="W106" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>keep:6, "Anomaly Detection":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z106" t="b">
@@ -18016,7 +18020,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>FS describes work style (planning and coordination) already embedded in PCs and other skills</t>
+          <t>FS describes work style (planning and coordination) rather than a distinct task; capability already embedded in strategy development PCs</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -18777,7 +18781,7 @@
       <c r="X118" t="inlineStr"/>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>keep:5, "Risk Evaluation":1, "Protection Risk Assessment":1</t>
+          <t>keep:5, "Risk Evaluation":2</t>
         </is>
       </c>
       <c r="Z118" t="b">
@@ -19405,7 +19409,7 @@
       <c r="X122" t="inlineStr"/>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:5, "Feedback Documentation Management/Feedback Submission Management":2</t>
         </is>
       </c>
       <c r="Z122" t="b">
@@ -19611,7 +19615,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Problem Solving in Security</t>
+          <t>Contextual Anomaly Identification</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -19718,16 +19722,16 @@
         <v>1</v>
       </c>
       <c r="W124" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>keep:0, "Security Contextual Problem Solving":3, "Contextual Anomaly Identification":3, "Contextual Anomaly Detection":1</t>
+          <t>keep:0, "Contextual Anomaly Identification/Security Anomaly Identification":5, "Security Contextual Problem Solving":2</t>
         </is>
       </c>
       <c r="Z124" t="b">
@@ -19735,13 +19739,9 @@
       </c>
       <c r="AA124" t="inlineStr"/>
       <c r="AB124" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Foundation Skill describes a work style (recognising anomalies) that is already embedded in other skills and PCs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC124" t="inlineStr"/>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Security Requirements Documentation</t>
+          <t>Security Findings Documentation</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -19885,16 +19885,16 @@
         <v>1</v>
       </c>
       <c r="W125" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>keep:1, "Security Requirements Documentation":6</t>
+          <t>keep:0, "Security Findings Documentation/Security Requirements Documentation":7</t>
         </is>
       </c>
       <c r="Z125" t="b">
@@ -21177,16 +21177,16 @@
         <v>1</v>
       </c>
       <c r="W133" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>keep:2, "Technical Documentation Reading":5</t>
+          <t>keep:0, "Technical Documentation Reading":7</t>
         </is>
       </c>
       <c r="Z133" t="b">
@@ -21374,7 +21374,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>FS describes work style (autonomous decision making) not a distinct task; capability already implicit in PCs</t>
+          <t>FS describes work style not skill, implicit in PCs</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -22565,12 +22565,12 @@
         <v>0</v>
       </c>
       <c r="W141" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X141" t="inlineStr"/>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Communication Effectiveness Assessment":1</t>
         </is>
       </c>
       <c r="Z141" t="b">
@@ -23290,7 +23290,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>FS capability is embedded in other skills such as Risk Analysis and Incident Response Plan Evaluation, not a distinct standalone skill</t>
+          <t>FS capability is embedded in other skills such as Risk Analysis and Security Incident Handling, not a distinct standalone skill</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -23624,7 +23624,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Foundation Skill describes work style (ensuring compliance) already implicit in other skills and not a distinct task for this unit</t>
+          <t>FS describes work style and compliance strategy, which is implicit in other skills and not a distinct task for this unit</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -25176,7 +25176,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Strategic Planning</t>
+          <t>Priority Planning</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -25282,15 +25282,19 @@
         </is>
       </c>
       <c r="V157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W157" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X157" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 4/7: </t>
+        </is>
+      </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>keep:5, "Strategy Prioritisation":2</t>
+          <t>keep:1, "Priority Planning":4, "Strategy Prioritisation":2</t>
         </is>
       </c>
       <c r="Z157" t="b">
@@ -25298,9 +25302,13 @@
       </c>
       <c r="AA157" t="inlineStr"/>
       <c r="AB157" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC157" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Foundation Skill describes work style (strategic planning) already embedded in PCs and other skills</t>
+        </is>
+      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
@@ -25863,7 +25871,7 @@
         </is>
       </c>
       <c r="J161" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -25925,7 +25933,7 @@
         <v>0</v>
       </c>
       <c r="W161" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="X161" t="inlineStr">
         <is>
@@ -25989,7 +25997,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>APPLY</t>
+          <t>ASSIST</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -25999,7 +26007,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Identify and confirm the types of information stored on each registered digital device within the organisation.</t>
+          <t>Assists in confirming and documenting the types of information stored on each registered digital device.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -26008,7 +26016,7 @@
         </is>
       </c>
       <c r="J162" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
@@ -26070,7 +26078,7 @@
         <v>0</v>
       </c>
       <c r="W162" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="X162" t="inlineStr">
         <is>
@@ -26095,7 +26103,7 @@
       </c>
       <c r="AG162" t="inlineStr">
         <is>
-          <t>Identify and confirm the types of information stored on each registered digital device within the organisation.</t>
+          <t>Assists in confirming and documenting the types of information stored on each registered digital device.</t>
         </is>
       </c>
       <c r="AH162" t="b">
@@ -26144,12 +26152,12 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Secures final approval from designated personnel by organising, presenting, and confirming required documentation.</t>
+          <t>Secures final approval from designated personnel by managing sign‑off processes and confirming compliance.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>approval process, stakeholder engagement, documentation review, sign‑off meeting, finalisation</t>
+          <t>approval management, stakeholder engagement, compliance confirmation, sign‑off process, finalisation</t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -26242,7 +26250,7 @@
       </c>
       <c r="AG163" t="inlineStr">
         <is>
-          <t>Secures final approval from designated personnel by organising, presenting, and confirming required documentation.</t>
+          <t>Secures final approval from designated personnel by managing sign‑off processes and confirming compliance.</t>
         </is>
       </c>
       <c r="AH163" t="b">
@@ -26250,7 +26258,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>approval process, stakeholder engagement, documentation review, sign‑off meeting, finalisation</t>
+          <t>approval management, stakeholder engagement, compliance confirmation, sign‑off process, finalisation</t>
         </is>
       </c>
       <c r="AJ163" t="b">
@@ -26291,16 +26299,16 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation, considering relevant legislation and policies.</t>
+          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>process evaluation, transaction analysis, blockchain suitability, regulatory compliance, organisational policy</t>
+          <t>process evaluation, transaction analysis, blockchain suitability, organisational assessment, compliance impact</t>
         </is>
       </c>
       <c r="J164" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
@@ -26372,7 +26380,7 @@
         <v>0</v>
       </c>
       <c r="W164" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="X164" t="inlineStr">
         <is>
@@ -26397,7 +26405,7 @@
       </c>
       <c r="AG164" t="inlineStr">
         <is>
-          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation, considering relevant legislation and policies.</t>
+          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation.</t>
         </is>
       </c>
       <c r="AH164" t="b">
@@ -26405,7 +26413,7 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>process evaluation, transaction analysis, blockchain suitability, regulatory compliance, organisational policy</t>
+          <t>process evaluation, transaction analysis, blockchain suitability, organisational assessment, compliance impact</t>
         </is>
       </c>
       <c r="AJ164" t="b">
@@ -26451,7 +26459,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>data log requirements, processing strategy, personnel consultation, requirement confirmation, log discussion</t>
+          <t>data log requirements, processing strategy, personnel consultation, requirement confirmation, collaborative discussion</t>
         </is>
       </c>
       <c r="J165" t="n">
@@ -26550,7 +26558,7 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>data log requirements, processing strategy, personnel consultation, requirement confirmation, log discussion</t>
+          <t>data log requirements, processing strategy, personnel consultation, requirement confirmation, collaborative discussion</t>
         </is>
       </c>
       <c r="AJ165" t="b">
@@ -26868,7 +26876,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Incident Plan Alignment</t>
+          <t>Plan Alignment Documentation</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -26888,16 +26896,16 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>The worker assesses the current incident response plan, documents its conformity with requirements, and submits it for feedback.</t>
+          <t>The worker aligns the current incident response plan with requirements and records the findings for review.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>incident response plan, alignment assessment, documentation, requirements compliance, feedback submission</t>
+          <t>incident response plan, alignment, documentation, requirements, feedback</t>
         </is>
       </c>
       <c r="J168" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -26966,14 +26974,14 @@
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>Incident Plan Alignment</t>
+          <t>Plan Alignment Documentation</t>
         </is>
       </c>
       <c r="V168" t="b">
         <v>0</v>
       </c>
       <c r="W168" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="X168" t="inlineStr">
         <is>
@@ -26998,7 +27006,7 @@
       </c>
       <c r="AG168" t="inlineStr">
         <is>
-          <t>The worker assesses the current incident response plan, documents its conformity with requirements, and submits it for feedback.</t>
+          <t>The worker aligns the current incident response plan with requirements and records the findings for review.</t>
         </is>
       </c>
       <c r="AH168" t="b">
@@ -27006,7 +27014,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>incident response plan, alignment assessment, documentation, requirements compliance, feedback submission</t>
+          <t>incident response plan, alignment, documentation, requirements, feedback</t>
         </is>
       </c>
       <c r="AJ168" t="b">
@@ -27047,12 +27055,12 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Assist in gathering, processing and preserving incident evidence in line with organisational requirements and standards.</t>
+          <t>Assist in gathering, processing, and preserving evidence in line with specified incident response requirements.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>evidence collection, evidence processing, evidence preservation, incident response, organisational requirements</t>
+          <t>evidence collection, evidence processing, evidence preservation, incident response, assistance</t>
         </is>
       </c>
       <c r="J169" t="n">
@@ -27156,7 +27164,7 @@
       </c>
       <c r="AG169" t="inlineStr">
         <is>
-          <t>Assist in gathering, processing and preserving incident evidence in line with organisational requirements and standards.</t>
+          <t>Assist in gathering, processing, and preserving evidence in line with specified incident response requirements.</t>
         </is>
       </c>
       <c r="AH169" t="b">
@@ -27164,7 +27172,7 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>evidence collection, evidence processing, evidence preservation, incident response, organisational requirements</t>
+          <t>evidence collection, evidence processing, evidence preservation, incident response, assistance</t>
         </is>
       </c>
       <c r="AJ169" t="b">
@@ -27205,16 +27213,16 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Identify essential business functions, critical data, and software, and assess ICT risk impacts on them.</t>
+          <t>Identifies essential business functions, critical data, and software, and evaluates ICT risk impacts on them.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>business critical functions, security environment, critical data, software assets, ICT risk assessment</t>
+          <t>business critical functions, security environment, critical data, software assets, ICT risk impact</t>
         </is>
       </c>
       <c r="J170" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -27284,7 +27292,7 @@
         <v>0</v>
       </c>
       <c r="W170" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="X170" t="inlineStr">
         <is>
@@ -27309,7 +27317,7 @@
       </c>
       <c r="AG170" t="inlineStr">
         <is>
-          <t>Identify essential business functions, critical data, and software, and assess ICT risk impacts on them.</t>
+          <t>Identifies essential business functions, critical data, and software, and evaluates ICT risk impacts on them.</t>
         </is>
       </c>
       <c r="AH170" t="b">
@@ -27317,7 +27325,7 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>business critical functions, security environment, critical data, software assets, ICT risk assessment</t>
+          <t>business critical functions, security environment, critical data, software assets, ICT risk impact</t>
         </is>
       </c>
       <c r="AJ170" t="b">

--- a/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v5.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v5.xlsx
@@ -1717,16 +1717,16 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>keep:0, "Idea Viability Evaluation":6, "Solution Viability Assessment":1</t>
+          <t>keep:0, "Idea Viability Evaluation":7</t>
         </is>
       </c>
       <c r="Z8" t="b">
@@ -2202,16 +2202,16 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>keep:0, "Solution Research":7</t>
+          <t>keep:1, "Solution Research":5, "Information Research":1</t>
         </is>
       </c>
       <c r="Z11" t="b">
@@ -2365,16 +2365,16 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t>postprocess: spelling/redundancy</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>keep:3, "Solution Presentation":4</t>
+          <t>keep:5, "Solution Presentation":2</t>
         </is>
       </c>
       <c r="Z12" t="b">
@@ -2532,16 +2532,16 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t>postprocess: spelling/redundancy</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>keep:1, "Solution Refinement":6</t>
+          <t>keep:4, "Solution Refinement":3</t>
         </is>
       </c>
       <c r="Z13" t="b">
@@ -3514,9 +3514,13 @@
       </c>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>Skill name uses 'Assessment' but evidence action is 'Establish', not a synonym</t>
+        </is>
+      </c>
       <c r="AF19" t="b">
         <v>0</v>
       </c>
@@ -3805,16 +3809,16 @@
         <v>1</v>
       </c>
       <c r="W21" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>keep:2, "Insight Presentation":5</t>
+          <t>keep:0, "Insight Presentation":7</t>
         </is>
       </c>
       <c r="Z21" t="b">
@@ -4921,7 +4925,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr">
@@ -5081,7 +5085,7 @@
         <v>1</v>
       </c>
       <c r="W29" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -6341,7 +6345,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>domain term "inventory" (asset management) not found in unit text</t>
+          <t>Skill name uses 'Inventory Management' while evidence describes creating and maintaining a register; 'inventory' is not mentioned and implies a different activity</t>
         </is>
       </c>
       <c r="AF38" t="b">
@@ -6814,13 +6818,9 @@
         </is>
       </c>
       <c r="Z41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>Security Plan Communication</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA41" t="inlineStr"/>
       <c r="AB41" t="b">
         <v>0</v>
       </c>
@@ -6972,18 +6972,22 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>keep:2, "Data Risk Categorisation":5</t>
+          <t>keep:1, "Data Risk Categorisation":6</t>
         </is>
       </c>
       <c r="Z42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA42" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>Security Protocol Selection</t>
+        </is>
+      </c>
       <c r="AB42" t="b">
         <v>0</v>
       </c>
@@ -7028,7 +7032,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Security Plan Communication</t>
+          <t>Physical Security Plan Communication</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -7132,21 +7136,29 @@
         </is>
       </c>
       <c r="V43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W43" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X43" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/7: </t>
+        </is>
+      </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>keep:4, "Physical Security Plan Communication":3</t>
+          <t>keep:2, "Physical Security Plan Communication/Physical Security Communication":5</t>
         </is>
       </c>
       <c r="Z43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>Physical Security Planning</t>
+        </is>
+      </c>
       <c r="AB43" t="b">
         <v>0</v>
       </c>
@@ -7298,7 +7310,7 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr">
@@ -7517,7 +7529,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Security Development Monitoring</t>
+          <t>Security Trend Monitoring</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -7617,19 +7629,15 @@
         </is>
       </c>
       <c r="V46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 6/7: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>keep:1, "Security Development Monitoring":6</t>
+          <t>keep:6, "Security Development Monitoring":1</t>
         </is>
       </c>
       <c r="Z46" t="b">
@@ -7843,7 +7851,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Multi-factor Authentication Enablement</t>
+          <t>Two-factor Authentication Enablement</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -7950,16 +7958,16 @@
         <v>1</v>
       </c>
       <c r="W48" t="n">
-        <v>0.9</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t>postprocess: spelling/redundancy</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>keep:3, "Multi-factor Authentication Enablement":4</t>
+          <t>keep:6, "Multi-factor Authentication Enablement":1</t>
         </is>
       </c>
       <c r="Z48" t="b">
@@ -8546,22 +8554,26 @@
         <v>1</v>
       </c>
       <c r="W52" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>keep:1, "Evaluation Documentation":4, "Evaluation Documentation Preparation":2</t>
+          <t>keep:0, "Evaluation Documentation":7</t>
         </is>
       </c>
       <c r="Z52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA52" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>Strategic Plan Analysis</t>
+        </is>
+      </c>
       <c r="AB52" t="b">
         <v>0</v>
       </c>
@@ -8708,16 +8720,16 @@
         <v>1</v>
       </c>
       <c r="W53" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>keep:1, "ICT Gap Identification":6</t>
+          <t>keep:0, "ICT Gap Identification":7</t>
         </is>
       </c>
       <c r="Z53" t="b">
@@ -9329,13 +9341,9 @@
       </c>
       <c r="AC57" t="inlineStr"/>
       <c r="AD57" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE57" t="inlineStr">
-        <is>
-          <t>Skill name 'Policy Compliance Assessment' does not match evidence which describes detailing standards, targets and implementation methods in an action plan</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="b">
         <v>0</v>
       </c>
@@ -9613,7 +9621,7 @@
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>keep:4, "Implementation Difficulty Assessment/Change Difficulty Assessment":3</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z59" t="b">
@@ -10373,16 +10381,16 @@
         <v>1</v>
       </c>
       <c r="W64" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>keep:1, "Legislative Text Analysis":6</t>
+          <t>keep:0, "Legislative Text Analysis":7</t>
         </is>
       </c>
       <c r="Z64" t="b">
@@ -10824,12 +10832,12 @@
         <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>keep:4, "Feedback Management":3</t>
+          <t>keep:6, "Feedback Management":1</t>
         </is>
       </c>
       <c r="Z67" t="b">
@@ -12812,7 +12820,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Foundation Skill describes problem‑solving capability already embedded in other skills and PCs; not a distinct standalone activity</t>
+          <t>Foundation Skill describes problem‑solving capability that is already embedded in other blockchain solution skills and PCs</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -13735,12 +13743,12 @@
         <v>0</v>
       </c>
       <c r="W86" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Maintenance Schedule Development":1</t>
         </is>
       </c>
       <c r="Z86" t="b">
@@ -13752,9 +13760,13 @@
       </c>
       <c r="AC86" t="inlineStr"/>
       <c r="AD86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE86" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
       <c r="AF86" t="b">
         <v>0</v>
       </c>
@@ -13791,7 +13803,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Maintenance Testing</t>
+          <t>Maintenance Testing Execution</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -13888,19 +13900,15 @@
         </is>
       </c>
       <c r="V87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W87" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 6/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X87" t="inlineStr"/>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>keep:1, "Maintenance Testing":6</t>
+          <t>keep:4, "Maintenance Testing":3</t>
         </is>
       </c>
       <c r="Z87" t="b">
@@ -14068,9 +14076,13 @@
       </c>
       <c r="AC88" t="inlineStr"/>
       <c r="AD88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE88" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>Skill name uses 'Selection' which is not a synonym of the evidence verb 'Determine' and does not appear in the PCs or elements</t>
+        </is>
+      </c>
       <c r="AF88" t="b">
         <v>0</v>
       </c>
@@ -15483,12 +15495,12 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>keep:1, "Dataset Creation":6</t>
+          <t>keep:3, "Dataset Creation":4</t>
         </is>
       </c>
       <c r="Z97" t="b">
@@ -16513,7 +16525,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Threat Findings Communication</t>
+          <t>Stakeholder Findings Communication</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -16613,19 +16625,15 @@
         </is>
       </c>
       <c r="V104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W104" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 4/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X104" t="inlineStr"/>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>keep:3, "Threat Findings Communication":4</t>
+          <t>keep:5, "Threat Findings Communication":2</t>
         </is>
       </c>
       <c r="Z104" t="b">
@@ -16788,9 +16796,13 @@
         </is>
       </c>
       <c r="Z105" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA105" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>Dataset Creation</t>
+        </is>
+      </c>
       <c r="AB105" t="b">
         <v>0</v>
       </c>
@@ -16932,12 +16944,12 @@
         <v>0</v>
       </c>
       <c r="W106" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Anomaly Detection":1</t>
         </is>
       </c>
       <c r="Z106" t="b">
@@ -18003,12 +18015,12 @@
         <v>0</v>
       </c>
       <c r="W113" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X113" t="inlineStr"/>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>keep:5, "Protection Strategy Coordination":2</t>
+          <t>keep:6, "Protection Strategy Coordination":1</t>
         </is>
       </c>
       <c r="Z113" t="b">
@@ -18020,7 +18032,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>FS describes work style (planning and coordination) rather than a distinct task; capability already embedded in strategy development PCs</t>
+          <t>FS describes work style (planning and coordination) rather than a distinct task; capability already embedded in PCs and other skills</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -18160,7 +18172,7 @@
         <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>0.9428571428571428</v>
+        <v>0.95</v>
       </c>
       <c r="X114" t="inlineStr"/>
       <c r="Y114" t="inlineStr">
@@ -18781,7 +18793,7 @@
       <c r="X118" t="inlineStr"/>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>keep:5, "Risk Evaluation":2</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z118" t="b">
@@ -19245,12 +19257,12 @@
         <v>0</v>
       </c>
       <c r="W121" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X121" t="inlineStr"/>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Data Type Identification":1</t>
         </is>
       </c>
       <c r="Z121" t="b">
@@ -19409,7 +19421,7 @@
       <c r="X122" t="inlineStr"/>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>keep:5, "Feedback Documentation Management/Feedback Submission Management":2</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z122" t="b">
@@ -19726,12 +19738,12 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>keep:0, "Contextual Anomaly Identification/Security Anomaly Identification":5, "Security Contextual Problem Solving":2</t>
+          <t>keep:0, "Contextual Anomaly Identification":6, "Contextual Anomaly Detection":1</t>
         </is>
       </c>
       <c r="Z124" t="b">
@@ -19782,7 +19794,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Security Findings Documentation</t>
+          <t>Security Requirements Documentation</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -19894,7 +19906,7 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>keep:0, "Security Findings Documentation/Security Requirements Documentation":7</t>
+          <t>keep:0, "Security Requirements Documentation":7</t>
         </is>
       </c>
       <c r="Z125" t="b">
@@ -21177,16 +21189,16 @@
         <v>1</v>
       </c>
       <c r="W133" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>keep:0, "Technical Documentation Reading":7</t>
+          <t>keep:1, "Technical Documentation Reading":6</t>
         </is>
       </c>
       <c r="Z133" t="b">
@@ -21374,7 +21386,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>FS describes work style not skill, implicit in PCs</t>
+          <t>FS describes work style (autonomous decision making) not a distinct task; capability already implicit in PCs</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -21718,9 +21730,13 @@
       </c>
       <c r="AC136" t="inlineStr"/>
       <c r="AD136" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE136" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>Skill name uses 'Preparation' which does not appear in evidence; evidence describes 'Document' activity</t>
+        </is>
+      </c>
       <c r="AF136" t="b">
         <v>0</v>
       </c>
@@ -21873,16 +21889,16 @@
         <v>1</v>
       </c>
       <c r="W137" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>keep:0, "Incident Response Plan Evaluation":7</t>
+          <t>keep:3, "Incident Response Plan Evaluation":4</t>
         </is>
       </c>
       <c r="Z137" t="b">
@@ -22565,12 +22581,12 @@
         <v>0</v>
       </c>
       <c r="W141" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X141" t="inlineStr"/>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>keep:6, "Communication Effectiveness Assessment":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z141" t="b">
@@ -23290,7 +23306,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>FS capability is embedded in other skills such as Risk Analysis and Security Incident Handling, not a distinct standalone skill</t>
+          <t>FS capability is embedded in other skills such as Risk Analysis and Incident Response Plan Evaluation, not a distinct standalone skill</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -23624,7 +23640,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>FS describes work style and compliance strategy, which is implicit in other skills and not a distinct task for this unit</t>
+          <t>FS describes work style (ensuring compliance) rather than a distinct task; capability is implicit in other skills like Risk Analysis and Business Continuity Evaluation</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -25176,7 +25192,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Priority Planning</t>
+          <t>Strategic Planning</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -25282,19 +25298,15 @@
         </is>
       </c>
       <c r="V157" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W157" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 4/7: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="X157" t="inlineStr"/>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>keep:1, "Priority Planning":4, "Strategy Prioritisation":2</t>
+          <t>keep:6, "Strategy Prioritisation":1</t>
         </is>
       </c>
       <c r="Z157" t="b">
@@ -25306,7 +25318,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Foundation Skill describes work style (strategic planning) already embedded in PCs and other skills</t>
+          <t>Foundation Skill describes a work style (strategic planning) that is already embedded in other skills and PCs</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -25862,12 +25874,12 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting each response with relevant data or rationale.</t>
+          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting decisions with relevant data and reasoning.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>evidence based answers, stakeholder queries, substantiated responses, data support, rationale provision</t>
+          <t>evidence based answers, stakeholder queries, substantiated responses, data support, reasoning justification</t>
         </is>
       </c>
       <c r="J161" t="n">
@@ -25958,7 +25970,7 @@
       </c>
       <c r="AG161" t="inlineStr">
         <is>
-          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting each response with relevant data or rationale.</t>
+          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting decisions with relevant data and reasoning.</t>
         </is>
       </c>
       <c r="AH161" t="b">
@@ -25966,7 +25978,7 @@
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>evidence based answers, stakeholder queries, substantiated responses, data support, rationale provision</t>
+          <t>evidence based answers, stakeholder queries, substantiated responses, data support, reasoning justification</t>
         </is>
       </c>
       <c r="AJ161" t="b">
@@ -26012,7 +26024,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>device data inventory, information classification, data mapping, asset documentation, storage verification</t>
+          <t>device data inventory, information classification, data mapping, asset documentation, digital records</t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -26111,7 +26123,7 @@
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>device data inventory, information classification, data mapping, asset documentation, storage verification</t>
+          <t>device data inventory, information classification, data mapping, asset documentation, digital records</t>
         </is>
       </c>
       <c r="AJ162" t="b">
@@ -26132,7 +26144,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Sign‑off Coordination</t>
+          <t>Sign‑off Acquisition</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -26152,12 +26164,12 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Secures final approval from designated personnel by managing sign‑off processes and confirming compliance.</t>
+          <t>Secures final approval from designated stakeholders by coordinating, presenting, and confirming sign‑off requirements.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>approval management, stakeholder engagement, compliance confirmation, sign‑off process, finalisation</t>
+          <t>approval coordination, stakeholder confirmation, final sign‑off, approval documentation, sign‑off process</t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -26218,7 +26230,7 @@
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>Sign‑off Coordination</t>
+          <t>Sign‑off Acquisition</t>
         </is>
       </c>
       <c r="V163" t="b">
@@ -26250,7 +26262,7 @@
       </c>
       <c r="AG163" t="inlineStr">
         <is>
-          <t>Secures final approval from designated personnel by managing sign‑off processes and confirming compliance.</t>
+          <t>Secures final approval from designated stakeholders by coordinating, presenting, and confirming sign‑off requirements.</t>
         </is>
       </c>
       <c r="AH163" t="b">
@@ -26258,7 +26270,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>approval management, stakeholder engagement, compliance confirmation, sign‑off process, finalisation</t>
+          <t>approval coordination, stakeholder confirmation, final sign‑off, approval documentation, sign‑off process</t>
         </is>
       </c>
       <c r="AJ163" t="b">
@@ -26299,16 +26311,16 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation.</t>
+          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation, considering relevant legislation and policies.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>process evaluation, transaction analysis, blockchain suitability, organisational assessment, compliance impact</t>
+          <t>process analysis, transaction evaluation, blockchain suitability, regulatory compliance, organisational policy</t>
         </is>
       </c>
       <c r="J164" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
@@ -26380,7 +26392,7 @@
         <v>0</v>
       </c>
       <c r="W164" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="X164" t="inlineStr">
         <is>
@@ -26405,7 +26417,7 @@
       </c>
       <c r="AG164" t="inlineStr">
         <is>
-          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation.</t>
+          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation, considering relevant legislation and policies.</t>
         </is>
       </c>
       <c r="AH164" t="b">
@@ -26413,7 +26425,7 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>process evaluation, transaction analysis, blockchain suitability, organisational assessment, compliance impact</t>
+          <t>process analysis, transaction evaluation, blockchain suitability, regulatory compliance, organisational policy</t>
         </is>
       </c>
       <c r="AJ164" t="b">
@@ -26454,12 +26466,12 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Facilitates discussion with relevant personnel to confirm data log requirements and processing strategy.</t>
+          <t>Collaborates with relevant personnel to discuss and confirm data log requirements and processing strategy.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>data log requirements, processing strategy, personnel consultation, requirement confirmation, collaborative discussion</t>
+          <t>data log requirements, processing strategy, personnel consultation, requirement discussion, log planning</t>
         </is>
       </c>
       <c r="J165" t="n">
@@ -26550,7 +26562,7 @@
       </c>
       <c r="AG165" t="inlineStr">
         <is>
-          <t>Facilitates discussion with relevant personnel to confirm data log requirements and processing strategy.</t>
+          <t>Collaborates with relevant personnel to discuss and confirm data log requirements and processing strategy.</t>
         </is>
       </c>
       <c r="AH165" t="b">
@@ -26558,7 +26570,7 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>data log requirements, processing strategy, personnel consultation, requirement confirmation, collaborative discussion</t>
+          <t>data log requirements, processing strategy, personnel consultation, requirement discussion, log planning</t>
         </is>
       </c>
       <c r="AJ165" t="b">
@@ -26599,7 +26611,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Evaluates threat data results to confirm reliability and consistency before further processing.</t>
+          <t>Evaluates gathered threat data results to ensure reliability and consistency across sources and methods.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -26695,7 +26707,7 @@
       </c>
       <c r="AG166" t="inlineStr">
         <is>
-          <t>Evaluates threat data results to confirm reliability and consistency before further processing.</t>
+          <t>Evaluates gathered threat data results to ensure reliability and consistency across sources and methods.</t>
         </is>
       </c>
       <c r="AH166" t="b">
@@ -26749,7 +26761,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>protection plan assessment, organisational alignment, effectiveness analysis, legislative compliance, critical asset identification</t>
+          <t>effectiveness assessment, alignment verification, organisational requirements, legislative compliance, protection plan</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -26855,7 +26867,7 @@
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>protection plan assessment, organisational alignment, effectiveness analysis, legislative compliance, critical asset identification</t>
+          <t>effectiveness assessment, alignment verification, organisational requirements, legislative compliance, protection plan</t>
         </is>
       </c>
       <c r="AJ167" t="b">
@@ -26876,7 +26888,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Plan Alignment Documentation</t>
+          <t>Incident Plan Alignment</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -26896,12 +26908,12 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>The worker aligns the current incident response plan with requirements and records the findings for review.</t>
+          <t>The worker assesses the current incident response plan, documents its conformity with requirements, and submits it for feedback.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>incident response plan, alignment, documentation, requirements, feedback</t>
+          <t>incident response plan, alignment assessment, documentation, requirements compliance, feedback submission</t>
         </is>
       </c>
       <c r="J168" t="n">
@@ -26974,7 +26986,7 @@
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>Plan Alignment Documentation</t>
+          <t>Incident Plan Alignment</t>
         </is>
       </c>
       <c r="V168" t="b">
@@ -27006,7 +27018,7 @@
       </c>
       <c r="AG168" t="inlineStr">
         <is>
-          <t>The worker aligns the current incident response plan with requirements and records the findings for review.</t>
+          <t>The worker assesses the current incident response plan, documents its conformity with requirements, and submits it for feedback.</t>
         </is>
       </c>
       <c r="AH168" t="b">
@@ -27014,7 +27026,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>incident response plan, alignment, documentation, requirements, feedback</t>
+          <t>incident response plan, alignment assessment, documentation, requirements compliance, feedback submission</t>
         </is>
       </c>
       <c r="AJ168" t="b">
@@ -27055,12 +27067,12 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Assist in gathering, processing, and preserving evidence in line with specified incident response requirements.</t>
+          <t>Assist in gathering, processing, and preserving evidence in line with organisational and legal requirements.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>evidence collection, evidence processing, evidence preservation, incident response, assistance</t>
+          <t>evidence collection, evidence processing, evidence preservation, incident response, legal compliance</t>
         </is>
       </c>
       <c r="J169" t="n">
@@ -27164,7 +27176,7 @@
       </c>
       <c r="AG169" t="inlineStr">
         <is>
-          <t>Assist in gathering, processing, and preserving evidence in line with specified incident response requirements.</t>
+          <t>Assist in gathering, processing, and preserving evidence in line with organisational and legal requirements.</t>
         </is>
       </c>
       <c r="AH169" t="b">
@@ -27172,7 +27184,7 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>evidence collection, evidence processing, evidence preservation, incident response, assistance</t>
+          <t>evidence collection, evidence processing, evidence preservation, incident response, legal compliance</t>
         </is>
       </c>
       <c r="AJ169" t="b">
@@ -27213,12 +27225,12 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Identifies essential business functions, critical data, and software, and evaluates ICT risk impacts on them.</t>
+          <t>Identify essential business functions, critical data, and software, and assess ICT risk impacts on them.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>business critical functions, security environment, critical data, software assets, ICT risk impact</t>
+          <t>business critical functions, security environment, critical data, software assets, ICT risk assessment</t>
         </is>
       </c>
       <c r="J170" t="n">
@@ -27317,7 +27329,7 @@
       </c>
       <c r="AG170" t="inlineStr">
         <is>
-          <t>Identifies essential business functions, critical data, and software, and evaluates ICT risk impacts on them.</t>
+          <t>Identify essential business functions, critical data, and software, and assess ICT risk impacts on them.</t>
         </is>
       </c>
       <c r="AH170" t="b">
@@ -27325,7 +27337,7 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>business critical functions, security environment, critical data, software assets, ICT risk impact</t>
+          <t>business critical functions, security environment, critical data, software assets, ICT risk assessment</t>
         </is>
       </c>
       <c r="AJ170" t="b">

--- a/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v5.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v5.xlsx
@@ -1717,16 +1717,16 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>keep:0, "Idea Viability Evaluation":7</t>
+          <t>keep:0, "Idea Viability Evaluation":6, "Solution Viability Assessment":1</t>
         </is>
       </c>
       <c r="Z8" t="b">
@@ -2206,12 +2206,12 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>keep:1, "Solution Research":5, "Information Research":1</t>
+          <t>keep:0, "Solution Research":4, "Information Research":3</t>
         </is>
       </c>
       <c r="Z11" t="b">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>keep:5, "Solution Presentation":2</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z12" t="b">
@@ -2532,16 +2532,16 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>keep:4, "Solution Refinement":3</t>
+          <t>keep:3, "Solution Refinement":4</t>
         </is>
       </c>
       <c r="Z13" t="b">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>keep:3, "Discussion Facilitation":4</t>
+          <t>keep:2, "Discussion Facilitation":5</t>
         </is>
       </c>
       <c r="Z16" t="b">
@@ -3514,13 +3514,9 @@
       </c>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>Skill name uses 'Assessment' but evidence action is 'Establish', not a synonym</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="b">
         <v>0</v>
       </c>
@@ -4925,7 +4921,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr">
@@ -5085,7 +5081,7 @@
         <v>1</v>
       </c>
       <c r="W29" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -6007,7 +6003,7 @@
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:4, "Device Configuration":3</t>
         </is>
       </c>
       <c r="Z36" t="b">
@@ -6345,7 +6341,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>Skill name uses 'Inventory Management' while evidence describes creating and maintaining a register; 'inventory' is not mentioned and implies a different activity</t>
+          <t>domain term "inventory" (asset management) not found in unit text</t>
         </is>
       </c>
       <c r="AF38" t="b">
@@ -6646,12 +6642,12 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>keep:6, "Password Creation":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z40" t="b">
@@ -6818,9 +6814,13 @@
         </is>
       </c>
       <c r="Z41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA41" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>Security Plan Communication</t>
+        </is>
+      </c>
       <c r="AB41" t="b">
         <v>0</v>
       </c>
@@ -6968,26 +6968,22 @@
         <v>1</v>
       </c>
       <c r="W42" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>keep:1, "Data Risk Categorisation":6</t>
+          <t>keep:0, "Data Risk Categorisation":7</t>
         </is>
       </c>
       <c r="Z42" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>Security Protocol Selection</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="b">
         <v>0</v>
       </c>
@@ -7032,7 +7028,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Physical Security Plan Communication</t>
+          <t>Security Plan Communication</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -7136,29 +7132,21 @@
         </is>
       </c>
       <c r="V43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 5/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>keep:2, "Physical Security Plan Communication/Physical Security Communication":5</t>
+          <t>keep:2, "Physical Security Planning":3, "Physical Security Plan Communication":2</t>
         </is>
       </c>
       <c r="Z43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>Physical Security Planning</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="b">
         <v>0</v>
       </c>
@@ -7310,7 +7298,7 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0.95</v>
+        <v>0.9528571428571428</v>
       </c>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr">
@@ -7529,7 +7517,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Security Trend Monitoring</t>
+          <t>Security Development Monitoring</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -7629,15 +7617,19 @@
         </is>
       </c>
       <c r="V46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W46" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="X46" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 6/7: </t>
+        </is>
+      </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>keep:6, "Security Development Monitoring":1</t>
+          <t>keep:1, "Security Development Monitoring":6</t>
         </is>
       </c>
       <c r="Z46" t="b">
@@ -7851,7 +7843,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Two-factor Authentication Enablement</t>
+          <t>Multi-factor Authentication Enablement</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -7958,16 +7950,16 @@
         <v>1</v>
       </c>
       <c r="W48" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.9</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>keep:6, "Multi-factor Authentication Enablement":1</t>
+          <t>keep:1, "Multi-factor Authentication Enablement":6</t>
         </is>
       </c>
       <c r="Z48" t="b">
@@ -8554,16 +8546,16 @@
         <v>1</v>
       </c>
       <c r="W52" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>keep:0, "Evaluation Documentation":7</t>
+          <t>keep:0, "Evaluation Documentation":4, "Evaluation Documentation Preparation":3</t>
         </is>
       </c>
       <c r="Z52" t="b">
@@ -8720,16 +8712,16 @@
         <v>1</v>
       </c>
       <c r="W53" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>keep:0, "ICT Gap Identification":7</t>
+          <t>keep:1, "ICT Gap Identification":6</t>
         </is>
       </c>
       <c r="Z53" t="b">
@@ -9183,7 +9175,7 @@
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>keep:4, "Financial Impact Interpretation":3</t>
+          <t>keep:4, "Financial Impact Interpretation":2, "Financial Impact Assessment":1</t>
         </is>
       </c>
       <c r="Z56" t="b">
@@ -9616,12 +9608,12 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Change Difficulty Evaluation":1</t>
         </is>
       </c>
       <c r="Z59" t="b">
@@ -10551,9 +10543,13 @@
       </c>
       <c r="AC65" t="inlineStr"/>
       <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>Skill name uses 'Management' which is not reflected in evidence actions of reviewing and determining compliance</t>
+        </is>
+      </c>
       <c r="AF65" t="b">
         <v>0</v>
       </c>
@@ -11484,7 +11480,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Privacy Policy Documentation</t>
+          <t>Policy Documentation</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -11574,19 +11570,15 @@
         </is>
       </c>
       <c r="V72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W72" t="n">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 7/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>keep:0, "Privacy Policy Documentation":7</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z72" t="b">
@@ -12181,12 +12173,12 @@
         <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Digital Information Security":1</t>
         </is>
       </c>
       <c r="Z76" t="b">
@@ -12330,16 +12322,16 @@
         <v>1</v>
       </c>
       <c r="W77" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>keep:0, "Policy Distribution":7</t>
+          <t>keep:3, "Policy Distribution":4</t>
         </is>
       </c>
       <c r="Z77" t="b">
@@ -12699,7 +12691,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Blockchain Anomaly Resolution</t>
+          <t>Blockchain Anomaly Problem Solving</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -12803,12 +12795,12 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>keep:0, "Blockchain Anomaly Resolution":6, "Blockchain Anomaly Problem Solving":1</t>
+          <t>keep:0, "Blockchain Anomaly Problem Solving":4, "Blockchain Anomaly Resolution":3</t>
         </is>
       </c>
       <c r="Z80" t="b">
@@ -12816,13 +12808,9 @@
       </c>
       <c r="AA80" t="inlineStr"/>
       <c r="AB80" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Foundation Skill describes problem‑solving capability that is already embedded in other blockchain solution skills and PCs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC80" t="inlineStr"/>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -13743,12 +13731,12 @@
         <v>0</v>
       </c>
       <c r="W86" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>keep:6, "Maintenance Schedule Development":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z86" t="b">
@@ -13760,13 +13748,9 @@
       </c>
       <c r="AC86" t="inlineStr"/>
       <c r="AD86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE86" t="inlineStr">
-        <is>
-          <t>...</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AE86" t="inlineStr"/>
       <c r="AF86" t="b">
         <v>0</v>
       </c>
@@ -13803,7 +13787,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Maintenance Testing Execution</t>
+          <t>Maintenance Testing</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -13900,15 +13884,19 @@
         </is>
       </c>
       <c r="V87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W87" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X87" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 6/7: </t>
+        </is>
+      </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>keep:4, "Maintenance Testing":3</t>
+          <t>keep:1, "Maintenance Testing":6</t>
         </is>
       </c>
       <c r="Z87" t="b">
@@ -14076,13 +14064,9 @@
       </c>
       <c r="AC88" t="inlineStr"/>
       <c r="AD88" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE88" t="inlineStr">
-        <is>
-          <t>Skill name uses 'Selection' which is not a synonym of the evidence verb 'Determine' and does not appear in the PCs or elements</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AE88" t="inlineStr"/>
       <c r="AF88" t="b">
         <v>0</v>
       </c>
@@ -16944,12 +16928,12 @@
         <v>0</v>
       </c>
       <c r="W106" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>keep:6, "Anomaly Detection":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z106" t="b">
@@ -17714,7 +17698,7 @@
       <c r="X111" t="inlineStr"/>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:5, "Feedback Management":2</t>
         </is>
       </c>
       <c r="Z111" t="b">
@@ -18015,12 +17999,12 @@
         <v>0</v>
       </c>
       <c r="W113" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X113" t="inlineStr"/>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>keep:6, "Protection Strategy Coordination":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z113" t="b">
@@ -18032,7 +18016,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>FS describes work style (planning and coordination) rather than a distinct task; capability already embedded in PCs and other skills</t>
+          <t>FS describes work style (planning coordination) rather than a distinct task; activity is implicit in strategy development and implementation PCs</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -18172,7 +18156,7 @@
         <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X114" t="inlineStr"/>
       <c r="Y114" t="inlineStr">
@@ -18793,7 +18777,7 @@
       <c r="X118" t="inlineStr"/>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:4, "Risk Evaluation":3</t>
         </is>
       </c>
       <c r="Z118" t="b">
@@ -19257,12 +19241,12 @@
         <v>0</v>
       </c>
       <c r="W121" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X121" t="inlineStr"/>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>keep:6, "Data Type Identification":1</t>
+          <t>keep:5, "Data Type Identification":2</t>
         </is>
       </c>
       <c r="Z121" t="b">
@@ -19416,12 +19400,12 @@
         <v>0</v>
       </c>
       <c r="W122" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X122" t="inlineStr"/>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Feedback Documentation Management":1</t>
         </is>
       </c>
       <c r="Z122" t="b">
@@ -19738,12 +19722,12 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>keep:0, "Contextual Anomaly Identification":6, "Contextual Anomaly Detection":1</t>
+          <t>keep:0, "Contextual Anomaly Identification":5, "Security Contextual Problem Solving":2</t>
         </is>
       </c>
       <c r="Z124" t="b">
@@ -21189,16 +21173,16 @@
         <v>1</v>
       </c>
       <c r="W133" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>keep:1, "Technical Documentation Reading":6</t>
+          <t>keep:0, "Technical Documentation Reading":7</t>
         </is>
       </c>
       <c r="Z133" t="b">
@@ -21386,7 +21370,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>FS describes work style (autonomous decision making) not a distinct task; capability already implicit in PCs</t>
+          <t>FS describes work style (autonomous decision making) not a distinct task; capability is implicit in other skills</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -21730,13 +21714,9 @@
       </c>
       <c r="AC136" t="inlineStr"/>
       <c r="AD136" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE136" t="inlineStr">
-        <is>
-          <t>Skill name uses 'Preparation' which does not appear in evidence; evidence describes 'Document' activity</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AE136" t="inlineStr"/>
       <c r="AF136" t="b">
         <v>0</v>
       </c>
@@ -22074,9 +22054,13 @@
         </is>
       </c>
       <c r="Z138" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA138" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>Incident Response Plan Evaluation</t>
+        </is>
+      </c>
       <c r="AB138" t="b">
         <v>0</v>
       </c>
@@ -22414,7 +22398,7 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>keep:0, "Incident Response Exercise Design":7</t>
+          <t>keep:0, "Incident Response Exercise Design/Incident Response Red‑Team Design":7</t>
         </is>
       </c>
       <c r="Z140" t="b">
@@ -22757,12 +22741,12 @@
         <v>0</v>
       </c>
       <c r="W142" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X142" t="inlineStr"/>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Technical Data Interpretation":1</t>
         </is>
       </c>
       <c r="Z142" t="b">
@@ -23640,7 +23624,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>FS describes work style (ensuring compliance) rather than a distinct task; capability is implicit in other skills like Risk Analysis and Business Continuity Evaluation</t>
+          <t>FS describes work style and compliance activity already embedded in other skills; not a distinct task for this unit</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -25192,7 +25176,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Strategic Planning</t>
+          <t>Strategy Prioritisation</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -25298,15 +25282,19 @@
         </is>
       </c>
       <c r="V157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W157" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="X157" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 4/7: </t>
+        </is>
+      </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>keep:6, "Strategy Prioritisation":1</t>
+          <t>keep:3, "Strategy Prioritisation":4</t>
         </is>
       </c>
       <c r="Z157" t="b">
@@ -25314,13 +25302,9 @@
       </c>
       <c r="AA157" t="inlineStr"/>
       <c r="AB157" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Foundation Skill describes a work style (strategic planning) that is already embedded in other skills and PCs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC157" t="inlineStr"/>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
@@ -26019,12 +26003,12 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Assists in confirming and documenting the types of information stored on each registered digital device.</t>
+          <t>Assists in identifying and confirming the types of information stored on each registered digital device.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>device data inventory, information classification, data mapping, asset documentation, digital records</t>
+          <t>device data inventory, information classification, data mapping, asset documentation, storage verification</t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -26115,7 +26099,7 @@
       </c>
       <c r="AG162" t="inlineStr">
         <is>
-          <t>Assists in confirming and documenting the types of information stored on each registered digital device.</t>
+          <t>Assists in identifying and confirming the types of information stored on each registered digital device.</t>
         </is>
       </c>
       <c r="AH162" t="b">
@@ -26123,7 +26107,7 @@
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>device data inventory, information classification, data mapping, asset documentation, digital records</t>
+          <t>device data inventory, information classification, data mapping, asset documentation, storage verification</t>
         </is>
       </c>
       <c r="AJ162" t="b">
@@ -26144,7 +26128,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Sign‑off Acquisition</t>
+          <t>Sign‑off Coordination</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -26164,12 +26148,12 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Secures final approval from designated stakeholders by coordinating, presenting, and confirming sign‑off requirements.</t>
+          <t>Secures final approval from designated personnel by managing sign‑off processes and confirming compliance.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>approval coordination, stakeholder confirmation, final sign‑off, approval documentation, sign‑off process</t>
+          <t>approval process, stakeholder engagement, compliance confirmation, sign‑off management, finalisation</t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -26230,7 +26214,7 @@
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>Sign‑off Acquisition</t>
+          <t>Sign‑off Coordination</t>
         </is>
       </c>
       <c r="V163" t="b">
@@ -26262,7 +26246,7 @@
       </c>
       <c r="AG163" t="inlineStr">
         <is>
-          <t>Secures final approval from designated stakeholders by coordinating, presenting, and confirming sign‑off requirements.</t>
+          <t>Secures final approval from designated personnel by managing sign‑off processes and confirming compliance.</t>
         </is>
       </c>
       <c r="AH163" t="b">
@@ -26270,7 +26254,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>approval coordination, stakeholder confirmation, final sign‑off, approval documentation, sign‑off process</t>
+          <t>approval process, stakeholder engagement, compliance confirmation, sign‑off management, finalisation</t>
         </is>
       </c>
       <c r="AJ163" t="b">
@@ -26320,7 +26304,7 @@
         </is>
       </c>
       <c r="J164" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
@@ -26392,7 +26376,7 @@
         <v>0</v>
       </c>
       <c r="W164" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="X164" t="inlineStr">
         <is>
@@ -26446,7 +26430,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Log Requirement Consultation</t>
+          <t>Data Log Strategy Discussion</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -26466,16 +26450,16 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Collaborates with relevant personnel to discuss and confirm data log requirements and processing strategy.</t>
+          <t>Facilitates discussions with relevant personnel to confirm data log requirements and processing strategies.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>data log requirements, processing strategy, personnel consultation, requirement discussion, log planning</t>
+          <t>data log requirements, processing strategy, personnel coordination, discussion facilitation, requirement confirmation</t>
         </is>
       </c>
       <c r="J165" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
@@ -26530,14 +26514,14 @@
       </c>
       <c r="U165" t="inlineStr">
         <is>
-          <t>Log Requirement Consultation</t>
+          <t>Data Log Strategy Discussion</t>
         </is>
       </c>
       <c r="V165" t="b">
         <v>0</v>
       </c>
       <c r="W165" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="X165" t="inlineStr">
         <is>
@@ -26562,7 +26546,7 @@
       </c>
       <c r="AG165" t="inlineStr">
         <is>
-          <t>Collaborates with relevant personnel to discuss and confirm data log requirements and processing strategy.</t>
+          <t>Facilitates discussions with relevant personnel to confirm data log requirements and processing strategies.</t>
         </is>
       </c>
       <c r="AH165" t="b">
@@ -26570,7 +26554,7 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>data log requirements, processing strategy, personnel consultation, requirement discussion, log planning</t>
+          <t>data log requirements, processing strategy, personnel coordination, discussion facilitation, requirement confirmation</t>
         </is>
       </c>
       <c r="AJ165" t="b">
@@ -26611,7 +26595,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Evaluates gathered threat data results to ensure reliability and consistency across sources and methods.</t>
+          <t>Evaluates gathered threat data results to ensure reliability and consistency before further processing.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -26707,7 +26691,7 @@
       </c>
       <c r="AG166" t="inlineStr">
         <is>
-          <t>Evaluates gathered threat data results to ensure reliability and consistency across sources and methods.</t>
+          <t>Evaluates gathered threat data results to ensure reliability and consistency before further processing.</t>
         </is>
       </c>
       <c r="AH166" t="b">
@@ -26761,7 +26745,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>effectiveness assessment, alignment verification, organisational requirements, legislative compliance, protection plan</t>
+          <t>protection plan assessment, organisational alignment, effectiveness analysis, legislative compliance, critical asset identification</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -26867,7 +26851,7 @@
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>effectiveness assessment, alignment verification, organisational requirements, legislative compliance, protection plan</t>
+          <t>protection plan assessment, organisational alignment, effectiveness analysis, legislative compliance, critical asset identification</t>
         </is>
       </c>
       <c r="AJ167" t="b">
@@ -26893,7 +26877,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>DOMAIN_KNOWLEDGE</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -26903,17 +26887,17 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>PRACTICAL</t>
+          <t>THEORETICAL</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>The worker assesses the current incident response plan, documents its conformity with requirements, and submits it for feedback.</t>
+          <t>Aligns the current incident response plan with required standards and documents the comparison for stakeholders.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>incident response plan, alignment assessment, documentation, requirements compliance, feedback submission</t>
+          <t>incident response plan, alignment assessment, documentation, requirements mapping, stakeholder feedback</t>
         </is>
       </c>
       <c r="J168" t="n">
@@ -27018,7 +27002,7 @@
       </c>
       <c r="AG168" t="inlineStr">
         <is>
-          <t>The worker assesses the current incident response plan, documents its conformity with requirements, and submits it for feedback.</t>
+          <t>Aligns the current incident response plan with required standards and documents the comparison for stakeholders.</t>
         </is>
       </c>
       <c r="AH168" t="b">
@@ -27026,7 +27010,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>incident response plan, alignment assessment, documentation, requirements compliance, feedback submission</t>
+          <t>incident response plan, alignment assessment, documentation, requirements mapping, stakeholder feedback</t>
         </is>
       </c>
       <c r="AJ168" t="b">
@@ -27067,16 +27051,16 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Assist in gathering, processing, and preserving evidence in line with organisational and legal requirements.</t>
+          <t>Assist in gathering, processing, and securely preserving evidence in line with established requirements and protocols.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>evidence collection, evidence processing, evidence preservation, incident response, legal compliance</t>
+          <t>evidence collection, evidence processing, evidence preservation, security protocols, assistance</t>
         </is>
       </c>
       <c r="J169" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -27151,7 +27135,7 @@
         <v>0</v>
       </c>
       <c r="W169" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="X169" t="inlineStr">
         <is>
@@ -27176,7 +27160,7 @@
       </c>
       <c r="AG169" t="inlineStr">
         <is>
-          <t>Assist in gathering, processing, and preserving evidence in line with organisational and legal requirements.</t>
+          <t>Assist in gathering, processing, and securely preserving evidence in line with established requirements and protocols.</t>
         </is>
       </c>
       <c r="AH169" t="b">
@@ -27184,7 +27168,7 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>evidence collection, evidence processing, evidence preservation, incident response, legal compliance</t>
+          <t>evidence collection, evidence processing, evidence preservation, security protocols, assistance</t>
         </is>
       </c>
       <c r="AJ169" t="b">
@@ -27225,16 +27209,16 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Identify essential business functions, critical data, and software, and assess ICT risk impacts on them.</t>
+          <t>Identify essential business functions, critical data, and software, and assess risk impacts on ICT systems.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>business critical functions, security environment, critical data, software assets, ICT risk assessment</t>
+          <t>business critical functions, security environment, critical data, software assets, risk impact assessment</t>
         </is>
       </c>
       <c r="J170" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -27304,7 +27288,7 @@
         <v>0</v>
       </c>
       <c r="W170" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="X170" t="inlineStr">
         <is>
@@ -27329,7 +27313,7 @@
       </c>
       <c r="AG170" t="inlineStr">
         <is>
-          <t>Identify essential business functions, critical data, and software, and assess ICT risk impacts on them.</t>
+          <t>Identify essential business functions, critical data, and software, and assess risk impacts on ICT systems.</t>
         </is>
       </c>
       <c r="AH170" t="b">
@@ -27337,7 +27321,7 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>business critical functions, security environment, critical data, software assets, ICT risk assessment</t>
+          <t>business critical functions, security environment, critical data, software assets, risk impact assessment</t>
         </is>
       </c>
       <c r="AJ170" t="b">

--- a/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v5.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v5.xlsx
@@ -744,7 +744,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>keep:0, "Stakeholder Viewpoint Elicitation":7</t>
+          <t>keep:0, "Stakeholder Viewpoint Elicitation/Viewpoint Elicitation":7</t>
         </is>
       </c>
       <c r="Z2" t="b">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Solution Research</t>
+          <t>Information Research</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>keep:0, "Solution Research":4, "Information Research":3</t>
+          <t>keep:0, "Information Research":4, "Solution Research":3</t>
         </is>
       </c>
       <c r="Z11" t="b">
@@ -2365,7 +2365,7 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Solution Presentation":1</t>
         </is>
       </c>
       <c r="Z12" t="b">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>keep:2, "Discussion Facilitation":5</t>
+          <t>keep:3, "Discussion Facilitation":4</t>
         </is>
       </c>
       <c r="Z16" t="b">
@@ -3805,16 +3805,16 @@
         <v>1</v>
       </c>
       <c r="W21" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>keep:0, "Insight Presentation":7</t>
+          <t>keep:3, "Insight Presentation":4</t>
         </is>
       </c>
       <c r="Z21" t="b">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>domain term "inventory" (asset management) not found in unit text</t>
+          <t>Skill name uses 'Inventory Management' while evidence describes creating and maintaining a register, which is a distinct activity</t>
         </is>
       </c>
       <c r="AF38" t="b">
@@ -6814,13 +6814,9 @@
         </is>
       </c>
       <c r="Z41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>Security Plan Communication</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA41" t="inlineStr"/>
       <c r="AB41" t="b">
         <v>0</v>
       </c>
@@ -7028,7 +7024,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Security Plan Communication</t>
+          <t>Physical Security Plan Communication</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -7132,21 +7128,29 @@
         </is>
       </c>
       <c r="V43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W43" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X43" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 6/7: </t>
+        </is>
+      </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>keep:2, "Physical Security Planning":3, "Physical Security Plan Communication":2</t>
+          <t>keep:1, "Physical Security Plan Communication/Physical Security Communication":6</t>
         </is>
       </c>
       <c r="Z43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>Physical Security Planning</t>
+        </is>
+      </c>
       <c r="AB43" t="b">
         <v>0</v>
       </c>
@@ -7298,7 +7302,7 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0.9528571428571428</v>
+        <v>0.95</v>
       </c>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr">
@@ -7843,7 +7847,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Multi-factor Authentication Enablement</t>
+          <t>Two-factor Authentication Enablement</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -7950,16 +7954,16 @@
         <v>1</v>
       </c>
       <c r="W48" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t>postprocess: spelling/redundancy</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>keep:1, "Multi-factor Authentication Enablement":6</t>
+          <t>keep:5, "Multi-factor Authentication Enablement":2</t>
         </is>
       </c>
       <c r="Z48" t="b">
@@ -8559,13 +8563,9 @@
         </is>
       </c>
       <c r="Z52" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>Strategic Plan Analysis</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA52" t="inlineStr"/>
       <c r="AB52" t="b">
         <v>0</v>
       </c>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ICT Gap Identification</t>
+          <t>Ict Gap Identification</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -8709,19 +8709,15 @@
         </is>
       </c>
       <c r="V53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 6/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>keep:1, "ICT Gap Identification":6</t>
+          <t>keep:4, "ICT Gap Identification":3</t>
         </is>
       </c>
       <c r="Z53" t="b">
@@ -9175,7 +9171,7 @@
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>keep:4, "Financial Impact Interpretation":2, "Financial Impact Assessment":1</t>
+          <t>keep:4, "Financial Impact Interpretation":3</t>
         </is>
       </c>
       <c r="Z56" t="b">
@@ -9613,7 +9609,7 @@
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>keep:6, "Change Difficulty Evaluation":1</t>
+          <t>keep:6, "Risk Difficulty Assessment":1</t>
         </is>
       </c>
       <c r="Z59" t="b">
@@ -9629,7 +9625,7 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>Skill name uses 'Planning' but evidence describes evaluating difficulty, not planning</t>
+          <t>Skill name uses 'Planning' but evidence only involves evaluating difficulty, not planning</t>
         </is>
       </c>
       <c r="AF59" t="b">
@@ -11480,7 +11476,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Policy Documentation</t>
+          <t>Privacy Policy Documentation</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -11570,15 +11566,19 @@
         </is>
       </c>
       <c r="V72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W72" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X72" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 6/7: </t>
+        </is>
+      </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:1, "Privacy Policy Documentation":6</t>
         </is>
       </c>
       <c r="Z72" t="b">
@@ -12322,16 +12322,16 @@
         <v>1</v>
       </c>
       <c r="W77" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>keep:3, "Policy Distribution":4</t>
+          <t>keep:0, "Policy Distribution":7</t>
         </is>
       </c>
       <c r="Z77" t="b">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Blockchain Anomaly Problem Solving</t>
+          <t>Blockchain Anomaly Resolution</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>keep:0, "Blockchain Anomaly Problem Solving":4, "Blockchain Anomaly Resolution":3</t>
+          <t>keep:0, "Blockchain Anomaly Resolution":6, "Blockchain Anomaly Solving":1</t>
         </is>
       </c>
       <c r="Z80" t="b">
@@ -12808,9 +12808,13 @@
       </c>
       <c r="AA80" t="inlineStr"/>
       <c r="AB80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC80" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Foundation Skill describes problem‑solving capability already embedded in other blockchain solution skills and PCs</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -12951,7 +12955,7 @@
         <v>0</v>
       </c>
       <c r="W81" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr">
@@ -13731,12 +13735,12 @@
         <v>0</v>
       </c>
       <c r="W86" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Maintenance Schedule Development":1</t>
         </is>
       </c>
       <c r="Z86" t="b">
@@ -13891,12 +13895,12 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>keep:1, "Maintenance Testing":6</t>
+          <t>keep:2, "Maintenance Testing":5</t>
         </is>
       </c>
       <c r="Z87" t="b">
@@ -15479,12 +15483,12 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>keep:3, "Dataset Creation":4</t>
+          <t>keep:2, "Dataset Creation":5</t>
         </is>
       </c>
       <c r="Z97" t="b">
@@ -16509,7 +16513,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Stakeholder Findings Communication</t>
+          <t>Threat Findings Communication</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -16609,15 +16613,19 @@
         </is>
       </c>
       <c r="V104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W104" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X104" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 6/7: </t>
+        </is>
+      </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>keep:5, "Threat Findings Communication":2</t>
+          <t>keep:1, "Threat Findings Communication":6</t>
         </is>
       </c>
       <c r="Z104" t="b">
@@ -16771,12 +16779,12 @@
         <v>0</v>
       </c>
       <c r="W105" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X105" t="inlineStr"/>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Threat Data Collation":1</t>
         </is>
       </c>
       <c r="Z105" t="b">
@@ -17698,7 +17706,7 @@
       <c r="X111" t="inlineStr"/>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>keep:5, "Feedback Management":2</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z111" t="b">
@@ -18004,7 +18012,7 @@
       <c r="X113" t="inlineStr"/>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:4, "Protection Strategy Coordination":3</t>
         </is>
       </c>
       <c r="Z113" t="b">
@@ -18016,7 +18024,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>FS describes work style (planning coordination) rather than a distinct task; activity is implicit in strategy development and implementation PCs</t>
+          <t>FS describes work style (planning coordination) already embedded in strategy development and implementation PCs</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -18156,7 +18164,7 @@
         <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X114" t="inlineStr"/>
       <c r="Y114" t="inlineStr">
@@ -18309,7 +18317,7 @@
         <v>0</v>
       </c>
       <c r="W115" t="n">
-        <v>0.95</v>
+        <v>0.9428571428571428</v>
       </c>
       <c r="X115" t="inlineStr"/>
       <c r="Y115" t="inlineStr">
@@ -18675,7 +18683,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Risk Assessment Evaluation</t>
+          <t>Risk Evaluation</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -18769,15 +18777,19 @@
         </is>
       </c>
       <c r="V118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W118" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X118" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/7: </t>
+        </is>
+      </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>keep:4, "Risk Evaluation":3</t>
+          <t>keep:2, "Risk Evaluation":5</t>
         </is>
       </c>
       <c r="Z118" t="b">
@@ -19246,7 +19258,7 @@
       <c r="X121" t="inlineStr"/>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>keep:5, "Data Type Identification":2</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z121" t="b">
@@ -19718,16 +19730,16 @@
         <v>1</v>
       </c>
       <c r="W124" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>keep:0, "Contextual Anomaly Identification":5, "Security Contextual Problem Solving":2</t>
+          <t>keep:0, "Contextual Anomaly Identification":7</t>
         </is>
       </c>
       <c r="Z124" t="b">
@@ -19890,7 +19902,7 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>keep:0, "Security Requirements Documentation":7</t>
+          <t>keep:0, "Security Requirements Documentation/Security Findings Documentation":7</t>
         </is>
       </c>
       <c r="Z125" t="b">
@@ -21070,7 +21082,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Technical Documentation Reading</t>
+          <t>Technical Specification Reading</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -21170,19 +21182,15 @@
         </is>
       </c>
       <c r="V133" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W133" t="n">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="X133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 7/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X133" t="inlineStr"/>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>keep:0, "Technical Documentation Reading":7</t>
+          <t>keep:4, "Technical Documentation Reading":3</t>
         </is>
       </c>
       <c r="Z133" t="b">
@@ -21190,9 +21198,13 @@
       </c>
       <c r="AA133" t="inlineStr"/>
       <c r="AB133" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC133" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>FS describes reading/interpreting documentation, which is already embedded in other skills such as Industry Methodology Research and Security Requirements Documentation</t>
+        </is>
+      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
@@ -21370,7 +21382,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>FS describes work style (autonomous decision making) not a distinct task; capability is implicit in other skills</t>
+          <t>FS describes work style (autonomous decision making) not a distinct task; capability already implicit in PCs</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -21869,16 +21881,16 @@
         <v>1</v>
       </c>
       <c r="W137" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>keep:3, "Incident Response Plan Evaluation":4</t>
+          <t>keep:0, "Incident Response Plan Evaluation":7</t>
         </is>
       </c>
       <c r="Z137" t="b">
@@ -22054,13 +22066,9 @@
         </is>
       </c>
       <c r="Z138" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA138" t="inlineStr">
-        <is>
-          <t>Incident Response Plan Evaluation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA138" t="inlineStr"/>
       <c r="AB138" t="b">
         <v>0</v>
       </c>
@@ -22389,16 +22397,16 @@
         <v>1</v>
       </c>
       <c r="W140" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>keep:0, "Incident Response Exercise Design/Incident Response Red‑Team Design":7</t>
+          <t>keep:0, "Incident Response Exercise Design":6, "Incident Response Red Teaming":1</t>
         </is>
       </c>
       <c r="Z140" t="b">
@@ -22741,22 +22749,18 @@
         <v>0</v>
       </c>
       <c r="W142" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X142" t="inlineStr"/>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>keep:6, "Technical Data Interpretation":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z142" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA142" t="inlineStr">
-        <is>
-          <t>Technical Data Interpretation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA142" t="inlineStr"/>
       <c r="AB142" t="b">
         <v>0</v>
       </c>
@@ -23624,7 +23628,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>FS describes work style and compliance activity already embedded in other skills; not a distinct task for this unit</t>
+          <t>FS describes work style and compliance strategy that is implicit in other skills and not a distinct task for this unit</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -23789,13 +23793,9 @@
         </is>
       </c>
       <c r="Z148" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA148" t="inlineStr">
-        <is>
-          <t>Disaster Recovery Planning</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA148" t="inlineStr"/>
       <c r="AB148" t="b">
         <v>0</v>
       </c>
@@ -24799,9 +24799,13 @@
       </c>
       <c r="AA154" t="inlineStr"/>
       <c r="AB154" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC154" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Foundation Skill describes a work style (problem solving) that is already embedded in multiple PC-based skills and other skills; it does not add a distinct standalone task</t>
+        </is>
+      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
@@ -24956,17 +24960,13 @@
       <c r="X155" t="inlineStr"/>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:5, "Risk Assessment":2</t>
         </is>
       </c>
       <c r="Z155" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA155" t="inlineStr">
-        <is>
-          <t>Disaster Recovery Planning</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA155" t="inlineStr"/>
       <c r="AB155" t="b">
         <v>0</v>
       </c>
@@ -25176,7 +25176,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Strategy Prioritisation</t>
+          <t>Strategic Planning</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -25282,19 +25282,15 @@
         </is>
       </c>
       <c r="V157" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W157" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 4/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X157" t="inlineStr"/>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>keep:3, "Strategy Prioritisation":4</t>
+          <t>keep:4, "Strategy Prioritisation":3</t>
         </is>
       </c>
       <c r="Z157" t="b">
@@ -25867,7 +25863,7 @@
         </is>
       </c>
       <c r="J161" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -25929,7 +25925,7 @@
         <v>0</v>
       </c>
       <c r="W161" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="X161" t="inlineStr">
         <is>
@@ -26003,12 +25999,12 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Assists in identifying and confirming the types of information stored on each registered digital device.</t>
+          <t>Assists in confirming and documenting the types of information stored on each registered digital device.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>device data inventory, information classification, data mapping, asset documentation, storage verification</t>
+          <t>device data inventory, information classification, data mapping, asset documentation, digital records</t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -26099,7 +26095,7 @@
       </c>
       <c r="AG162" t="inlineStr">
         <is>
-          <t>Assists in identifying and confirming the types of information stored on each registered digital device.</t>
+          <t>Assists in confirming and documenting the types of information stored on each registered digital device.</t>
         </is>
       </c>
       <c r="AH162" t="b">
@@ -26107,7 +26103,7 @@
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>device data inventory, information classification, data mapping, asset documentation, storage verification</t>
+          <t>device data inventory, information classification, data mapping, asset documentation, digital records</t>
         </is>
       </c>
       <c r="AJ162" t="b">
@@ -26148,12 +26144,12 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Secures final approval from designated personnel by managing sign‑off processes and confirming compliance.</t>
+          <t>Secures final approval from designated personnel by organising, presenting, and confirming sign‑off requirements.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>approval process, stakeholder engagement, compliance confirmation, sign‑off management, finalisation</t>
+          <t>approval process, stakeholder engagement, documentation finalisation, authority confirmation, sign‑off management</t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -26246,7 +26242,7 @@
       </c>
       <c r="AG163" t="inlineStr">
         <is>
-          <t>Secures final approval from designated personnel by managing sign‑off processes and confirming compliance.</t>
+          <t>Secures final approval from designated personnel by organising, presenting, and confirming sign‑off requirements.</t>
         </is>
       </c>
       <c r="AH163" t="b">
@@ -26254,7 +26250,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>approval process, stakeholder engagement, compliance confirmation, sign‑off management, finalisation</t>
+          <t>approval process, stakeholder engagement, documentation finalisation, authority confirmation, sign‑off management</t>
         </is>
       </c>
       <c r="AJ163" t="b">
@@ -26300,11 +26296,11 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>process analysis, transaction evaluation, blockchain suitability, regulatory compliance, organisational policy</t>
+          <t>process evaluation, transaction analysis, blockchain suitability, regulatory compliance, organisational policy</t>
         </is>
       </c>
       <c r="J164" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
@@ -26376,7 +26372,7 @@
         <v>0</v>
       </c>
       <c r="W164" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="X164" t="inlineStr">
         <is>
@@ -26409,7 +26405,7 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>process analysis, transaction evaluation, blockchain suitability, regulatory compliance, organisational policy</t>
+          <t>process evaluation, transaction analysis, blockchain suitability, regulatory compliance, organisational policy</t>
         </is>
       </c>
       <c r="AJ164" t="b">
@@ -26430,7 +26426,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Data Log Strategy Discussion</t>
+          <t>Log Requirement Consultation</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -26450,16 +26446,16 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Facilitates discussions with relevant personnel to confirm data log requirements and processing strategies.</t>
+          <t>Collaborates with relevant personnel to discuss and confirm data log requirements and processing strategy.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>data log requirements, processing strategy, personnel coordination, discussion facilitation, requirement confirmation</t>
+          <t>data log requirements, processing strategy, personnel consultation, requirement discussion, log strategy confirmation</t>
         </is>
       </c>
       <c r="J165" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
@@ -26514,14 +26510,14 @@
       </c>
       <c r="U165" t="inlineStr">
         <is>
-          <t>Data Log Strategy Discussion</t>
+          <t>Log Requirement Consultation</t>
         </is>
       </c>
       <c r="V165" t="b">
         <v>0</v>
       </c>
       <c r="W165" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="X165" t="inlineStr">
         <is>
@@ -26546,7 +26542,7 @@
       </c>
       <c r="AG165" t="inlineStr">
         <is>
-          <t>Facilitates discussions with relevant personnel to confirm data log requirements and processing strategies.</t>
+          <t>Collaborates with relevant personnel to discuss and confirm data log requirements and processing strategy.</t>
         </is>
       </c>
       <c r="AH165" t="b">
@@ -26554,7 +26550,7 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>data log requirements, processing strategy, personnel coordination, discussion facilitation, requirement confirmation</t>
+          <t>data log requirements, processing strategy, personnel consultation, requirement discussion, log strategy confirmation</t>
         </is>
       </c>
       <c r="AJ165" t="b">
@@ -26595,7 +26591,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Evaluates gathered threat data results to ensure reliability and consistency before further processing.</t>
+          <t>Evaluates gathered threat data results to confirm reliability and consistency before further processing.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -26691,7 +26687,7 @@
       </c>
       <c r="AG166" t="inlineStr">
         <is>
-          <t>Evaluates gathered threat data results to ensure reliability and consistency before further processing.</t>
+          <t>Evaluates gathered threat data results to confirm reliability and consistency before further processing.</t>
         </is>
       </c>
       <c r="AH166" t="b">
@@ -26740,7 +26736,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Assess the current protection plan's effectiveness and ensure it aligns with organisational and legislative requirements.</t>
+          <t>Assess the current protection plan's effectiveness and ensure it aligns with organisational requirements and legislative standards.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -26843,7 +26839,7 @@
       </c>
       <c r="AG167" t="inlineStr">
         <is>
-          <t>Assess the current protection plan's effectiveness and ensure it aligns with organisational and legislative requirements.</t>
+          <t>Assess the current protection plan's effectiveness and ensure it aligns with organisational requirements and legislative standards.</t>
         </is>
       </c>
       <c r="AH167" t="b">
@@ -26892,12 +26888,12 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Aligns the current incident response plan with required standards and documents the comparison for stakeholders.</t>
+          <t>Aligns the current incident response plan with required standards and documents the findings for review.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>incident response plan, alignment assessment, documentation, requirements mapping, stakeholder feedback</t>
+          <t>incident response plan, alignment, documentation, requirements, feedback</t>
         </is>
       </c>
       <c r="J168" t="n">
@@ -27002,7 +26998,7 @@
       </c>
       <c r="AG168" t="inlineStr">
         <is>
-          <t>Aligns the current incident response plan with required standards and documents the comparison for stakeholders.</t>
+          <t>Aligns the current incident response plan with required standards and documents the findings for review.</t>
         </is>
       </c>
       <c r="AH168" t="b">
@@ -27010,7 +27006,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>incident response plan, alignment assessment, documentation, requirements mapping, stakeholder feedback</t>
+          <t>incident response plan, alignment, documentation, requirements, feedback</t>
         </is>
       </c>
       <c r="AJ168" t="b">
@@ -27051,16 +27047,16 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Assist in gathering, processing, and securely preserving evidence in line with established requirements and protocols.</t>
+          <t>Assist in gathering, processing, and preserving incident evidence in line with organisational requirements and standards.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>evidence collection, evidence processing, evidence preservation, security protocols, assistance</t>
+          <t>evidence collection, evidence processing, evidence preservation, incident response, organisational requirements</t>
         </is>
       </c>
       <c r="J169" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -27135,7 +27131,7 @@
         <v>0</v>
       </c>
       <c r="W169" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="X169" t="inlineStr">
         <is>
@@ -27160,7 +27156,7 @@
       </c>
       <c r="AG169" t="inlineStr">
         <is>
-          <t>Assist in gathering, processing, and securely preserving evidence in line with established requirements and protocols.</t>
+          <t>Assist in gathering, processing, and preserving incident evidence in line with organisational requirements and standards.</t>
         </is>
       </c>
       <c r="AH169" t="b">
@@ -27168,7 +27164,7 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>evidence collection, evidence processing, evidence preservation, security protocols, assistance</t>
+          <t>evidence collection, evidence processing, evidence preservation, incident response, organisational requirements</t>
         </is>
       </c>
       <c r="AJ169" t="b">
@@ -27209,12 +27205,12 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Identify essential business functions, critical data, and software, and assess risk impacts on ICT systems.</t>
+          <t>Identifies essential business functions, critical data, and software, and evaluates ICT risk impacts on them.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>business critical functions, security environment, critical data, software assets, risk impact assessment</t>
+          <t>business critical functions, security environment, critical data, software assets, ICT risk assessment</t>
         </is>
       </c>
       <c r="J170" t="n">
@@ -27313,7 +27309,7 @@
       </c>
       <c r="AG170" t="inlineStr">
         <is>
-          <t>Identify essential business functions, critical data, and software, and assess risk impacts on ICT systems.</t>
+          <t>Identifies essential business functions, critical data, and software, and evaluates ICT risk impacts on them.</t>
         </is>
       </c>
       <c r="AH170" t="b">
@@ -27321,7 +27317,7 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>business critical functions, security environment, critical data, software assets, risk impact assessment</t>
+          <t>business critical functions, security environment, critical data, software assets, ICT risk assessment</t>
         </is>
       </c>
       <c r="AJ170" t="b">
@@ -27362,12 +27358,12 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Creates and records detailed disaster strategy processes, cut‑over criteria, and secures final task sign‑off.</t>
+          <t>The worker identifies, records, and finalises disaster strategy processes, cut‑over criteria, and obtains sign‑off.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>disaster strategy, process documentation, cut‑over criteria, task sign‑off, implementation</t>
+          <t>disaster strategy, process documentation, cut‑over criteria, task sign‑off, finalisation</t>
         </is>
       </c>
       <c r="J171" t="n">
@@ -27466,7 +27462,7 @@
       </c>
       <c r="AG171" t="inlineStr">
         <is>
-          <t>Creates and records detailed disaster strategy processes, cut‑over criteria, and secures final task sign‑off.</t>
+          <t>The worker identifies, records, and finalises disaster strategy processes, cut‑over criteria, and obtains sign‑off.</t>
         </is>
       </c>
       <c r="AH171" t="b">
@@ -27474,7 +27470,7 @@
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>disaster strategy, process documentation, cut‑over criteria, task sign‑off, implementation</t>
+          <t>disaster strategy, process documentation, cut‑over criteria, task sign‑off, finalisation</t>
         </is>
       </c>
       <c r="AJ171" t="b">

--- a/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v5.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v5.xlsx
@@ -744,7 +744,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>keep:0, "Stakeholder Viewpoint Elicitation/Viewpoint Elicitation":7</t>
+          <t>keep:0, "Stakeholder Viewpoint Elicitation":7</t>
         </is>
       </c>
       <c r="Z2" t="b">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Idea Viability Evaluation</t>
+          <t>Solution Viability Assessment</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1721,12 +1721,12 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>keep:0, "Idea Viability Evaluation":6, "Solution Viability Assessment":1</t>
+          <t>keep:0, "Solution Viability Assessment":4, "Idea Viability Evaluation":3</t>
         </is>
       </c>
       <c r="Z8" t="b">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Information Research</t>
+          <t>Solution Research</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2202,16 +2202,16 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>keep:0, "Information Research":4, "Solution Research":3</t>
+          <t>keep:0, "Solution Research":7</t>
         </is>
       </c>
       <c r="Z11" t="b">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>keep:3, "Solution Refinement":4</t>
+          <t>keep:1, "Solution Refinement":6</t>
         </is>
       </c>
       <c r="Z13" t="b">
@@ -2700,9 +2700,13 @@
         </is>
       </c>
       <c r="Z14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Solution Research</t>
+        </is>
+      </c>
       <c r="AB14" t="b">
         <v>0</v>
       </c>
@@ -3017,16 +3021,16 @@
         <v>1</v>
       </c>
       <c r="W16" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>keep:3, "Discussion Facilitation":4</t>
+          <t>keep:0, "Discussion Facilitation":7</t>
         </is>
       </c>
       <c r="Z16" t="b">
@@ -3809,12 +3813,12 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>keep:3, "Insight Presentation":4</t>
+          <t>keep:1, "Insight Presentation":6</t>
         </is>
       </c>
       <c r="Z21" t="b">
@@ -6003,7 +6007,7 @@
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>keep:4, "Device Configuration":3</t>
+          <t>keep:5, "Device Configuration":2</t>
         </is>
       </c>
       <c r="Z36" t="b">
@@ -6341,7 +6345,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>Skill name uses 'Inventory Management' while evidence describes creating and maintaining a register, which is a distinct activity</t>
+          <t>domain term "inventory" (asset management) not found in unit text</t>
         </is>
       </c>
       <c r="AF38" t="b">
@@ -6814,9 +6818,13 @@
         </is>
       </c>
       <c r="Z41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA41" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>Security Plan Communication</t>
+        </is>
+      </c>
       <c r="AB41" t="b">
         <v>0</v>
       </c>
@@ -7024,7 +7032,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Physical Security Plan Communication</t>
+          <t>Security Plan Communication</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -7128,29 +7136,21 @@
         </is>
       </c>
       <c r="V43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 6/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>keep:1, "Physical Security Plan Communication/Physical Security Communication":6</t>
+          <t>keep:5, "Physical Security Plan Communication":2</t>
         </is>
       </c>
       <c r="Z43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>Physical Security Planning</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="b">
         <v>0</v>
       </c>
@@ -7521,7 +7521,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Security Development Monitoring</t>
+          <t>Security Trend Monitoring</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -7621,19 +7621,15 @@
         </is>
       </c>
       <c r="V46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 6/7: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>keep:1, "Security Development Monitoring":6</t>
+          <t>keep:6, "Security Development Monitoring":1</t>
         </is>
       </c>
       <c r="Z46" t="b">
@@ -7963,7 +7959,7 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>keep:5, "Multi-factor Authentication Enablement":2</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z48" t="b">
@@ -8460,7 +8456,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Evaluation Documentation</t>
+          <t>Documentation Preparation</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -8547,19 +8543,15 @@
         </is>
       </c>
       <c r="V52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 4/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>keep:0, "Evaluation Documentation":4, "Evaluation Documentation Preparation":3</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z52" t="b">
@@ -8717,7 +8709,7 @@
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>keep:4, "ICT Gap Identification":3</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z53" t="b">
@@ -9076,7 +9068,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Numerical Data Interpretation</t>
+          <t>Financial Impact Interpretation</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -9163,15 +9155,19 @@
         </is>
       </c>
       <c r="V56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W56" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X56" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 4/7: </t>
+        </is>
+      </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>keep:4, "Financial Impact Interpretation":3</t>
+          <t>keep:0, "Financial Impact Interpretation":4, "Financial Impact Assessment":3</t>
         </is>
       </c>
       <c r="Z56" t="b">
@@ -9604,12 +9600,12 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>keep:6, "Risk Difficulty Assessment":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z59" t="b">
@@ -9625,7 +9621,7 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>Skill name uses 'Planning' but evidence only involves evaluating difficulty, not planning</t>
+          <t>Skill name includes 'Planning' but evidence only involves evaluating difficulty, not planning</t>
         </is>
       </c>
       <c r="AF59" t="b">
@@ -10522,12 +10518,12 @@
         <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Compliance Review":1</t>
         </is>
       </c>
       <c r="Z65" t="b">
@@ -10539,13 +10535,9 @@
       </c>
       <c r="AC65" t="inlineStr"/>
       <c r="AD65" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE65" t="inlineStr">
-        <is>
-          <t>Skill name uses 'Management' which is not reflected in evidence actions of reviewing and determining compliance</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="b">
         <v>0</v>
       </c>
@@ -10824,12 +10816,12 @@
         <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>keep:6, "Feedback Management":1</t>
+          <t>keep:5, "Feedback Management":2</t>
         </is>
       </c>
       <c r="Z67" t="b">
@@ -11476,7 +11468,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Privacy Policy Documentation</t>
+          <t>Policy Documentation</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -11566,19 +11558,15 @@
         </is>
       </c>
       <c r="V72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W72" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 6/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>keep:1, "Privacy Policy Documentation":6</t>
+          <t>keep:5, "Privacy Policy Documentation":2</t>
         </is>
       </c>
       <c r="Z72" t="b">
@@ -12080,7 +12068,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Secure Digital Handling</t>
+          <t>Digital Information Security</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -12170,15 +12158,19 @@
         </is>
       </c>
       <c r="V76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W76" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="X76" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/7: </t>
+        </is>
+      </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>keep:6, "Digital Information Security":1</t>
+          <t>keep:2, "Digital Information Security":5</t>
         </is>
       </c>
       <c r="Z76" t="b">
@@ -12635,12 +12627,12 @@
         <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Blockchain Platform Installation":1</t>
         </is>
       </c>
       <c r="Z79" t="b">
@@ -12795,12 +12787,12 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>keep:0, "Blockchain Anomaly Resolution":6, "Blockchain Anomaly Solving":1</t>
+          <t>keep:2, "Blockchain Anomaly Resolution":5</t>
         </is>
       </c>
       <c r="Z80" t="b">
@@ -12812,7 +12804,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Foundation Skill describes problem‑solving capability already embedded in other blockchain solution skills and PCs</t>
+          <t>Foundation Skill describes problem‑solving behavior that is already embedded in other blockchain solution skills and PCs</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -12955,7 +12947,7 @@
         <v>0</v>
       </c>
       <c r="W81" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr">
@@ -13735,12 +13727,12 @@
         <v>0</v>
       </c>
       <c r="W86" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>keep:6, "Maintenance Schedule Development":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z86" t="b">
@@ -13895,12 +13887,12 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>keep:2, "Maintenance Testing":5</t>
+          <t>keep:1, "Maintenance Testing":6</t>
         </is>
       </c>
       <c r="Z87" t="b">
@@ -15483,12 +15475,12 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>keep:2, "Dataset Creation":5</t>
+          <t>keep:1, "Dataset Creation":6</t>
         </is>
       </c>
       <c r="Z97" t="b">
@@ -15496,7 +15488,7 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>Threat Data Collection</t>
+          <t>Threat Data Collation</t>
         </is>
       </c>
       <c r="AB97" t="b">
@@ -16513,7 +16505,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Threat Findings Communication</t>
+          <t>Stakeholder Findings Communication</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -16613,19 +16605,15 @@
         </is>
       </c>
       <c r="V104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W104" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 6/7: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="X104" t="inlineStr"/>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>keep:1, "Threat Findings Communication":6</t>
+          <t>keep:6, "Threat Findings Communication":1</t>
         </is>
       </c>
       <c r="Z104" t="b">
@@ -16676,7 +16664,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Threat Data Collection</t>
+          <t>Threat Data Collation</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -16776,15 +16764,19 @@
         </is>
       </c>
       <c r="V105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W105" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="X105" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/7: </t>
+        </is>
+      </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>keep:6, "Threat Data Collation":1</t>
+          <t>keep:2, "Threat Data Collation":5</t>
         </is>
       </c>
       <c r="Z105" t="b">
@@ -17701,12 +17693,12 @@
         <v>0</v>
       </c>
       <c r="W111" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X111" t="inlineStr"/>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Feedback Management":1</t>
         </is>
       </c>
       <c r="Z111" t="b">
@@ -18012,7 +18004,7 @@
       <c r="X113" t="inlineStr"/>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>keep:4, "Protection Strategy Coordination":3</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z113" t="b">
@@ -18024,7 +18016,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>FS describes work style (planning coordination) already embedded in strategy development and implementation PCs</t>
+          <t>FS describes work style (planning coordination) rather than a distinct task; activity is implicit in strategy development and implementation PCs</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -18317,12 +18309,12 @@
         <v>0</v>
       </c>
       <c r="W115" t="n">
-        <v>0.9428571428571428</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X115" t="inlineStr"/>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Critical Infrastructure Protection Planning":1</t>
         </is>
       </c>
       <c r="Z115" t="b">
@@ -18683,7 +18675,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Risk Evaluation</t>
+          <t>Risk Assessment Evaluation</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -18777,19 +18769,15 @@
         </is>
       </c>
       <c r="V118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W118" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 5/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X118" t="inlineStr"/>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>keep:2, "Risk Evaluation":5</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z118" t="b">
@@ -19623,7 +19611,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Contextual Anomaly Identification</t>
+          <t>Security Contextual Problem Solving</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -19730,16 +19718,16 @@
         <v>1</v>
       </c>
       <c r="W124" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>keep:0, "Contextual Anomaly Identification":7</t>
+          <t>keep:0, "Security Contextual Problem Solving/Security Context Problem Solving":6, "Security Anomaly Identification":1</t>
         </is>
       </c>
       <c r="Z124" t="b">
@@ -20558,7 +20546,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>FS describes work style (planning and reviewing) not a distinct task; capability already embedded in PCs and other skills</t>
+          <t>FS describes work style (planning and reviewing) not a distinct task; capability is implicit in other skills and PCs</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -21190,7 +21178,7 @@
       <c r="X133" t="inlineStr"/>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>keep:4, "Technical Documentation Reading":3</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z133" t="b">
@@ -21202,7 +21190,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>FS describes reading/interpreting documentation, which is already embedded in other skills such as Industry Methodology Research and Security Requirements Documentation</t>
+          <t>Foundation Skill describes reading/interpreting documentation, which is already embedded in other skills such as Industry Methodology Research and Security Requirements Analysis</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -21382,7 +21370,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>FS describes work style (autonomous decision making) not a distinct task; capability already implicit in PCs</t>
+          <t>FS describes work style (autonomous decision‑making) rather than a distinct task; the activity is implicit in other PC‑based skills</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -21881,16 +21869,16 @@
         <v>1</v>
       </c>
       <c r="W137" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>keep:0, "Incident Response Plan Evaluation":7</t>
+          <t>keep:1, "Incident Response Plan Evaluation":6</t>
         </is>
       </c>
       <c r="Z137" t="b">
@@ -22281,7 +22269,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Incident Response Exercise Design</t>
+          <t>Incident Response Training</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -22397,16 +22385,16 @@
         <v>1</v>
       </c>
       <c r="W140" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>keep:0, "Incident Response Exercise Design":6, "Incident Response Red Teaming":1</t>
+          <t>keep:0, "Incident Response Training":7</t>
         </is>
       </c>
       <c r="Z140" t="b">
@@ -23628,7 +23616,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>FS describes work style and compliance strategy that is implicit in other skills and not a distinct task for this unit</t>
+          <t>FS describes work style (ensuring compliance) rather than a distinct task; capability is implicit in other skills like Risk Analysis and Business Continuity Evaluation</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -24448,16 +24436,16 @@
         <v>1</v>
       </c>
       <c r="W152" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>keep:0, "Business Data Analysis":7</t>
+          <t>keep:1, "Business Data Analysis":6</t>
         </is>
       </c>
       <c r="Z152" t="b">
@@ -24786,7 +24774,7 @@
         <v>0</v>
       </c>
       <c r="W154" t="n">
-        <v>0.95</v>
+        <v>0.9428571428571428</v>
       </c>
       <c r="X154" t="inlineStr"/>
       <c r="Y154" t="inlineStr">
@@ -24803,7 +24791,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Foundation Skill describes a work style (problem solving) that is already embedded in multiple PC-based skills and other skills; it does not add a distinct standalone task</t>
+          <t>Foundation Skill describes a work style (problem solving) that is already embedded in multiple PC-based skills and other skills; it does not represent a distinct task for this unit</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -24960,13 +24948,17 @@
       <c r="X155" t="inlineStr"/>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>keep:5, "Risk Assessment":2</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z155" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA155" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>Disaster Recovery Planning</t>
+        </is>
+      </c>
       <c r="AB155" t="b">
         <v>0</v>
       </c>
@@ -25290,7 +25282,7 @@
       <c r="X157" t="inlineStr"/>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>keep:4, "Strategy Prioritisation":3</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z157" t="b">
@@ -25854,16 +25846,16 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting decisions with relevant data and reasoning.</t>
+          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting each response with relevant data or rationale.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>evidence based answers, stakeholder queries, substantiated responses, data support, reasoning justification</t>
+          <t>evidence based answers, stakeholder queries, substantiated responses, data support, rationale provision</t>
         </is>
       </c>
       <c r="J161" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -25925,7 +25917,7 @@
         <v>0</v>
       </c>
       <c r="W161" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="X161" t="inlineStr">
         <is>
@@ -25950,7 +25942,7 @@
       </c>
       <c r="AG161" t="inlineStr">
         <is>
-          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting decisions with relevant data and reasoning.</t>
+          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting each response with relevant data or rationale.</t>
         </is>
       </c>
       <c r="AH161" t="b">
@@ -25958,7 +25950,7 @@
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>evidence based answers, stakeholder queries, substantiated responses, data support, reasoning justification</t>
+          <t>evidence based answers, stakeholder queries, substantiated responses, data support, rationale provision</t>
         </is>
       </c>
       <c r="AJ161" t="b">
@@ -26004,7 +25996,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>device data inventory, information classification, data mapping, asset documentation, digital records</t>
+          <t>device data inventory, information classification, data mapping, asset documentation, storage verification</t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -26103,7 +26095,7 @@
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>device data inventory, information classification, data mapping, asset documentation, digital records</t>
+          <t>device data inventory, information classification, data mapping, asset documentation, storage verification</t>
         </is>
       </c>
       <c r="AJ162" t="b">
@@ -26144,12 +26136,12 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Secures final approval from designated personnel by organising, presenting, and confirming sign‑off requirements.</t>
+          <t>Secures final approval from designated personnel by managing sign‑off processes and confirming compliance.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>approval process, stakeholder engagement, documentation finalisation, authority confirmation, sign‑off management</t>
+          <t>approval process, stakeholder engagement, compliance confirmation, sign‑off management, finalisation</t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -26242,7 +26234,7 @@
       </c>
       <c r="AG163" t="inlineStr">
         <is>
-          <t>Secures final approval from designated personnel by organising, presenting, and confirming sign‑off requirements.</t>
+          <t>Secures final approval from designated personnel by managing sign‑off processes and confirming compliance.</t>
         </is>
       </c>
       <c r="AH163" t="b">
@@ -26250,7 +26242,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>approval process, stakeholder engagement, documentation finalisation, authority confirmation, sign‑off management</t>
+          <t>approval process, stakeholder engagement, compliance confirmation, sign‑off management, finalisation</t>
         </is>
       </c>
       <c r="AJ163" t="b">
@@ -26291,12 +26283,12 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation, considering relevant legislation and policies.</t>
+          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>process evaluation, transaction analysis, blockchain suitability, regulatory compliance, organisational policy</t>
+          <t>process analysis, transaction evaluation, blockchain suitability, organisational fit, compliance assessment</t>
         </is>
       </c>
       <c r="J164" t="n">
@@ -26397,7 +26389,7 @@
       </c>
       <c r="AG164" t="inlineStr">
         <is>
-          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation, considering relevant legislation and policies.</t>
+          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation.</t>
         </is>
       </c>
       <c r="AH164" t="b">
@@ -26405,7 +26397,7 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>process evaluation, transaction analysis, blockchain suitability, regulatory compliance, organisational policy</t>
+          <t>process analysis, transaction evaluation, blockchain suitability, organisational fit, compliance assessment</t>
         </is>
       </c>
       <c r="AJ164" t="b">
@@ -26426,7 +26418,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Log Requirement Consultation</t>
+          <t>Data Log Strategy Discussion</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -26446,12 +26438,12 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Collaborates with relevant personnel to discuss and confirm data log requirements and processing strategy.</t>
+          <t>Facilitates discussions with relevant personnel to confirm data log requirements and processing strategies.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>data log requirements, processing strategy, personnel consultation, requirement discussion, log strategy confirmation</t>
+          <t>data log requirements, processing strategy, personnel coordination, discussion facilitation, requirement confirmation</t>
         </is>
       </c>
       <c r="J165" t="n">
@@ -26510,7 +26502,7 @@
       </c>
       <c r="U165" t="inlineStr">
         <is>
-          <t>Log Requirement Consultation</t>
+          <t>Data Log Strategy Discussion</t>
         </is>
       </c>
       <c r="V165" t="b">
@@ -26542,7 +26534,7 @@
       </c>
       <c r="AG165" t="inlineStr">
         <is>
-          <t>Collaborates with relevant personnel to discuss and confirm data log requirements and processing strategy.</t>
+          <t>Facilitates discussions with relevant personnel to confirm data log requirements and processing strategies.</t>
         </is>
       </c>
       <c r="AH165" t="b">
@@ -26550,7 +26542,7 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>data log requirements, processing strategy, personnel consultation, requirement discussion, log strategy confirmation</t>
+          <t>data log requirements, processing strategy, personnel coordination, discussion facilitation, requirement confirmation</t>
         </is>
       </c>
       <c r="AJ165" t="b">
@@ -26591,7 +26583,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Evaluates gathered threat data results to confirm reliability and consistency before further processing.</t>
+          <t>Evaluates threat data results to confirm reliability and consistency before further processing.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -26687,7 +26679,7 @@
       </c>
       <c r="AG166" t="inlineStr">
         <is>
-          <t>Evaluates gathered threat data results to confirm reliability and consistency before further processing.</t>
+          <t>Evaluates threat data results to confirm reliability and consistency before further processing.</t>
         </is>
       </c>
       <c r="AH166" t="b">
@@ -26736,12 +26728,12 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Assess the current protection plan's effectiveness and ensure it aligns with organisational requirements and legislative standards.</t>
+          <t>Assess the current protection plan's effectiveness and ensure it aligns with organisational and legislative requirements.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>protection plan assessment, organisational alignment, effectiveness analysis, legislative compliance, critical asset identification</t>
+          <t>protection plan assessment, effectiveness analysis, organisational alignment, legislative compliance, critical asset identification</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -26839,7 +26831,7 @@
       </c>
       <c r="AG167" t="inlineStr">
         <is>
-          <t>Assess the current protection plan's effectiveness and ensure it aligns with organisational requirements and legislative standards.</t>
+          <t>Assess the current protection plan's effectiveness and ensure it aligns with organisational and legislative requirements.</t>
         </is>
       </c>
       <c r="AH167" t="b">
@@ -26847,7 +26839,7 @@
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>protection plan assessment, organisational alignment, effectiveness analysis, legislative compliance, critical asset identification</t>
+          <t>protection plan assessment, effectiveness analysis, organisational alignment, legislative compliance, critical asset identification</t>
         </is>
       </c>
       <c r="AJ167" t="b">
@@ -26873,7 +26865,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>DOMAIN_KNOWLEDGE</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -26883,17 +26875,17 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>THEORETICAL</t>
+          <t>PRACTICAL</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Aligns the current incident response plan with required standards and documents the findings for review.</t>
+          <t>Aligns the current incident response plan with requirements and documents the comparison for stakeholders.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>incident response plan, alignment, documentation, requirements, feedback</t>
+          <t>incident response plan, alignment assessment, documentation, requirements mapping, stakeholder review</t>
         </is>
       </c>
       <c r="J168" t="n">
@@ -26998,7 +26990,7 @@
       </c>
       <c r="AG168" t="inlineStr">
         <is>
-          <t>Aligns the current incident response plan with required standards and documents the findings for review.</t>
+          <t>Aligns the current incident response plan with requirements and documents the comparison for stakeholders.</t>
         </is>
       </c>
       <c r="AH168" t="b">
@@ -27006,7 +26998,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>incident response plan, alignment, documentation, requirements, feedback</t>
+          <t>incident response plan, alignment assessment, documentation, requirements mapping, stakeholder review</t>
         </is>
       </c>
       <c r="AJ168" t="b">
@@ -27205,7 +27197,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Identifies essential business functions, critical data, and software, and evaluates ICT risk impacts on them.</t>
+          <t>Identify essential business functions, data, and software, and assess ICT risk impacts on them.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -27309,7 +27301,7 @@
       </c>
       <c r="AG170" t="inlineStr">
         <is>
-          <t>Identifies essential business functions, critical data, and software, and evaluates ICT risk impacts on them.</t>
+          <t>Identify essential business functions, data, and software, and assess ICT risk impacts on them.</t>
         </is>
       </c>
       <c r="AH170" t="b">
@@ -27363,7 +27355,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>disaster strategy, process documentation, cut‑over criteria, task sign‑off, finalisation</t>
+          <t>disaster strategy, process documentation, cut‑over criteria, final sign‑off, task completion</t>
         </is>
       </c>
       <c r="J171" t="n">
@@ -27470,7 +27462,7 @@
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>disaster strategy, process documentation, cut‑over criteria, task sign‑off, finalisation</t>
+          <t>disaster strategy, process documentation, cut‑over criteria, final sign‑off, task completion</t>
         </is>
       </c>
       <c r="AJ171" t="b">

--- a/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v5.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v5.xlsx
@@ -744,7 +744,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>keep:0, "Stakeholder Viewpoint Elicitation":7</t>
+          <t>keep:0, "Stakeholder Viewpoint Elicitation/Viewpoint Elicitation":7</t>
         </is>
       </c>
       <c r="Z2" t="b">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Skill name uses 'Planning' but evidence describes gathering and evaluating concepts, not planning</t>
+          <t>Skill name uses 'Planning' which is not present in evidence; evidence describes gathering and evaluating concepts, not planning</t>
         </is>
       </c>
       <c r="AF5" t="b">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Solution Viability Assessment</t>
+          <t>Idea Viability Evaluation</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1717,16 +1717,16 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>keep:0, "Solution Viability Assessment":4, "Idea Viability Evaluation":3</t>
+          <t>keep:0, "Idea Viability Evaluation":7</t>
         </is>
       </c>
       <c r="Z8" t="b">
@@ -2202,16 +2202,16 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>keep:0, "Solution Research":7</t>
+          <t>keep:0, "Solution Research":6, "Information Research":1</t>
         </is>
       </c>
       <c r="Z11" t="b">
@@ -2365,7 +2365,7 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>keep:6, "Solution Presentation":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z12" t="b">
@@ -2532,16 +2532,16 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t>postprocess: spelling/redundancy</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>keep:1, "Solution Refinement":6</t>
+          <t>keep:4, "Solution Refinement":3</t>
         </is>
       </c>
       <c r="Z13" t="b">
@@ -2700,13 +2700,9 @@
         </is>
       </c>
       <c r="Z14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Solution Research</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="b">
         <v>0</v>
       </c>
@@ -3021,16 +3017,16 @@
         <v>1</v>
       </c>
       <c r="W16" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>keep:0, "Discussion Facilitation":7</t>
+          <t>keep:1, "Discussion Facilitation":6</t>
         </is>
       </c>
       <c r="Z16" t="b">
@@ -6007,7 +6003,7 @@
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>keep:5, "Device Configuration":2</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z36" t="b">
@@ -6345,7 +6341,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>domain term "inventory" (asset management) not found in unit text</t>
+          <t>Skill name uses 'Inventory Management' which is not a synonym of 'create and maintain register' and does not appear in the unit text; it swaps the action to inventory management rather than register creation/maintenance</t>
         </is>
       </c>
       <c r="AF38" t="b">
@@ -6818,13 +6814,9 @@
         </is>
       </c>
       <c r="Z41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>Security Plan Communication</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA41" t="inlineStr"/>
       <c r="AB41" t="b">
         <v>0</v>
       </c>
@@ -6972,16 +6964,16 @@
         <v>1</v>
       </c>
       <c r="W42" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>keep:0, "Data Risk Categorisation":7</t>
+          <t>keep:2, "Data Risk Categorisation":5</t>
         </is>
       </c>
       <c r="Z42" t="b">
@@ -7032,7 +7024,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Security Plan Communication</t>
+          <t>Physical Security Plan Communication</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -7136,21 +7128,29 @@
         </is>
       </c>
       <c r="V43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W43" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X43" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/7: </t>
+        </is>
+      </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>keep:5, "Physical Security Plan Communication":2</t>
+          <t>keep:1, "Physical Security Plan Communication":5, "Physical Security Planning":1</t>
         </is>
       </c>
       <c r="Z43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>Physical Security Planning</t>
+        </is>
+      </c>
       <c r="AB43" t="b">
         <v>0</v>
       </c>
@@ -7624,12 +7624,12 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>keep:6, "Security Development Monitoring":1</t>
+          <t>keep:5, "Security Development Monitoring":2</t>
         </is>
       </c>
       <c r="Z46" t="b">
@@ -8546,12 +8546,12 @@
         <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Evaluation Documentation":1</t>
         </is>
       </c>
       <c r="Z52" t="b">
@@ -8704,12 +8704,12 @@
         <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "ICT Gap Identification":1</t>
         </is>
       </c>
       <c r="Z53" t="b">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Financial Impact Interpretation</t>
+          <t>Numerical Data Interpretation</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -9155,19 +9155,15 @@
         </is>
       </c>
       <c r="V56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 4/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>keep:0, "Financial Impact Interpretation":4, "Financial Impact Assessment":3</t>
+          <t>keep:5, "Financial Impact Interpretation":2</t>
         </is>
       </c>
       <c r="Z56" t="b">
@@ -10518,12 +10514,12 @@
         <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>keep:6, "Compliance Review":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z65" t="b">
@@ -10723,7 +10719,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Feedback Handling</t>
+          <t>Feedback Management</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -10813,15 +10809,19 @@
         </is>
       </c>
       <c r="V67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W67" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X67" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 4/7: </t>
+        </is>
+      </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>keep:5, "Feedback Management":2</t>
+          <t>keep:3, "Feedback Management":4</t>
         </is>
       </c>
       <c r="Z67" t="b">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Policy Documentation</t>
+          <t>Privacy Policy Documentation</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -11558,15 +11558,19 @@
         </is>
       </c>
       <c r="V72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W72" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X72" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 6/7: </t>
+        </is>
+      </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>keep:5, "Privacy Policy Documentation":2</t>
+          <t>keep:1, "Privacy Policy Documentation":6</t>
         </is>
       </c>
       <c r="Z72" t="b">
@@ -12012,7 +12016,7 @@
         <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr">
@@ -12068,7 +12072,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Digital Information Security</t>
+          <t>Secure Digital Handling</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -12158,19 +12162,15 @@
         </is>
       </c>
       <c r="V76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 5/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>keep:2, "Digital Information Security":5</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z76" t="b">
@@ -12314,16 +12314,16 @@
         <v>1</v>
       </c>
       <c r="W77" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>keep:0, "Policy Distribution":7</t>
+          <t>keep:3, "Policy Distribution":4</t>
         </is>
       </c>
       <c r="Z77" t="b">
@@ -12627,12 +12627,12 @@
         <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>keep:6, "Blockchain Platform Installation":1</t>
+          <t>keep:5, "Blockchain Platform Installation":2</t>
         </is>
       </c>
       <c r="Z79" t="b">
@@ -12683,7 +12683,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Blockchain Anomaly Resolution</t>
+          <t>Blockchain Problem Solving</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -12780,19 +12780,15 @@
         </is>
       </c>
       <c r="V80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W80" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 5/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X80" t="inlineStr"/>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>keep:2, "Blockchain Anomaly Resolution":5</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z80" t="b">
@@ -12804,7 +12800,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Foundation Skill describes problem‑solving behavior that is already embedded in other blockchain solution skills and PCs</t>
+          <t>Foundation Skill describes a general problem‑solving capability that is already embedded in multiple performance criteria and other skills; it does not represent a distinct task for this unit</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -13887,12 +13883,12 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>keep:1, "Maintenance Testing":6</t>
+          <t>keep:2, "Maintenance Testing":5</t>
         </is>
       </c>
       <c r="Z87" t="b">
@@ -15329,9 +15325,13 @@
       </c>
       <c r="AC96" t="inlineStr"/>
       <c r="AD96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE96" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>Skill name uses 'Analysis' while evidence describes 'detect and describe' actions, which are different activities</t>
+        </is>
+      </c>
       <c r="AF96" t="b">
         <v>0</v>
       </c>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>Threat Data Collation</t>
+          <t>Threat Data Collection</t>
         </is>
       </c>
       <c r="AB97" t="b">
@@ -16664,7 +16664,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Threat Data Collation</t>
+          <t>Threat Data Collection</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -16764,19 +16764,15 @@
         </is>
       </c>
       <c r="V105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W105" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 5/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X105" t="inlineStr"/>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>keep:2, "Threat Data Collation":5</t>
+          <t>keep:5, "Threat Data Collation":2</t>
         </is>
       </c>
       <c r="Z105" t="b">
@@ -17693,12 +17689,12 @@
         <v>0</v>
       </c>
       <c r="W111" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X111" t="inlineStr"/>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>keep:6, "Feedback Management":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z111" t="b">
@@ -18016,7 +18012,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>FS describes work style (planning coordination) rather than a distinct task; activity is implicit in strategy development and implementation PCs</t>
+          <t>FS describes work style (planning and coordinating operational detail) rather than a distinct task; capability is already embedded in strategy development and implementation PCs</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -18059,7 +18055,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Protection Plan Analysis</t>
+          <t>Critical Infrastructure Protection Analysis</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -18153,15 +18149,19 @@
         </is>
       </c>
       <c r="V114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W114" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X114" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 6/7: </t>
+        </is>
+      </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:1, "Critical Infrastructure Protection Analysis":6</t>
         </is>
       </c>
       <c r="Z114" t="b">
@@ -18309,12 +18309,12 @@
         <v>0</v>
       </c>
       <c r="W115" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.9099999999999999</v>
       </c>
       <c r="X115" t="inlineStr"/>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>keep:6, "Critical Infrastructure Protection Planning":1</t>
+          <t>keep:5, "Critical Infrastructure Protection Development":2</t>
         </is>
       </c>
       <c r="Z115" t="b">
@@ -19400,12 +19400,12 @@
         <v>0</v>
       </c>
       <c r="W122" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X122" t="inlineStr"/>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>keep:6, "Feedback Documentation Management":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z122" t="b">
@@ -19718,16 +19718,16 @@
         <v>1</v>
       </c>
       <c r="W124" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>keep:0, "Security Contextual Problem Solving/Security Context Problem Solving":6, "Security Anomaly Identification":1</t>
+          <t>keep:0, "Security Contextual Problem Solving/Security Context Problem Solving":7</t>
         </is>
       </c>
       <c r="Z124" t="b">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Security Requirements Documentation</t>
+          <t>Security Findings Documentation</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -19890,7 +19890,7 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>keep:0, "Security Requirements Documentation/Security Findings Documentation":7</t>
+          <t>keep:0, "Security Findings Documentation/Security Requirements Documentation":7</t>
         </is>
       </c>
       <c r="Z125" t="b">
@@ -20546,7 +20546,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>FS describes work style (planning and reviewing) not a distinct task; capability is implicit in other skills and PCs</t>
+          <t>FS describes work style (planning and reviewing) not a distinct task; capability already embedded in PCs and other skills</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -21190,7 +21190,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Foundation Skill describes reading/interpreting documentation, which is already embedded in other skills such as Industry Methodology Research and Security Requirements Analysis</t>
+          <t>FS interpret/read is implicit in prepare/research element</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -21869,16 +21869,16 @@
         <v>1</v>
       </c>
       <c r="W137" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>keep:1, "Incident Response Plan Evaluation":6</t>
+          <t>keep:0, "Incident Response Plan Evaluation":7</t>
         </is>
       </c>
       <c r="Z137" t="b">
@@ -22406,9 +22406,13 @@
       </c>
       <c r="AC140" t="inlineStr"/>
       <c r="AD140" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE140" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>Skill name uses 'Training' but evidence describes creating incident response exercises, red‑teaming activities and training requirements, not delivering training</t>
+        </is>
+      </c>
       <c r="AF140" t="b">
         <v>0</v>
       </c>
@@ -23616,7 +23620,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>FS describes work style (ensuring compliance) rather than a distinct task; capability is implicit in other skills like Risk Analysis and Business Continuity Evaluation</t>
+          <t>FS describes work style/strategic compliance activity already implicit in other skills and not a distinct task for this unit</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -23781,9 +23785,13 @@
         </is>
       </c>
       <c r="Z148" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA148" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>Disaster Recovery Planning</t>
+        </is>
+      </c>
       <c r="AB148" t="b">
         <v>0</v>
       </c>
@@ -24436,16 +24444,16 @@
         <v>1</v>
       </c>
       <c r="W152" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>keep:1, "Business Data Analysis":6</t>
+          <t>keep:0, "Business Data Analysis":7</t>
         </is>
       </c>
       <c r="Z152" t="b">
@@ -24614,9 +24622,13 @@
         </is>
       </c>
       <c r="Z153" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA153" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>element heading - all PCs covered by other skills</t>
+        </is>
+      </c>
       <c r="AB153" t="b">
         <v>0</v>
       </c>
@@ -24774,7 +24786,7 @@
         <v>0</v>
       </c>
       <c r="W154" t="n">
-        <v>0.9428571428571428</v>
+        <v>0.95</v>
       </c>
       <c r="X154" t="inlineStr"/>
       <c r="Y154" t="inlineStr">
@@ -24791,7 +24803,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Foundation Skill describes a work style (problem solving) that is already embedded in multiple PC-based skills and other skills; it does not represent a distinct task for this unit</t>
+          <t>Foundation Skill describes a general problem‑solving capability that is already embedded in multiple performance criteria and other skills; it does not represent a distinct standalone task for this unit</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -24952,13 +24964,9 @@
         </is>
       </c>
       <c r="Z155" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA155" t="inlineStr">
-        <is>
-          <t>Disaster Recovery Planning</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA155" t="inlineStr"/>
       <c r="AB155" t="b">
         <v>0</v>
       </c>
@@ -25282,7 +25290,7 @@
       <c r="X157" t="inlineStr"/>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:4, "Strategy Prioritisation":3</t>
         </is>
       </c>
       <c r="Z157" t="b">
@@ -25846,12 +25854,12 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting each response with relevant data or rationale.</t>
+          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting decisions with relevant data and reasoning.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>evidence based answers, stakeholder queries, substantiated responses, data support, rationale provision</t>
+          <t>evidence based answers, stakeholder queries, substantiated responses, data support, reasoning justification</t>
         </is>
       </c>
       <c r="J161" t="n">
@@ -25942,7 +25950,7 @@
       </c>
       <c r="AG161" t="inlineStr">
         <is>
-          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting each response with relevant data or rationale.</t>
+          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting decisions with relevant data and reasoning.</t>
         </is>
       </c>
       <c r="AH161" t="b">
@@ -25950,7 +25958,7 @@
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>evidence based answers, stakeholder queries, substantiated responses, data support, rationale provision</t>
+          <t>evidence based answers, stakeholder queries, substantiated responses, data support, reasoning justification</t>
         </is>
       </c>
       <c r="AJ161" t="b">
@@ -25996,7 +26004,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>device data inventory, information classification, data mapping, asset documentation, storage verification</t>
+          <t>device data inventory, information classification, data mapping, asset documentation, digital records</t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -26095,7 +26103,7 @@
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>device data inventory, information classification, data mapping, asset documentation, storage verification</t>
+          <t>device data inventory, information classification, data mapping, asset documentation, digital records</t>
         </is>
       </c>
       <c r="AJ162" t="b">
@@ -26116,7 +26124,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Sign‑off Coordination</t>
+          <t>Sign‑off Acquisition</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -26136,12 +26144,12 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Secures final approval from designated personnel by managing sign‑off processes and confirming compliance.</t>
+          <t>Secures final approval from designated stakeholders by coordinating, presenting, and confirming sign‑off requirements.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>approval process, stakeholder engagement, compliance confirmation, sign‑off management, finalisation</t>
+          <t>approval coordination, stakeholder confirmation, final sign‑off, approval documentation, sign‑off process</t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -26202,7 +26210,7 @@
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>Sign‑off Coordination</t>
+          <t>Sign‑off Acquisition</t>
         </is>
       </c>
       <c r="V163" t="b">
@@ -26234,7 +26242,7 @@
       </c>
       <c r="AG163" t="inlineStr">
         <is>
-          <t>Secures final approval from designated personnel by managing sign‑off processes and confirming compliance.</t>
+          <t>Secures final approval from designated stakeholders by coordinating, presenting, and confirming sign‑off requirements.</t>
         </is>
       </c>
       <c r="AH163" t="b">
@@ -26242,7 +26250,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>approval process, stakeholder engagement, compliance confirmation, sign‑off management, finalisation</t>
+          <t>approval coordination, stakeholder confirmation, final sign‑off, approval documentation, sign‑off process</t>
         </is>
       </c>
       <c r="AJ163" t="b">
@@ -26283,16 +26291,16 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation.</t>
+          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation, considering relevant legislation and policies.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>process analysis, transaction evaluation, blockchain suitability, organisational fit, compliance assessment</t>
+          <t>process analysis, transaction evaluation, blockchain suitability, regulatory compliance, organisational policy</t>
         </is>
       </c>
       <c r="J164" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
@@ -26364,7 +26372,7 @@
         <v>0</v>
       </c>
       <c r="W164" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="X164" t="inlineStr">
         <is>
@@ -26389,7 +26397,7 @@
       </c>
       <c r="AG164" t="inlineStr">
         <is>
-          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation.</t>
+          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation, considering relevant legislation and policies.</t>
         </is>
       </c>
       <c r="AH164" t="b">
@@ -26397,7 +26405,7 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>process analysis, transaction evaluation, blockchain suitability, organisational fit, compliance assessment</t>
+          <t>process analysis, transaction evaluation, blockchain suitability, regulatory compliance, organisational policy</t>
         </is>
       </c>
       <c r="AJ164" t="b">
@@ -26418,7 +26426,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Data Log Strategy Discussion</t>
+          <t>Log Requirement Consultation</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -26438,12 +26446,12 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Facilitates discussions with relevant personnel to confirm data log requirements and processing strategies.</t>
+          <t>Facilitates discussion with relevant personnel to confirm data log requirements and processing strategy.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>data log requirements, processing strategy, personnel coordination, discussion facilitation, requirement confirmation</t>
+          <t>data log requirements, processing strategy, personnel consultation, requirement confirmation, log discussion</t>
         </is>
       </c>
       <c r="J165" t="n">
@@ -26502,7 +26510,7 @@
       </c>
       <c r="U165" t="inlineStr">
         <is>
-          <t>Data Log Strategy Discussion</t>
+          <t>Log Requirement Consultation</t>
         </is>
       </c>
       <c r="V165" t="b">
@@ -26534,7 +26542,7 @@
       </c>
       <c r="AG165" t="inlineStr">
         <is>
-          <t>Facilitates discussions with relevant personnel to confirm data log requirements and processing strategies.</t>
+          <t>Facilitates discussion with relevant personnel to confirm data log requirements and processing strategy.</t>
         </is>
       </c>
       <c r="AH165" t="b">
@@ -26542,7 +26550,7 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>data log requirements, processing strategy, personnel coordination, discussion facilitation, requirement confirmation</t>
+          <t>data log requirements, processing strategy, personnel consultation, requirement confirmation, log discussion</t>
         </is>
       </c>
       <c r="AJ165" t="b">
@@ -26583,7 +26591,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Evaluates threat data results to confirm reliability and consistency before further processing.</t>
+          <t>Evaluates gathered threat data results to confirm reliability and consistency before further processing.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -26679,7 +26687,7 @@
       </c>
       <c r="AG166" t="inlineStr">
         <is>
-          <t>Evaluates threat data results to confirm reliability and consistency before further processing.</t>
+          <t>Evaluates gathered threat data results to confirm reliability and consistency before further processing.</t>
         </is>
       </c>
       <c r="AH166" t="b">
@@ -26708,7 +26716,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Plan Alignment Evaluation</t>
+          <t>Protection Alignment Evaluation</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -26728,12 +26736,12 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Assess the current protection plan's effectiveness and ensure it aligns with organisational and legislative requirements.</t>
+          <t>Evaluates how well the current protection plan meets organisational needs and regulatory requirements.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>protection plan assessment, effectiveness analysis, organisational alignment, legislative compliance, critical asset identification</t>
+          <t>plan effectiveness, organisational alignment, regulatory compliance, critical assets, system segmentation</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -26799,7 +26807,7 @@
       </c>
       <c r="U167" t="inlineStr">
         <is>
-          <t>Plan Alignment Evaluation</t>
+          <t>Protection Alignment Evaluation</t>
         </is>
       </c>
       <c r="V167" t="b">
@@ -26831,7 +26839,7 @@
       </c>
       <c r="AG167" t="inlineStr">
         <is>
-          <t>Assess the current protection plan's effectiveness and ensure it aligns with organisational and legislative requirements.</t>
+          <t>Evaluates how well the current protection plan meets organisational needs and regulatory requirements.</t>
         </is>
       </c>
       <c r="AH167" t="b">
@@ -26839,7 +26847,7 @@
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>protection plan assessment, effectiveness analysis, organisational alignment, legislative compliance, critical asset identification</t>
+          <t>plan effectiveness, organisational alignment, regulatory compliance, critical assets, system segmentation</t>
         </is>
       </c>
       <c r="AJ167" t="b">
@@ -26865,7 +26873,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>TECHNICAL</t>
+          <t>DOMAIN_KNOWLEDGE</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -26875,21 +26883,21 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>PRACTICAL</t>
+          <t>THEORETICAL</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Aligns the current incident response plan with requirements and documents the comparison for stakeholders.</t>
+          <t>Aligns the current incident response plan with required standards and documents the findings for review.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>incident response plan, alignment assessment, documentation, requirements mapping, stakeholder review</t>
+          <t>incident response plan, alignment assessment, documentation, requirements mapping, feedback handling</t>
         </is>
       </c>
       <c r="J168" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -26965,7 +26973,7 @@
         <v>0</v>
       </c>
       <c r="W168" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="X168" t="inlineStr">
         <is>
@@ -26990,7 +26998,7 @@
       </c>
       <c r="AG168" t="inlineStr">
         <is>
-          <t>Aligns the current incident response plan with requirements and documents the comparison for stakeholders.</t>
+          <t>Aligns the current incident response plan with required standards and documents the findings for review.</t>
         </is>
       </c>
       <c r="AH168" t="b">
@@ -26998,7 +27006,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>incident response plan, alignment assessment, documentation, requirements mapping, stakeholder review</t>
+          <t>incident response plan, alignment assessment, documentation, requirements mapping, feedback handling</t>
         </is>
       </c>
       <c r="AJ168" t="b">
@@ -27039,12 +27047,12 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Assist in gathering, processing, and preserving incident evidence in line with organisational requirements and standards.</t>
+          <t>Assist in gathering, processing, and securely preserving incident evidence in line with established requirements.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>evidence collection, evidence processing, evidence preservation, incident response, organisational requirements</t>
+          <t>evidence collection, evidence processing, evidence preservation, incident response, forensic requirements</t>
         </is>
       </c>
       <c r="J169" t="n">
@@ -27148,7 +27156,7 @@
       </c>
       <c r="AG169" t="inlineStr">
         <is>
-          <t>Assist in gathering, processing, and preserving incident evidence in line with organisational requirements and standards.</t>
+          <t>Assist in gathering, processing, and securely preserving incident evidence in line with established requirements.</t>
         </is>
       </c>
       <c r="AH169" t="b">
@@ -27156,7 +27164,7 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>evidence collection, evidence processing, evidence preservation, incident response, organisational requirements</t>
+          <t>evidence collection, evidence processing, evidence preservation, incident response, forensic requirements</t>
         </is>
       </c>
       <c r="AJ169" t="b">
@@ -27197,16 +27205,16 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Identify essential business functions, data, and software, and assess ICT risk impacts on them.</t>
+          <t>Identifies essential business functions, critical data, and software, and evaluates ICT risk impacts on them.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>business critical functions, security environment, critical data, software assets, ICT risk assessment</t>
+          <t>business critical functions, security environment, critical data, software assets, ICT risk impact</t>
         </is>
       </c>
       <c r="J170" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -27276,7 +27284,7 @@
         <v>0</v>
       </c>
       <c r="W170" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="X170" t="inlineStr">
         <is>
@@ -27301,7 +27309,7 @@
       </c>
       <c r="AG170" t="inlineStr">
         <is>
-          <t>Identify essential business functions, data, and software, and assess ICT risk impacts on them.</t>
+          <t>Identifies essential business functions, critical data, and software, and evaluates ICT risk impacts on them.</t>
         </is>
       </c>
       <c r="AH170" t="b">
@@ -27309,7 +27317,7 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>business critical functions, security environment, critical data, software assets, ICT risk assessment</t>
+          <t>business critical functions, security environment, critical data, software assets, ICT risk impact</t>
         </is>
       </c>
       <c r="AJ170" t="b">
@@ -27350,12 +27358,12 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>The worker identifies, records, and finalises disaster strategy processes, cut‑over criteria, and obtains sign‑off.</t>
+          <t>Creates and records detailed disaster strategy processes, cut‑over criteria, and secures final task sign‑off.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>disaster strategy, process documentation, cut‑over criteria, final sign‑off, task completion</t>
+          <t>disaster strategy, process documentation, cut‑over criteria, task sign‑off, implementation</t>
         </is>
       </c>
       <c r="J171" t="n">
@@ -27454,7 +27462,7 @@
       </c>
       <c r="AG171" t="inlineStr">
         <is>
-          <t>The worker identifies, records, and finalises disaster strategy processes, cut‑over criteria, and obtains sign‑off.</t>
+          <t>Creates and records detailed disaster strategy processes, cut‑over criteria, and secures final task sign‑off.</t>
         </is>
       </c>
       <c r="AH171" t="b">
@@ -27462,7 +27470,7 @@
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>disaster strategy, process documentation, cut‑over criteria, final sign‑off, task completion</t>
+          <t>disaster strategy, process documentation, cut‑over criteria, task sign‑off, implementation</t>
         </is>
       </c>
       <c r="AJ171" t="b">

--- a/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v5.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined_v5.xlsx
@@ -744,7 +744,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>keep:0, "Stakeholder Viewpoint Elicitation/Viewpoint Elicitation":7</t>
+          <t>keep:0, "Stakeholder Viewpoint Elicitation":7</t>
         </is>
       </c>
       <c r="Z2" t="b">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Skill name uses 'Planning' which is not present in evidence; evidence describes gathering and evaluating concepts, not planning</t>
+          <t>Skill name uses 'Planning' but evidence describes gathering and evaluating concepts, not planning</t>
         </is>
       </c>
       <c r="AF5" t="b">
@@ -2206,12 +2206,12 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>keep:0, "Solution Research":6, "Information Research":1</t>
+          <t>keep:0, "Solution Research":5, "Information Research":2</t>
         </is>
       </c>
       <c r="Z11" t="b">
@@ -2365,7 +2365,7 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Solution Presentation":1</t>
         </is>
       </c>
       <c r="Z12" t="b">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>keep:4, "Solution Refinement":3</t>
+          <t>keep:5, "Solution Refinement":2</t>
         </is>
       </c>
       <c r="Z13" t="b">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Discussion Facilitation</t>
+          <t>Team Facilitation</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3014,19 +3014,15 @@
         </is>
       </c>
       <c r="V16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 6/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>keep:1, "Discussion Facilitation":6</t>
+          <t>keep:4, "Discussion Facilitation":3</t>
         </is>
       </c>
       <c r="Z16" t="b">
@@ -3809,12 +3805,12 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>keep:1, "Insight Presentation":6</t>
+          <t>keep:2, "Insight Presentation":5</t>
         </is>
       </c>
       <c r="Z21" t="b">
@@ -4285,7 +4281,7 @@
         <v>1</v>
       </c>
       <c r="W24" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9028571428571429</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -5998,12 +5994,12 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Device Configuration":1</t>
         </is>
       </c>
       <c r="Z36" t="b">
@@ -6341,7 +6337,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>Skill name uses 'Inventory Management' which is not a synonym of 'create and maintain register' and does not appear in the unit text; it swaps the action to inventory management rather than register creation/maintenance</t>
+          <t>domain term "inventory" (asset management) not found in unit text</t>
         </is>
       </c>
       <c r="AF38" t="b">
@@ -6964,16 +6960,16 @@
         <v>1</v>
       </c>
       <c r="W42" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>keep:2, "Data Risk Categorisation":5</t>
+          <t>keep:0, "Data Risk Categorisation":7</t>
         </is>
       </c>
       <c r="Z42" t="b">
@@ -7135,12 +7131,12 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>keep:1, "Physical Security Plan Communication":5, "Physical Security Planning":1</t>
+          <t>keep:3, "Physical Security Plan Communication":4</t>
         </is>
       </c>
       <c r="Z43" t="b">
@@ -7624,12 +7620,12 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>keep:5, "Security Development Monitoring":2</t>
+          <t>keep:6, "Security Development Monitoring":1</t>
         </is>
       </c>
       <c r="Z46" t="b">
@@ -8546,12 +8542,12 @@
         <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>keep:6, "Evaluation Documentation":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z52" t="b">
@@ -8704,12 +8700,12 @@
         <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>keep:6, "ICT Gap Identification":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z53" t="b">
@@ -9068,7 +9064,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Numerical Data Interpretation</t>
+          <t>Financial Impact Interpretation</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -9155,15 +9151,19 @@
         </is>
       </c>
       <c r="V56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W56" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X56" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 4/7: </t>
+        </is>
+      </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>keep:5, "Financial Impact Interpretation":2</t>
+          <t>keep:2, "Financial Impact Interpretation":4, "Financial Impact Assessment":1</t>
         </is>
       </c>
       <c r="Z56" t="b">
@@ -10719,7 +10719,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Feedback Management</t>
+          <t>Feedback Handling</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -10809,19 +10809,15 @@
         </is>
       </c>
       <c r="V67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 4/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>keep:3, "Feedback Management":4</t>
+          <t>keep:5, "Feedback Management":2</t>
         </is>
       </c>
       <c r="Z67" t="b">
@@ -11561,16 +11557,16 @@
         <v>1</v>
       </c>
       <c r="W72" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>keep:1, "Privacy Policy Documentation":6</t>
+          <t>keep:0, "Privacy Policy Documentation":7</t>
         </is>
       </c>
       <c r="Z72" t="b">
@@ -12016,7 +12012,7 @@
         <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr">
@@ -12314,16 +12310,16 @@
         <v>1</v>
       </c>
       <c r="W77" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>keep:3, "Policy Distribution":4</t>
+          <t>keep:0, "Policy Distribution":7</t>
         </is>
       </c>
       <c r="Z77" t="b">
@@ -12632,7 +12628,7 @@
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>keep:5, "Blockchain Platform Installation":2</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z79" t="b">
@@ -12788,7 +12784,7 @@
       <c r="X80" t="inlineStr"/>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:5, "Blockchain Anomaly Resolution":2</t>
         </is>
       </c>
       <c r="Z80" t="b">
@@ -12800,7 +12796,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Foundation Skill describes a general problem‑solving capability that is already embedded in multiple performance criteria and other skills; it does not represent a distinct task for this unit</t>
+          <t>Foundation Skill describes a work style (problem solving) that is already embedded in other skills and PCs</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -15325,13 +15321,9 @@
       </c>
       <c r="AC96" t="inlineStr"/>
       <c r="AD96" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE96" t="inlineStr">
-        <is>
-          <t>Skill name uses 'Analysis' while evidence describes 'detect and describe' actions, which are different activities</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AE96" t="inlineStr"/>
       <c r="AF96" t="b">
         <v>0</v>
       </c>
@@ -15475,12 +15467,12 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>keep:1, "Dataset Creation":6</t>
+          <t>keep:3, "Dataset Creation":4</t>
         </is>
       </c>
       <c r="Z97" t="b">
@@ -15488,7 +15480,7 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>Threat Data Collection</t>
+          <t>Threat Data Collation</t>
         </is>
       </c>
       <c r="AB97" t="b">
@@ -16454,13 +16446,9 @@
         </is>
       </c>
       <c r="Z103" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA103" t="inlineStr">
-        <is>
-          <t>Data Log Ingestion</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA103" t="inlineStr"/>
       <c r="AB103" t="b">
         <v>0</v>
       </c>
@@ -16608,12 +16596,12 @@
         <v>0</v>
       </c>
       <c r="W104" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X104" t="inlineStr"/>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>keep:6, "Threat Findings Communication":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z104" t="b">
@@ -16664,7 +16652,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Threat Data Collection</t>
+          <t>Threat Data Collation</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -16764,15 +16752,19 @@
         </is>
       </c>
       <c r="V105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W105" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X105" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/7: </t>
+        </is>
+      </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>keep:5, "Threat Data Collation":2</t>
+          <t>keep:2, "Threat Data Collation":5</t>
         </is>
       </c>
       <c r="Z105" t="b">
@@ -17995,12 +17987,12 @@
         <v>0</v>
       </c>
       <c r="W113" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X113" t="inlineStr"/>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Protection Strategy Coordination":1</t>
         </is>
       </c>
       <c r="Z113" t="b">
@@ -18012,7 +18004,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>FS describes work style (planning and coordinating operational detail) rather than a distinct task; capability is already embedded in strategy development and implementation PCs</t>
+          <t>FS describes work style (planning and coordination) rather than a distinct task; capability already embedded in strategy development and implementation PCs</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -18156,12 +18148,12 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>keep:1, "Critical Infrastructure Protection Analysis":6</t>
+          <t>keep:3, "Critical Infrastructure Protection Analysis":4</t>
         </is>
       </c>
       <c r="Z114" t="b">
@@ -18309,12 +18301,12 @@
         <v>0</v>
       </c>
       <c r="W115" t="n">
-        <v>0.9099999999999999</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="X115" t="inlineStr"/>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>keep:5, "Critical Infrastructure Protection Development":2</t>
+          <t>keep:6, "Critical Infrastructure Protection Planning":1</t>
         </is>
       </c>
       <c r="Z115" t="b">
@@ -18772,12 +18764,12 @@
         <v>0</v>
       </c>
       <c r="W118" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X118" t="inlineStr"/>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Risk Evaluation":1</t>
         </is>
       </c>
       <c r="Z118" t="b">
@@ -19727,7 +19719,7 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>keep:0, "Security Contextual Problem Solving/Security Context Problem Solving":7</t>
+          <t>keep:0, "Security Contextual Problem Solving":7</t>
         </is>
       </c>
       <c r="Z124" t="b">
@@ -21173,12 +21165,12 @@
         <v>0</v>
       </c>
       <c r="W133" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X133" t="inlineStr"/>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Technical Documentation Reading":1</t>
         </is>
       </c>
       <c r="Z133" t="b">
@@ -21370,7 +21362,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>FS describes work style (autonomous decision‑making) rather than a distinct task; the activity is implicit in other PC‑based skills</t>
+          <t>generic FS capability "Autonomous Decision Making" is implicit in other skills</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -22054,9 +22046,13 @@
         </is>
       </c>
       <c r="Z138" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA138" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>Incident Response Plan Evaluation</t>
+        </is>
+      </c>
       <c r="AB138" t="b">
         <v>0</v>
       </c>
@@ -22385,16 +22381,16 @@
         <v>1</v>
       </c>
       <c r="W140" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>keep:0, "Incident Response Training":7</t>
+          <t>keep:0, "Incident Response Training":6, "Incident Response Training Design":1</t>
         </is>
       </c>
       <c r="Z140" t="b">
@@ -22406,13 +22402,9 @@
       </c>
       <c r="AC140" t="inlineStr"/>
       <c r="AD140" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE140" t="inlineStr">
-        <is>
-          <t>Skill name uses 'Training' but evidence describes creating incident response exercises, red‑teaming activities and training requirements, not delivering training</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AE140" t="inlineStr"/>
       <c r="AF140" t="b">
         <v>0</v>
       </c>
@@ -22621,7 +22613,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Risk Analysis</t>
+          <t>Technical Data Interpretation</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -22738,21 +22730,29 @@
         </is>
       </c>
       <c r="V142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W142" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X142" t="inlineStr"/>
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 7/7: </t>
+        </is>
+      </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:0, "Technical Data Interpretation":7</t>
         </is>
       </c>
       <c r="Z142" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA142" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>Technical Data Interpretation</t>
+        </is>
+      </c>
       <c r="AB142" t="b">
         <v>0</v>
       </c>
@@ -23286,7 +23286,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>FS capability is embedded in other skills such as Risk Analysis and Incident Response Plan Evaluation, not a distinct standalone skill</t>
+          <t>FS interpret/read is implicit in prepare/research element</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -23620,7 +23620,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>FS describes work style/strategic compliance activity already implicit in other skills and not a distinct task for this unit</t>
+          <t>FS describes work style/strategic compliance, not a distinct task; capability already embedded in other skills and PCs</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -24123,7 +24123,7 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>Disaster Strategy Documentation</t>
+          <t>element heading - all PCs covered by other skills</t>
         </is>
       </c>
       <c r="AB150" t="b">
@@ -24803,7 +24803,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Foundation Skill describes a general problem‑solving capability that is already embedded in multiple performance criteria and other skills; it does not represent a distinct standalone task for this unit</t>
+          <t>generic FS capability "Problem Solving" is implicit in other skills</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -24964,9 +24964,13 @@
         </is>
       </c>
       <c r="Z155" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA155" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>Disaster Recovery Planning</t>
+        </is>
+      </c>
       <c r="AB155" t="b">
         <v>0</v>
       </c>
@@ -25290,7 +25294,7 @@
       <c r="X157" t="inlineStr"/>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>keep:4, "Strategy Prioritisation":3</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z157" t="b">
@@ -25789,9 +25793,13 @@
         </is>
       </c>
       <c r="Z160" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA160" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>element heading - all PCs covered by other skills</t>
+        </is>
+      </c>
       <c r="AB160" t="b">
         <v>0</v>
       </c>
@@ -25989,7 +25997,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>ASSIST</t>
+          <t>APPLY</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -25999,12 +26007,12 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Assists in confirming and documenting the types of information stored on each registered digital device.</t>
+          <t>Identify and confirm the types of information stored on each registered digital device within the organisation.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>device data inventory, information classification, data mapping, asset documentation, digital records</t>
+          <t>device data inventory, information classification, digital asset records, data held verification, device content audit</t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -26095,7 +26103,7 @@
       </c>
       <c r="AG162" t="inlineStr">
         <is>
-          <t>Assists in confirming and documenting the types of information stored on each registered digital device.</t>
+          <t>Identify and confirm the types of information stored on each registered digital device within the organisation.</t>
         </is>
       </c>
       <c r="AH162" t="b">
@@ -26103,7 +26111,7 @@
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>device data inventory, information classification, data mapping, asset documentation, digital records</t>
+          <t>device data inventory, information classification, digital asset records, data held verification, device content audit</t>
         </is>
       </c>
       <c r="AJ162" t="b">
@@ -26124,7 +26132,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Sign‑off Acquisition</t>
+          <t>Sign‑off Coordination</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -26144,12 +26152,12 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Secures final approval from designated stakeholders by coordinating, presenting, and confirming sign‑off requirements.</t>
+          <t>Secures final approval from designated personnel by managing sign‑off processes and confirming compliance.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>approval coordination, stakeholder confirmation, final sign‑off, approval documentation, sign‑off process</t>
+          <t>approval management, stakeholder engagement, compliance confirmation, sign‑off process, finalisation</t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -26210,7 +26218,7 @@
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>Sign‑off Acquisition</t>
+          <t>Sign‑off Coordination</t>
         </is>
       </c>
       <c r="V163" t="b">
@@ -26242,7 +26250,7 @@
       </c>
       <c r="AG163" t="inlineStr">
         <is>
-          <t>Secures final approval from designated stakeholders by coordinating, presenting, and confirming sign‑off requirements.</t>
+          <t>Secures final approval from designated personnel by managing sign‑off processes and confirming compliance.</t>
         </is>
       </c>
       <c r="AH163" t="b">
@@ -26250,7 +26258,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>approval coordination, stakeholder confirmation, final sign‑off, approval documentation, sign‑off process</t>
+          <t>approval management, stakeholder engagement, compliance confirmation, sign‑off process, finalisation</t>
         </is>
       </c>
       <c r="AJ163" t="b">
@@ -26291,12 +26299,12 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation, considering relevant legislation and policies.</t>
+          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>process analysis, transaction evaluation, blockchain suitability, regulatory compliance, organisational policy</t>
+          <t>process analysis, transaction evaluation, blockchain suitability, organisational fit, compliance assessment</t>
         </is>
       </c>
       <c r="J164" t="n">
@@ -26397,7 +26405,7 @@
       </c>
       <c r="AG164" t="inlineStr">
         <is>
-          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation, considering relevant legislation and policies.</t>
+          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation.</t>
         </is>
       </c>
       <c r="AH164" t="b">
@@ -26405,7 +26413,7 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>process analysis, transaction evaluation, blockchain suitability, regulatory compliance, organisational policy</t>
+          <t>process analysis, transaction evaluation, blockchain suitability, organisational fit, compliance assessment</t>
         </is>
       </c>
       <c r="AJ164" t="b">
@@ -26451,7 +26459,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>data log requirements, processing strategy, personnel consultation, requirement confirmation, log discussion</t>
+          <t>data log requirements, processing strategy, personnel consultation, requirement confirmation, collaborative discussion</t>
         </is>
       </c>
       <c r="J165" t="n">
@@ -26550,7 +26558,7 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>data log requirements, processing strategy, personnel consultation, requirement confirmation, log discussion</t>
+          <t>data log requirements, processing strategy, personnel consultation, requirement confirmation, collaborative discussion</t>
         </is>
       </c>
       <c r="AJ165" t="b">
@@ -26716,7 +26724,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Protection Alignment Evaluation</t>
+          <t>Plan Alignment Evaluation</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -26736,12 +26744,12 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Evaluates how well the current protection plan meets organisational needs and regulatory requirements.</t>
+          <t>Evaluates how well the current protection plan meets organisational needs and regulatory standards.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>plan effectiveness, organisational alignment, regulatory compliance, critical assets, system segmentation</t>
+          <t>plan effectiveness, organisational requirements, alignment assessment, regulatory compliance, critical assets</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -26807,7 +26815,7 @@
       </c>
       <c r="U167" t="inlineStr">
         <is>
-          <t>Protection Alignment Evaluation</t>
+          <t>Plan Alignment Evaluation</t>
         </is>
       </c>
       <c r="V167" t="b">
@@ -26839,7 +26847,7 @@
       </c>
       <c r="AG167" t="inlineStr">
         <is>
-          <t>Evaluates how well the current protection plan meets organisational needs and regulatory requirements.</t>
+          <t>Evaluates how well the current protection plan meets organisational needs and regulatory standards.</t>
         </is>
       </c>
       <c r="AH167" t="b">
@@ -26847,7 +26855,7 @@
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>plan effectiveness, organisational alignment, regulatory compliance, critical assets, system segmentation</t>
+          <t>plan effectiveness, organisational requirements, alignment assessment, regulatory compliance, critical assets</t>
         </is>
       </c>
       <c r="AJ167" t="b">
@@ -26868,12 +26876,12 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Incident Plan Alignment</t>
+          <t>Plan Alignment Documentation</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>DOMAIN_KNOWLEDGE</t>
+          <t>TECHNICAL</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -26883,21 +26891,21 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>THEORETICAL</t>
+          <t>PRACTICAL</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Aligns the current incident response plan with required standards and documents the findings for review.</t>
+          <t>The worker aligns the current incident response plan with requirements and documents the findings for review.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>incident response plan, alignment assessment, documentation, requirements mapping, feedback handling</t>
+          <t>incident response plan, alignment, documentation, requirements, feedback</t>
         </is>
       </c>
       <c r="J168" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -26966,14 +26974,14 @@
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>Incident Plan Alignment</t>
+          <t>Plan Alignment Documentation</t>
         </is>
       </c>
       <c r="V168" t="b">
         <v>0</v>
       </c>
       <c r="W168" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="X168" t="inlineStr">
         <is>
@@ -26998,7 +27006,7 @@
       </c>
       <c r="AG168" t="inlineStr">
         <is>
-          <t>Aligns the current incident response plan with required standards and documents the findings for review.</t>
+          <t>The worker aligns the current incident response plan with requirements and documents the findings for review.</t>
         </is>
       </c>
       <c r="AH168" t="b">
@@ -27006,7 +27014,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>incident response plan, alignment assessment, documentation, requirements mapping, feedback handling</t>
+          <t>incident response plan, alignment, documentation, requirements, feedback</t>
         </is>
       </c>
       <c r="AJ168" t="b">
@@ -27047,16 +27055,16 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Assist in gathering, processing, and securely preserving incident evidence in line with established requirements.</t>
+          <t>Assist in gathering, processing, and securely preserving evidence in line with established incident response requirements.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>evidence collection, evidence processing, evidence preservation, incident response, forensic requirements</t>
+          <t>evidence collection, evidence processing, evidence preservation, incident response, assistance</t>
         </is>
       </c>
       <c r="J169" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -27131,7 +27139,7 @@
         <v>0</v>
       </c>
       <c r="W169" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="X169" t="inlineStr">
         <is>
@@ -27156,7 +27164,7 @@
       </c>
       <c r="AG169" t="inlineStr">
         <is>
-          <t>Assist in gathering, processing, and securely preserving incident evidence in line with established requirements.</t>
+          <t>Assist in gathering, processing, and securely preserving evidence in line with established incident response requirements.</t>
         </is>
       </c>
       <c r="AH169" t="b">
@@ -27164,7 +27172,7 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>evidence collection, evidence processing, evidence preservation, incident response, forensic requirements</t>
+          <t>evidence collection, evidence processing, evidence preservation, incident response, assistance</t>
         </is>
       </c>
       <c r="AJ169" t="b">
@@ -27214,7 +27222,7 @@
         </is>
       </c>
       <c r="J170" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -27284,7 +27292,7 @@
         <v>0</v>
       </c>
       <c r="W170" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="X170" t="inlineStr">
         <is>
